--- a/Acervo_Jurisprudencial.xlsx
+++ b/Acervo_Jurisprudencial.xlsx
@@ -20,16 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penal" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Civil — Condominio'!$A$1:$V$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fiscal'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Laboral'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Penal'!$A$1:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Penal'!$A$1:$V$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,23 +629,23 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2857,7 +2857,7 @@
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>pen-tor-001</t>
+          <t>auto-2032145</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>1ª Sala SCJN</t>
+          <t>2ª Sala SCJN</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Tortura de coimputado e investigación oficiosa</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
@@ -2905,61 +2905,57 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>TORTURA. OBLIGACIONES DE LA AUTORIDAD JUDICIAL CUANDO EL QUEJOSO ALEGA QUE SU COIMPUTADO FUE TORTURADO PARA HACER IMPUTACIONES EN SU CONTRA.</t>
+          <t>TORTURA Y OTROS TRATOS O PENAS CRUELES, INHUMANOS O DEGRADANTES EN EL ESTADO DE TAMAULIPAS. EL ARTÍCULO 3 DE LA LEY RELATIVA ES INCONSTITUCIONAL, AL ESTABLECER LA APLICACIÓN SUPLETORIA DE LA LEY GENERAL DE LA MATERIA.</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>2029150</t>
+          <t>2032145</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr"/>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>05 de julio de 2024</t>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
         </is>
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P9" s="13" t="inlineStr"/>
       <c r="Q9" s="13" t="inlineStr">
         <is>
-          <t>Cuando el quejoso alega que su coimputado fue torturado para incriminarlo, la autoridad judicial tiene obligación oficiosa de investigar, aunque la víctima directa de la tortura sea otra persona.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R9" s="13" t="inlineStr">
         <is>
-          <t>Expande deber de investigar tortura a casos de coimputados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S9" s="13" t="inlineStr">
         <is>
-          <t>Si tu cliente está siendo incriminado por coimputado torturado: invocar esta tesis para excluir prueba.</t>
-        </is>
-      </c>
-      <c r="T9" s="13" t="inlineStr">
-        <is>
-          <t>1a./J. 118/2024 (11a.)</t>
-        </is>
-      </c>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T9" s="13" t="inlineStr"/>
       <c r="U9" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029150</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032145</t>
         </is>
       </c>
       <c r="V9" s="13" t="inlineStr">
         <is>
-          <t>tortura · coimputado · 1a./J. 118/2024 · investigación oficiosa</t>
+          <t>Tortura · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>sen-003</t>
+          <t>pen-tor-001</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
@@ -2977,22 +2973,22 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Uso lúdico de cannabis</t>
+          <t>Tortura</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Amparos en revisión 237/2014 y siguientes</t>
+          <t>Tortura de coimputado e investigación oficiosa</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -3007,61 +3003,69 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Inconstitucionalidad de la prohibición absoluta de uso lúdico de cannabis</t>
+          <t>TORTURA. OBLIGACIONES DE LA AUTORIDAD JUDICIAL CUANDO EL QUEJOSO ALEGA QUE SU COIMPUTADO FUE TORTURADO PARA HACER IMPUTACIONES EN SU CONTRA.</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>Amparo en Revisión 237/2014</t>
+          <t>2029150</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>2015 y reiteración 2018</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="inlineStr"/>
+          <t>05 de julio de 2024</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>La prohibición absoluta del autoconsumo lúdico de cannabis viola el libre desarrollo de la personalidad (art. 1 CPEUM). El Estado no puede prohibir actos que no afectan a terceros bajo argumento paternalista.</t>
+          <t>Cuando el quejoso alega que su coimputado fue torturado para incriminarlo, la autoridad judicial tiene obligación oficiosa de investigar, aunque la víctima directa de la tortura sea otra persona.</t>
         </is>
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>Hito de libre desarrollo de la personalidad y autonomía individual.</t>
+          <t>Expande deber de investigar tortura a casos de coimputados.</t>
         </is>
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>Cinco sentencias en el mismo sentido configuraron declaratoria general de inconstitucionalidad en 2021. El Congreso aún no ha cumplido la orden de legislar regulando la sustancia.</t>
-        </is>
-      </c>
-      <c r="T10" s="11" t="inlineStr"/>
+          <t>Si tu cliente está siendo incriminado por coimputado torturado: invocar esta tesis para excluir prueba.</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>1a./J. 118/2024 (11a.)</t>
+        </is>
+      </c>
       <c r="U10" s="11" t="inlineStr">
         <is>
-          <t>https://www.scjn.gob.mx/sites/default/files/proyectos_resolucion_scjn/documento/2018-11/AR-237-2014.pdf</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029150</t>
         </is>
       </c>
       <c r="V10" s="11" t="inlineStr">
         <is>
-          <t>cannabis · libre desarrollo personalidad · declaratoria general</t>
+          <t>tortura · coimputado · 1a./J. 118/2024 · investigación oficiosa</t>
         </is>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>pen-rep-001</t>
+          <t>sen-003</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Plenos Regionales</t>
+          <t>1ª Sala SCJN</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -3071,22 +3075,22 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Uso lúdico de cannabis</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Compensación directa como parte de reparación integral</t>
+          <t>Amparos en revisión 237/2014 y siguientes</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
@@ -3101,69 +3105,61 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
+          <t>Inconstitucionalidad de la prohibición absoluta de uso lúdico de cannabis</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>2032030</t>
+          <t>Amparo en Revisión 237/2014</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr"/>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+          <t>2015 y reiteración 2018</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr"/>
       <c r="P11" s="13" t="inlineStr"/>
       <c r="Q11" s="13" t="inlineStr">
         <is>
-          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
+          <t>La prohibición absoluta del autoconsumo lúdico de cannabis viola el libre desarrollo de la personalidad (art. 1 CPEUM). El Estado no puede prohibir actos que no afectan a terceros bajo argumento paternalista.</t>
         </is>
       </c>
       <c r="R11" s="13" t="inlineStr">
         <is>
-          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
+          <t>Hito de libre desarrollo de la personalidad y autonomía individual.</t>
         </is>
       </c>
       <c r="S11" s="13" t="inlineStr">
         <is>
-          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
-        </is>
-      </c>
-      <c r="T11" s="13" t="inlineStr">
-        <is>
-          <t>PR.P.T.CN. J/8 P (12a.)</t>
-        </is>
-      </c>
+          <t>Cinco sentencias en el mismo sentido configuraron declaratoria general de inconstitucionalidad en 2021. El Congreso aún no ha cumplido la orden de legislar regulando la sustancia.</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr"/>
       <c r="U11" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
+          <t>https://www.scjn.gob.mx/sites/default/files/proyectos_resolucion_scjn/documento/2018-11/AR-237-2014.pdf</t>
         </is>
       </c>
       <c r="V11" s="13" t="inlineStr">
         <is>
-          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
+          <t>cannabis · libre desarrollo personalidad · declaratoria general</t>
         </is>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>pen-rep-001</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>Plenos Regionales</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -3173,12 +3169,12 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Reparación del daño</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Compensación directa como parte de reparación integral</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -3188,7 +3184,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -3203,57 +3199,61 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2032030</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
         </is>
       </c>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
         </is>
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
-        </is>
-      </c>
-      <c r="T12" s="11" t="inlineStr"/>
+          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>PR.P.T.CN. J/8 P (12a.)</t>
+        </is>
+      </c>
       <c r="U12" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
         </is>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>pen-cad-002</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
@@ -3301,18 +3301,18 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2027962</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O13" s="13" t="inlineStr">
@@ -3323,35 +3323,35 @@
       <c r="P13" s="13" t="inlineStr"/>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
         </is>
       </c>
       <c r="S13" s="13" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr"/>
       <c r="U13" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
         </is>
       </c>
       <c r="V13" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
         </is>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>pen-cad-003</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Transgresión no torna ilícita la prueba</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -3399,57 +3399,57 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2021845</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
         </is>
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
         </is>
       </c>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>cadena custodia · valor probatorio · exclusión</t>
         </is>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>pen-ppo-001</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2032107</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
@@ -3519,33 +3519,131 @@
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
         </is>
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr"/>
       <c r="U15" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>PPO · víctima · legitimación · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>pen-ppo-002</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Cese cuando MP no prueba prolongación</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>2032108</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr"/>
+      <c r="Q16" s="11" t="inlineStr">
+        <is>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+        </is>
+      </c>
+      <c r="R16" s="11" t="inlineStr">
+        <is>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+        </is>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr"/>
+      <c r="U16" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
         </is>
       </c>
-      <c r="V15" s="13" t="inlineStr">
+      <c r="V16" s="11" t="inlineStr">
         <is>
           <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V15"/>
+  <autoFilter ref="A1:V16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3556,7 +3654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:V108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5816,7 +5914,7 @@
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>civ-urb-002</t>
+          <t>auto-2032122</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
@@ -5834,12 +5932,12 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Urbanización y desarrollo urbano</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Licencia de construcción y derechos adquiridos</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -5849,7 +5947,7 @@
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -5864,49 +5962,57 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>LICENCIA DE CONSTRUCCIÓN. SU NEGATIVA POR CAMBIO DE ZONIFICACIÓN POSTERIOR A LA SOLICITUD VIOLA EL DERECHO ADQUIRIDO DEL PARTICULAR.</t>
+          <t>CANCELACIÓN DE LICENCIA PARA CONDUCIR. LA PREVISTA EN LOS ARTÍCULOS 168 Y 26, FRACCIÓN XXX, DE LA LEY DE MOVILIDAD Y SEGURIDAD VIAL DEL ESTADO DE PUEBLA, ES INCONSTITUCIONAL.</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>Criterio administrativo</t>
+          <t>2032122</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr"/>
-      <c r="N25" s="13" t="inlineStr"/>
-      <c r="O25" s="13" t="inlineStr"/>
+      <c r="N25" s="13" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O25" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P25" s="13" t="inlineStr"/>
       <c r="Q25" s="13" t="inlineStr">
         <is>
-          <t>Si el particular presentó solicitud completa de licencia bajo cierta zonificación, el cambio posterior de uso de suelo no puede aplicarse retroactivamente para negar la licencia, en respeto al principio de irretroactividad y derechos adquiridos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R25" s="13" t="inlineStr">
         <is>
-          <t>Protege desarrollos inmobiliarios frente a cambios de zonificación.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S25" s="13" t="inlineStr">
         <is>
-          <t>Conserva siempre acuse sellado de recepción de solicitud. La fecha de presentación fija el régimen aplicable. Combatir negativas tardías por vía de amparo administrativo.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T25" s="13" t="inlineStr"/>
       <c r="U25" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030153</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032122</t>
         </is>
       </c>
       <c r="V25" s="13" t="inlineStr">
         <is>
-          <t>licencia · zonificación · derechos adquiridos · irretroactividad</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="26" ht="80" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-001</t>
+          <t>civ-urb-002</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
@@ -5914,22 +6020,22 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>1ª Sala SCJN</t>
+          <t>2ª Sala SCJN</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Urbanización y desarrollo urbano</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Terminación por falta de pago</t>
+          <t>Licencia de construcción y derechos adquiridos</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -5949,17 +6055,17 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>CDMX — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA FALTA DE PAGO DE DOS O MÁS MENSUALIDADES ACTUALIZA LA CAUSAL DE RESCISIÓN, SIN NECESIDAD DE INTERPELACIÓN PREVIA.</t>
+          <t>LICENCIA DE CONSTRUCCIÓN. SU NEGATIVA POR CAMBIO DE ZONIFICACIÓN POSTERIOR A LA SOLICITUD VIOLA EL DERECHO ADQUIRIDO DEL PARTICULAR.</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>167030</t>
+          <t>Criterio administrativo</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr"/>
@@ -5968,35 +6074,35 @@
       <c r="P26" s="11" t="inlineStr"/>
       <c r="Q26" s="11" t="inlineStr">
         <is>
-          <t>El art. 2489 fracc. I CCCDMX permite al arrendador rescindir el contrato cuando el arrendatario adeude dos o más mensualidades. No se requiere requerimiento previo: la sola omisión de pago configura la causal.</t>
+          <t>Si el particular presentó solicitud completa de licencia bajo cierta zonificación, el cambio posterior de uso de suelo no puede aplicarse retroactivamente para negar la licencia, en respeto al principio de irretroactividad y derechos adquiridos.</t>
         </is>
       </c>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>Es la causal más usada en juicios de arrendamiento en CDMX.</t>
+          <t>Protege desarrollos inmobiliarios frente a cambios de zonificación.</t>
         </is>
       </c>
       <c r="S26" s="11" t="inlineStr">
         <is>
-          <t>El recibo de pago oportuno es la principal defensa del inquilino. Si demandas, acompaña el contrato y certificación de adeudo; si te demandan, ofrece consignación en pago como excepción.</t>
+          <t>Conserva siempre acuse sellado de recepción de solicitud. La fecha de presentación fija el régimen aplicable. Combatir negativas tardías por vía de amparo administrativo.</t>
         </is>
       </c>
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/167030</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030153</t>
         </is>
       </c>
       <c r="V26" s="11" t="inlineStr">
         <is>
-          <t>falta de pago · rescisión · art. 2489 CCCDMX</t>
+          <t>licencia · zonificación · derechos adquiridos · irretroactividad</t>
         </is>
       </c>
     </row>
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-002</t>
+          <t>civ-arr-001</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
@@ -6019,7 +6125,7 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Vía sumaria y oral</t>
+          <t>Terminación por falta de pago</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -6039,17 +6145,17 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>CDMX — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO DE INMUEBLES PARA HABITACIÓN. LA VÍA PROCEDENTE PARA SU CONTROVERSIA ES LA ESPECIAL DE ARRENDAMIENTO O LA ORAL CIVIL, SEGÚN LA CUANTÍA Y FECHA DEL CONTRATO.</t>
+          <t>ARRENDAMIENTO. LA FALTA DE PAGO DE DOS O MÁS MENSUALIDADES ACTUALIZA LA CAUSAL DE RESCISIÓN, SIN NECESIDAD DE INTERPELACIÓN PREVIA.</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>167030</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr"/>
@@ -6058,35 +6164,35 @@
       <c r="P27" s="13" t="inlineStr"/>
       <c r="Q27" s="13" t="inlineStr">
         <is>
-          <t>En CDMX, conforme a la reforma 2014 al CPCDMX, los conflictos de arrendamiento se tramitan por vía oral civil. Las controversias anteriores a esa reforma siguen tramitándose por la vía especial de arrendamiento (arts. 957-968 CPCDMX).</t>
+          <t>El art. 2489 fracc. I CCCDMX permite al arrendador rescindir el contrato cuando el arrendatario adeude dos o más mensualidades. No se requiere requerimiento previo: la sola omisión de pago configura la causal.</t>
         </is>
       </c>
       <c r="R27" s="13" t="inlineStr">
         <is>
-          <t>Define competencia y vía. Error en la vía = desechamiento.</t>
+          <t>Es la causal más usada en juicios de arrendamiento en CDMX.</t>
         </is>
       </c>
       <c r="S27" s="13" t="inlineStr">
         <is>
-          <t>Hay que verificar fecha del contrato y de la primera demanda. La oralidad acelera el procedimiento pero exige mayor rigor probatorio en audiencia.</t>
+          <t>El recibo de pago oportuno es la principal defensa del inquilino. Si demandas, acompaña el contrato y certificación de adeudo; si te demandan, ofrece consignación en pago como excepción.</t>
         </is>
       </c>
       <c r="T27" s="13" t="inlineStr"/>
       <c r="U27" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/167030</t>
         </is>
       </c>
       <c r="V27" s="13" t="inlineStr">
         <is>
-          <t>vía oral · vía especial · competencia</t>
+          <t>falta de pago · rescisión · art. 2489 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>sen-006</t>
+          <t>civ-arr-002</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
@@ -6104,17 +6210,17 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Compensación económica por trabajo doméstico</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Amparo Directo en Revisión 269/2014</t>
+          <t>Vía sumaria y oral</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -6129,58 +6235,54 @@
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>Federal — aplica CDMX/Edomex</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Compensación por trabajo doméstico no remunerado en divorcio</t>
+          <t>ARRENDAMIENTO DE INMUEBLES PARA HABITACIÓN. LA VÍA PROCEDENTE PARA SU CONTROVERSIA ES LA ESPECIAL DE ARRENDAMIENTO O LA ORAL CIVIL, SEGÚN LA CUANTÍA Y FECHA DEL CONTRATO.</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>ADR 269/2014</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr"/>
-      <c r="N28" s="11" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
+      <c r="N28" s="11" t="inlineStr"/>
       <c r="O28" s="11" t="inlineStr"/>
       <c r="P28" s="11" t="inlineStr"/>
       <c r="Q28" s="11" t="inlineStr">
         <is>
-          <t>El cónyuge (mayoritariamente mujer) que se dedicó preponderantemente al trabajo doméstico tiene derecho a compensación económica en el divorcio, hasta el 50% del patrimonio adquirido durante el matrimonio, aun bajo régimen de separación de bienes.</t>
+          <t>En CDMX, conforme a la reforma 2014 al CPCDMX, los conflictos de arrendamiento se tramitan por vía oral civil. Las controversias anteriores a esa reforma siguen tramitándose por la vía especial de arrendamiento (arts. 957-968 CPCDMX).</t>
         </is>
       </c>
       <c r="R28" s="11" t="inlineStr">
         <is>
-          <t>Reconoce trabajo doméstico como aportación económica.</t>
+          <t>Define competencia y vía. Error en la vía = desechamiento.</t>
         </is>
       </c>
       <c r="S28" s="11" t="inlineStr">
         <is>
-          <t>Recogida hoy en art. 267 fracc. VI CCCDMX y análogos en Edomex. Hay que probar la dedicación preponderante al hogar y la imposibilidad o limitación para generar patrimonio propio.</t>
+          <t>Hay que verificar fecha del contrato y de la primera demanda. La oralidad acelera el procedimiento pero exige mayor rigor probatorio en audiencia.</t>
         </is>
       </c>
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>https://www.scjn.gob.mx/sites/default/files/proyectos_resolucion_scjn/documento/2016-12/ADR-269-2014.pdf</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V28" s="11" t="inlineStr">
         <is>
-          <t>compensación · trabajo doméstico · divorcio · perspectiva de género</t>
+          <t>vía oral · vía especial · competencia</t>
         </is>
       </c>
     </row>
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>civ-con-001</t>
+          <t>sen-006</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
@@ -6198,17 +6300,17 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Contratos civiles — Teoría general</t>
+          <t>Compensación económica por trabajo doméstico</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Autonomía de la voluntad y orden público</t>
+          <t>Amparo Directo en Revisión 269/2014</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -6223,54 +6325,58 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — aplica CDMX/Edomex</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>AUTONOMÍA DE LA VOLUNTAD EN MATERIA CONTRACTUAL. SU EJERCICIO ENCUENTRA LÍMITES EN EL ORDEN PÚBLICO Y EN LOS DERECHOS HUMANOS.</t>
+          <t>Compensación por trabajo doméstico no remunerado en divorcio</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>Criterio doctrinal</t>
+          <t>ADR 269/2014</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
-      <c r="N29" s="13" t="inlineStr"/>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
       <c r="O29" s="13" t="inlineStr"/>
       <c r="P29" s="13" t="inlineStr"/>
       <c r="Q29" s="13" t="inlineStr">
         <is>
-          <t>Las partes pueden contratar libremente, pero las cláusulas que vulneren el orden público, las buenas costumbres o derechos humanos son nulas. El juez tiene facultad de control constitucional difuso sobre cláusulas contractuales.</t>
+          <t>El cónyuge (mayoritariamente mujer) que se dedicó preponderantemente al trabajo doméstico tiene derecho a compensación económica en el divorcio, hasta el 50% del patrimonio adquirido durante el matrimonio, aun bajo régimen de separación de bienes.</t>
         </is>
       </c>
       <c r="R29" s="13" t="inlineStr">
         <is>
-          <t>Base del control de cláusulas abusivas en contratos privados.</t>
+          <t>Reconoce trabajo doméstico como aportación económica.</t>
         </is>
       </c>
       <c r="S29" s="13" t="inlineStr">
         <is>
-          <t>Permite atacar cláusulas leoninas en contratos privados aun fuera del régimen de consumo (LFPC). Útil en contratos de adhesión empresariales y arrendamientos abusivos.</t>
+          <t>Recogida hoy en art. 267 fracc. VI CCCDMX y análogos en Edomex. Hay que probar la dedicación preponderante al hogar y la imposibilidad o limitación para generar patrimonio propio.</t>
         </is>
       </c>
       <c r="T29" s="13" t="inlineStr"/>
       <c r="U29" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031733</t>
+          <t>https://www.scjn.gob.mx/sites/default/files/proyectos_resolucion_scjn/documento/2016-12/ADR-269-2014.pdf</t>
         </is>
       </c>
       <c r="V29" s="13" t="inlineStr">
         <is>
-          <t>autonomía · orden público · control difuso</t>
+          <t>compensación · trabajo doméstico · divorcio · perspectiva de género</t>
         </is>
       </c>
     </row>
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>civ-con-002</t>
+          <t>civ-con-001</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
@@ -6293,7 +6399,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Interpretación contractual</t>
+          <t>Autonomía de la voluntad y orden público</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -6318,12 +6424,12 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>INTERPRETACIÓN DE LOS CONTRATOS. REGLAS APLICABLES Y JERARQUÍA ENTRE ELLAS.</t>
+          <t>AUTONOMÍA DE LA VOLUNTAD EN MATERIA CONTRACTUAL. SU EJERCICIO ENCUENTRA LÍMITES EN EL ORDEN PÚBLICO Y EN LOS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>Criterio normativo</t>
+          <t>Criterio doctrinal</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr"/>
@@ -6332,35 +6438,35 @@
       <c r="P30" s="11" t="inlineStr"/>
       <c r="Q30" s="11" t="inlineStr">
         <is>
-          <t>Conforme a los arts. 1851-1859 CCCDMX, primero se atiende a la literalidad si es clara; si hay ambigüedad, a la intención evidente de las partes; en último lugar, a usos, costumbres y al sentido más conforme con la naturaleza del contrato.</t>
+          <t>Las partes pueden contratar libremente, pero las cláusulas que vulneren el orden público, las buenas costumbres o derechos humanos son nulas. El juez tiene facultad de control constitucional difuso sobre cláusulas contractuales.</t>
         </is>
       </c>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>Marco para resolver controversias de cláusulas oscuras.</t>
+          <t>Base del control de cláusulas abusivas en contratos privados.</t>
         </is>
       </c>
       <c r="S30" s="11" t="inlineStr">
         <is>
-          <t>Cuando litigues una cláusula ambigua, ofrece prueba de contexto: correos previos, tratos preliminares, ejecución parcial. La intención no se prueba sola.</t>
+          <t>Permite atacar cláusulas leoninas en contratos privados aun fuera del régimen de consumo (LFPC). Útil en contratos de adhesión empresariales y arrendamientos abusivos.</t>
         </is>
       </c>
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032022</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031733</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
         <is>
-          <t>interpretación · intención · literalidad</t>
+          <t>autonomía · orden público · control difuso</t>
         </is>
       </c>
     </row>
     <row r="31" ht="80" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>civ-con-003</t>
+          <t>civ-con-002</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
@@ -6383,7 +6489,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Pacta sunt servanda vs. rebus sic stantibus</t>
+          <t>Interpretación contractual</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -6408,12 +6514,12 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>TEORÍA DE LA IMPREVISIÓN. SU APLICABILIDAD EN MATERIA CIVIL Y MERCANTIL FEDERAL ANTE SUCESOS EXTRAORDINARIOS QUE ROMPAN EL EQUILIBRIO CONTRACTUAL.</t>
+          <t>INTERPRETACIÓN DE LOS CONTRATOS. REGLAS APLICABLES Y JERARQUÍA ENTRE ELLAS.</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>Arts. 1796 bis y 1796 ter CCCDMX</t>
+          <t>Criterio normativo</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr"/>
@@ -6422,35 +6528,35 @@
       <c r="P31" s="13" t="inlineStr"/>
       <c r="Q31" s="13" t="inlineStr">
         <is>
-          <t>Ante hechos extraordinarios, imprevisibles y ajenos a las partes que rompan gravemente el equilibrio del contrato, procede la revisión judicial o la resolución, aunque la legislación civil federal no la regule expresamente.</t>
+          <t>Conforme a los arts. 1851-1859 CCCDMX, primero se atiende a la literalidad si es clara; si hay ambigüedad, a la intención evidente de las partes; en último lugar, a usos, costumbres y al sentido más conforme con la naturaleza del contrato.</t>
         </is>
       </c>
       <c r="R31" s="13" t="inlineStr">
         <is>
-          <t>Marco para impacto COVID-19, inflación severa, devaluaciones.</t>
+          <t>Marco para resolver controversias de cláusulas oscuras.</t>
         </is>
       </c>
       <c r="S31" s="13" t="inlineStr">
         <is>
-          <t>CCCDMX sí la reconoce expresamente (arts. 1796 bis y 1796 ter, reforma 2010). En contratos mercantiles federales hay que invocar buena fe (art. 1796 CCF supletorio) y los criterios de la Primera Sala. Esencial para casos pandemia.</t>
+          <t>Cuando litigues una cláusula ambigua, ofrece prueba de contexto: correos previos, tratos preliminares, ejecución parcial. La intención no se prueba sola.</t>
         </is>
       </c>
       <c r="T31" s="13" t="inlineStr"/>
       <c r="U31" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030399</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032022</t>
         </is>
       </c>
       <c r="V31" s="13" t="inlineStr">
         <is>
-          <t>imprevisión · rebus sic stantibus · buena fe · COVID</t>
+          <t>interpretación · intención · literalidad</t>
         </is>
       </c>
     </row>
     <row r="32" ht="80" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>sen-017</t>
+          <t>civ-con-003</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
@@ -6468,17 +6574,17 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Divorcio incausado</t>
+          <t>Contratos civiles — Teoría general</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Amparo Directo en Revisión 917/2009 y línea posterior</t>
+          <t>Pacta sunt servanda vs. rebus sic stantibus</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -6493,58 +6599,54 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa — desafectación del vínculo y dignidad</t>
+          <t>TEORÍA DE LA IMPREVISIÓN. SU APLICABILIDAD EN MATERIA CIVIL Y MERCANTIL FEDERAL ANTE SUCESOS EXTRAORDINARIOS QUE ROMPAN EL EQUILIBRIO CONTRACTUAL.</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>ADR 917/2009 — Primera Sala</t>
+          <t>Arts. 1796 bis y 1796 ter CCCDMX</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr"/>
-      <c r="N32" s="11" t="inlineStr">
-        <is>
-          <t>2009-2015 (consolidada)</t>
-        </is>
-      </c>
+      <c r="N32" s="11" t="inlineStr"/>
       <c r="O32" s="11" t="inlineStr"/>
       <c r="P32" s="11" t="inlineStr"/>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>La voluntad unilateral de uno de los cónyuges es suficiente para disolver el matrimonio. Exigir causales específicas violenta el libre desarrollo de la personalidad y la dignidad. El divorcio incausado es constitucional y debe garantizarse en todas las entidades.</t>
+          <t>Ante hechos extraordinarios, imprevisibles y ajenos a las partes que rompan gravemente el equilibrio del contrato, procede la revisión judicial o la resolución, aunque la legislación civil federal no la regule expresamente.</t>
         </is>
       </c>
       <c r="R32" s="11" t="inlineStr">
         <is>
-          <t>Cambia paradigma del divorcio en México: de divorcio-sanción a divorcio-remedio.</t>
+          <t>Marco para impacto COVID-19, inflación severa, devaluaciones.</t>
         </is>
       </c>
       <c r="S32" s="11" t="inlineStr">
         <is>
-          <t>Hoy en CDMX (reforma 2008), Edomex y la mayoría de entidades el divorcio incausado es la regla. Donde aún subsisten causales (algunas entidades), el amparo es la vía.</t>
+          <t>CCCDMX sí la reconoce expresamente (arts. 1796 bis y 1796 ter, reforma 2010). En contratos mercantiles federales hay que invocar buena fe (art. 1796 CCF supletorio) y los criterios de la Primera Sala. Esencial para casos pandemia.</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029516</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030399</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · libre desarrollo personalidad · ADR 917/2009</t>
+          <t>imprevisión · rebus sic stantibus · buena fe · COVID</t>
         </is>
       </c>
     </row>
     <row r="33" ht="80" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>civ-ext-002</t>
+          <t>sen-017</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
@@ -6562,22 +6664,22 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Divorcio incausado</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Buena fe del adquirente</t>
+          <t>Amparo Directo en Revisión 917/2009 y línea posterior</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -6587,54 +6689,58 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>EXTINCIÓN DE DOMINIO. LA BUENA FE DEL TERCERO ADQUIRENTE CONSTITUYE UNA DEFENSA PLENA QUE DEBE PROBARSE OBJETIVAMENTE.</t>
+          <t>Divorcio sin expresión de causa — desafectación del vínculo y dignidad</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>2022450</t>
+          <t>ADR 917/2009 — Primera Sala</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr"/>
-      <c r="N33" s="13" t="inlineStr"/>
+      <c r="N33" s="13" t="inlineStr">
+        <is>
+          <t>2009-2015 (consolidada)</t>
+        </is>
+      </c>
       <c r="O33" s="13" t="inlineStr"/>
       <c r="P33" s="13" t="inlineStr"/>
       <c r="Q33" s="13" t="inlineStr">
         <is>
-          <t>La buena fe se prueba mediante elementos objetivos: precio de mercado, debida diligencia registral, ausencia de vínculos con el sujeto activo del ilícito, razonabilidad de la operación.</t>
+          <t>La voluntad unilateral de uno de los cónyuges es suficiente para disolver el matrimonio. Exigir causales específicas violenta el libre desarrollo de la personalidad y la dignidad. El divorcio incausado es constitucional y debe garantizarse en todas las entidades.</t>
         </is>
       </c>
       <c r="R33" s="13" t="inlineStr">
         <is>
-          <t>Estándar probatorio para terceros adquirentes.</t>
+          <t>Cambia paradigma del divorcio en México: de divorcio-sanción a divorcio-remedio.</t>
         </is>
       </c>
       <c r="S33" s="13" t="inlineStr">
         <is>
-          <t>Recomendaciones para clientes que compran: due diligence documental, pago bancarizado trazable, certificado de libertad de gravamen reciente y conservación de toda evidencia.</t>
+          <t>Hoy en CDMX (reforma 2008), Edomex y la mayoría de entidades el divorcio incausado es la regla. Donde aún subsisten causales (algunas entidades), el amparo es la vía.</t>
         </is>
       </c>
       <c r="T33" s="13" t="inlineStr"/>
       <c r="U33" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2022450</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029516</t>
         </is>
       </c>
       <c r="V33" s="13" t="inlineStr">
         <is>
-          <t>buena fe · tercero · due diligence</t>
+          <t>divorcio incausado · libre desarrollo personalidad · ADR 917/2009</t>
         </is>
       </c>
     </row>
     <row r="34" ht="80" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>civ-fid-001</t>
+          <t>civ-ext-002</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
@@ -6652,12 +6758,12 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Naturaleza jurídica</t>
+          <t>Buena fe del adquirente</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -6667,7 +6773,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -6682,12 +6788,12 @@
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>FIDEICOMISO. SU NATURALEZA JURÍDICA Y EFECTOS DE LA TRANSMISIÓN FIDUCIARIA DE LA PROPIEDAD.</t>
+          <t>EXTINCIÓN DE DOMINIO. LA BUENA FE DEL TERCERO ADQUIRENTE CONSTITUYE UNA DEFENSA PLENA QUE DEBE PROBARSE OBJETIVAMENTE.</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>Arts. 381-394 LGTOC</t>
+          <t>2022450</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr"/>
@@ -6696,35 +6802,35 @@
       <c r="P34" s="11" t="inlineStr"/>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>El fideicomiso (arts. 381-394 LGTOC) implica transmisión de titularidad fiduciaria a una institución de crédito (no propiedad plena), afectada a un fin lícito y determinado, en beneficio de un fideicomisario.</t>
+          <t>La buena fe se prueba mediante elementos objetivos: precio de mercado, debida diligencia registral, ausencia de vínculos con el sujeto activo del ilícito, razonabilidad de la operación.</t>
         </is>
       </c>
       <c r="R34" s="11" t="inlineStr">
         <is>
-          <t>Base conceptual para todo litigio fiduciario.</t>
+          <t>Estándar probatorio para terceros adquirentes.</t>
         </is>
       </c>
       <c r="S34" s="11" t="inlineStr">
         <is>
-          <t>La fiduciaria no es dueña plena: actúa por encargo. Su responsabilidad es por diligencia en el encargo, no por resultado. En procedimientos de ejecución, hay que diferenciar afectación patrimonial fiduciaria de patrimonio propio del banco.</t>
+          <t>Recomendaciones para clientes que compran: due diligence documental, pago bancarizado trazable, certificado de libertad de gravamen reciente y conservación de toda evidencia.</t>
         </is>
       </c>
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2023996</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2022450</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
         <is>
-          <t>fideicomiso · fiduciaria · patrimonio afecto</t>
+          <t>buena fe · tercero · due diligence</t>
         </is>
       </c>
     </row>
     <row r="35" ht="80" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>civ-fid-002</t>
+          <t>civ-fid-001</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
@@ -6747,12 +6853,12 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y ejecución</t>
+          <t>Naturaleza jurídica</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -6772,12 +6878,12 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>FIDEICOMISO DE GARANTÍA. SU EJECUCIÓN EXTRAJUDICIAL ES CONSTITUCIONAL SIEMPRE QUE SE OBSERVEN LAS FORMALIDADES DEL ARTÍCULO 403 BIS DE LA LGTOC.</t>
+          <t>FIDEICOMISO. SU NATURALEZA JURÍDICA Y EFECTOS DE LA TRANSMISIÓN FIDUCIARIA DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>Arts. 381-394 LGTOC</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr"/>
@@ -6786,35 +6892,35 @@
       <c r="P35" s="13" t="inlineStr"/>
       <c r="Q35" s="13" t="inlineStr">
         <is>
-          <t>El procedimiento extrajudicial de ejecución del fideicomiso de garantía es constitucional porque no implica privación arbitraria de propiedad: el fideicomitente consintió por escrito y existe garantía de audiencia previa al remate.</t>
+          <t>El fideicomiso (arts. 381-394 LGTOC) implica transmisión de titularidad fiduciaria a una institución de crédito (no propiedad plena), afectada a un fin lícito y determinado, en beneficio de un fideicomisario.</t>
         </is>
       </c>
       <c r="R35" s="13" t="inlineStr">
         <is>
-          <t>Valida ejecuciones privadas habituales en banca de inversión.</t>
+          <t>Base conceptual para todo litigio fiduciario.</t>
         </is>
       </c>
       <c r="S35" s="13" t="inlineStr">
         <is>
-          <t>El deudor garantizado tiene poca defensa frente al fideicomiso de garantía: solo amparo si se incumplen las formalidades. Antes de firmar, hay que negociar plazos y notificaciones.</t>
+          <t>La fiduciaria no es dueña plena: actúa por encargo. Su responsabilidad es por diligencia en el encargo, no por resultado. En procedimientos de ejecución, hay que diferenciar afectación patrimonial fiduciaria de patrimonio propio del banco.</t>
         </is>
       </c>
       <c r="T35" s="13" t="inlineStr"/>
       <c r="U35" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2023996</t>
         </is>
       </c>
       <c r="V35" s="13" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · ejecución extrajudicial · art. 403 bis LGTOC</t>
+          <t>fideicomiso · fiduciaria · patrimonio afecto</t>
         </is>
       </c>
     </row>
     <row r="36" ht="80" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>sen-011</t>
+          <t>civ-fid-002</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
@@ -6832,17 +6938,17 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Identidad de género — rectificación de acta</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Amparo en Revisión 1317/2017</t>
+          <t>Fideicomiso de garantía y ejecución</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -6862,53 +6968,49 @@
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Identidad de género — derecho a rectificación administrativa de acta de nacimiento</t>
+          <t>FIDEICOMISO DE GARANTÍA. SU EJECUCIÓN EXTRAJUDICIAL ES CONSTITUCIONAL SIEMPRE QUE SE OBSERVEN LAS FORMALIDADES DEL ARTÍCULO 403 BIS DE LA LGTOC.</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>AR 1317/2017 — Primera Sala</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr"/>
-      <c r="N36" s="11" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+      <c r="N36" s="11" t="inlineStr"/>
       <c r="O36" s="11" t="inlineStr"/>
       <c r="P36" s="11" t="inlineStr"/>
       <c r="Q36" s="11" t="inlineStr">
         <is>
-          <t>Toda persona tiene derecho a la rectificación de su acta de nacimiento por motivo de identidad de género, sin necesidad de procedimiento judicial complejo, peritajes médicos invasivos ni intervención quirúrgica. Procede vía administrativa expedita.</t>
+          <t>El procedimiento extrajudicial de ejecución del fideicomiso de garantía es constitucional porque no implica privación arbitraria de propiedad: el fideicomitente consintió por escrito y existe garantía de audiencia previa al remate.</t>
         </is>
       </c>
       <c r="R36" s="11" t="inlineStr">
         <is>
-          <t>Marco para rectificaciones de género en toda la República.</t>
+          <t>Valida ejecuciones privadas habituales en banca de inversión.</t>
         </is>
       </c>
       <c r="S36" s="11" t="inlineStr">
         <is>
-          <t>CDMX y Edomex ya tienen procedimientos administrativos para ello. Para otras entidades sin marco legal, el amparo con esta jurisprudencia abre la vía.</t>
+          <t>El deudor garantizado tiene poca defensa frente al fideicomiso de garantía: solo amparo si se incumplen las formalidades. Antes de firmar, hay que negociar plazos y notificaciones.</t>
         </is>
       </c>
       <c r="T36" s="11" t="inlineStr"/>
       <c r="U36" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V36" s="11" t="inlineStr">
         <is>
-          <t>identidad de género · trans · rectificación · acta de nacimiento</t>
+          <t>fideicomiso garantía · ejecución extrajudicial · art. 403 bis LGTOC</t>
         </is>
       </c>
     </row>
     <row r="37" ht="80" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-001</t>
+          <t>sen-011</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
@@ -6926,17 +7028,17 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Identidad de género — rectificación de acta</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Procedencia de la vía especial</t>
+          <t>Amparo en Revisión 1317/2017</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -6951,54 +7053,58 @@
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>Federal — aplica CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO. PROCEDE CUANDO EL CRÉDITO CONSTA EN ESCRITURA PÚBLICA DEBIDAMENTE REGISTRADA Y SE EJERCITA LA ACCIÓN REAL DE PAGO.</t>
+          <t>Identidad de género — derecho a rectificación administrativa de acta de nacimiento</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>AR 1317/2017 — Primera Sala</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr"/>
-      <c r="N37" s="13" t="inlineStr"/>
+      <c r="N37" s="13" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="O37" s="13" t="inlineStr"/>
       <c r="P37" s="13" t="inlineStr"/>
       <c r="Q37" s="13" t="inlineStr">
         <is>
-          <t>La vía especial hipotecaria (arts. 468-488 CPCDMX) procede cuando: (i) el crédito está garantizado con hipoteca; (ii) la escritura está inscrita en el RPP; (iii) se ejercita acción real de pago y, en su defecto, remate del bien hipotecado.</t>
+          <t>Toda persona tiene derecho a la rectificación de su acta de nacimiento por motivo de identidad de género, sin necesidad de procedimiento judicial complejo, peritajes médicos invasivos ni intervención quirúrgica. Procede vía administrativa expedita.</t>
         </is>
       </c>
       <c r="R37" s="13" t="inlineStr">
         <is>
-          <t>Define la frontera entre vía especial y ordinaria.</t>
+          <t>Marco para rectificaciones de género en toda la República.</t>
         </is>
       </c>
       <c r="S37" s="13" t="inlineStr">
         <is>
-          <t>Si falta inscripción registral, la vía se vuelve ordinaria. El acreedor pierde tiempo y embargo precautorio. Hay que verificar siempre la inscripción antes de demandar.</t>
+          <t>CDMX y Edomex ya tienen procedimientos administrativos para ello. Para otras entidades sin marco legal, el amparo con esta jurisprudencia abre la vía.</t>
         </is>
       </c>
       <c r="T37" s="13" t="inlineStr"/>
       <c r="U37" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
         </is>
       </c>
       <c r="V37" s="13" t="inlineStr">
         <is>
-          <t>vía especial · RPP · acción real</t>
+          <t>identidad de género · trans · rectificación · acta de nacimiento</t>
         </is>
       </c>
     </row>
     <row r="38" ht="80" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-002</t>
+          <t>civ-hip-001</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
@@ -7021,7 +7127,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Cédula hipotecaria y embargo</t>
+          <t>Procedencia de la vía especial</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -7041,17 +7147,17 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — aplica CCCDMX</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>CÉDULA HIPOTECARIA. SU EXPEDICIÓN Y EFECTOS EN EL JUICIO ESPECIAL HIPOTECARIO.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO. PROCEDE CUANDO EL CRÉDITO CONSTA EN ESCRITURA PÚBLICA DEBIDAMENTE REGISTRADA Y SE EJERCITA LA ACCIÓN REAL DE PAGO.</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr"/>
@@ -7060,35 +7166,35 @@
       <c r="P38" s="11" t="inlineStr"/>
       <c r="Q38" s="11" t="inlineStr">
         <is>
-          <t>La cédula hipotecaria, expedida por el juez al admitir la demanda y debidamente inscrita en el RPP, produce los efectos del embargo sobre el bien hipotecado y constituye una medida cautelar real automática propia del juicio especial.</t>
+          <t>La vía especial hipotecaria (arts. 468-488 CPCDMX) procede cuando: (i) el crédito está garantizado con hipoteca; (ii) la escritura está inscrita en el RPP; (iii) se ejercita acción real de pago y, en su defecto, remate del bien hipotecado.</t>
         </is>
       </c>
       <c r="R38" s="11" t="inlineStr">
         <is>
-          <t>Sustituye al embargo común y bloquea enajenaciones a terceros.</t>
+          <t>Define la frontera entre vía especial y ordinaria.</t>
         </is>
       </c>
       <c r="S38" s="11" t="inlineStr">
         <is>
-          <t>Hay que solicitar expresamente la expedición y registrar de inmediato la cédula. Sin inscripción, terceros adquirentes pueden alegar buena fe registral.</t>
+          <t>Si falta inscripción registral, la vía se vuelve ordinaria. El acreedor pierde tiempo y embargo precautorio. Hay que verificar siempre la inscripción antes de demandar.</t>
         </is>
       </c>
       <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
         <is>
-          <t>cédula hipotecaria · medida cautelar · buena fe registral</t>
+          <t>vía especial · RPP · acción real</t>
         </is>
       </c>
     </row>
     <row r="39" ht="80" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>sen-002</t>
+          <t>civ-hip-002</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
@@ -7106,17 +7212,17 @@
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>Matrimonio igualitario</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Amparos en revisión 152/2013, 567/2012, 581/2012, 704/2014, 735/2014</t>
+          <t>Cédula hipotecaria y embargo</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -7136,61 +7242,49 @@
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>Matrimonio entre personas del mismo sexo — Jurisprudencia 1a./J. 43/2015</t>
+          <t>CÉDULA HIPOTECARIA. SU EXPEDICIÓN Y EFECTOS EN EL JUICIO ESPECIAL HIPOTECARIO.</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>2009407</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr"/>
-      <c r="N39" s="13" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="O39" s="13" t="inlineStr">
-        <is>
-          <t>Gaceta del SJF, Libro 19, Junio de 2015, Tomo I, página 536</t>
-        </is>
-      </c>
+      <c r="N39" s="13" t="inlineStr"/>
+      <c r="O39" s="13" t="inlineStr"/>
       <c r="P39" s="13" t="inlineStr"/>
       <c r="Q39" s="13" t="inlineStr">
         <is>
-          <t>Los códigos civiles estatales que limitan el matrimonio a hombre y mujer son inconstitucionales por violar el principio de igualdad y no discriminación. La finalidad reproductiva no es justificación constitucional admisible.</t>
+          <t>La cédula hipotecaria, expedida por el juez al admitir la demanda y debidamente inscrita en el RPP, produce los efectos del embargo sobre el bien hipotecado y constituye una medida cautelar real automática propia del juicio especial.</t>
         </is>
       </c>
       <c r="R39" s="13" t="inlineStr">
         <is>
-          <t>Una de las jurisprudencias más citadas en amparos contra códigos civiles estatales. Pavimentó el matrimonio igualitario en toda la República por vía de amparo. REGISTRO VERIFICADO directamente en el SJF.</t>
+          <t>Sustituye al embargo común y bloquea enajenaciones a terceros.</t>
         </is>
       </c>
       <c r="S39" s="13" t="inlineStr">
         <is>
-          <t>Para usuarios en estados donde la ley local aún no se reforma, el amparo con esta jurisprudencia es vía casi automática. CDMX lo reformó desde 2009 y Edomex en 2022.</t>
-        </is>
-      </c>
-      <c r="T39" s="13" t="inlineStr">
-        <is>
-          <t>1a./J. 43/2015 (10a.)</t>
-        </is>
-      </c>
+          <t>Hay que solicitar expresamente la expedición y registrar de inmediato la cédula. Sin inscripción, terceros adquirentes pueden alegar buena fe registral.</t>
+        </is>
+      </c>
+      <c r="T39" s="13" t="inlineStr"/>
       <c r="U39" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2009407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V39" s="13" t="inlineStr">
         <is>
-          <t>matrimonio igualitario · igualdad · no discriminación</t>
+          <t>cédula hipotecaria · medida cautelar · buena fe registral</t>
         </is>
       </c>
     </row>
     <row r="40" ht="80" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>sen-009</t>
+          <t>sen-002</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
@@ -7208,12 +7302,12 @@
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>Pensión alimenticia y perspectiva de género</t>
+          <t>Matrimonio igualitario</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>Amparo Directo en Revisión 1340/2015</t>
+          <t>Amparos en revisión 152/2013, 567/2012, 581/2012, 704/2014, 735/2014</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
@@ -7233,58 +7327,66 @@
       </c>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>Federal — aplica CDMX/Edomex</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Alimentos — perspectiva de género y carga procesal flexibilizada</t>
+          <t>Matrimonio entre personas del mismo sexo — Jurisprudencia 1a./J. 43/2015</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
         <is>
-          <t>ADR 1340/2015 — Primera Sala</t>
+          <t>2009407</t>
         </is>
       </c>
       <c r="M40" s="11" t="inlineStr"/>
       <c r="N40" s="11" t="inlineStr">
         <is>
-          <t>2015 y reiterada</t>
-        </is>
-      </c>
-      <c r="O40" s="11" t="inlineStr"/>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="O40" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta del SJF, Libro 19, Junio de 2015, Tomo I, página 536</t>
+        </is>
+      </c>
       <c r="P40" s="11" t="inlineStr"/>
       <c r="Q40" s="11" t="inlineStr">
         <is>
-          <t>En juicios de alimentos, el juzgador debe aplicar perspectiva de género: relajar cargas probatorias respecto del demandante alimentista, requerir información patrimonial al deudor y suplir deficiencia. La doctrina de igualdad sustantiva compensa asimetrías estructurales.</t>
+          <t>Los códigos civiles estatales que limitan el matrimonio a hombre y mujer son inconstitucionales por violar el principio de igualdad y no discriminación. La finalidad reproductiva no es justificación constitucional admisible.</t>
         </is>
       </c>
       <c r="R40" s="11" t="inlineStr">
         <is>
-          <t>Refuerza estándar pro-alimentista, especialmente para madres con hijos menores.</t>
+          <t>Una de las jurisprudencias más citadas en amparos contra códigos civiles estatales. Pavimentó el matrimonio igualitario en toda la República por vía de amparo. REGISTRO VERIFICADO directamente en el SJF.</t>
         </is>
       </c>
       <c r="S40" s="11" t="inlineStr">
         <is>
-          <t>Esencial cuando el deudor oculta ingresos. La sala obliga a auditar bienes, compulsar SAT y aplicar presunciones contra el contumaz.</t>
-        </is>
-      </c>
-      <c r="T40" s="11" t="inlineStr"/>
+          <t>Para usuarios en estados donde la ley local aún no se reforma, el amparo con esta jurisprudencia es vía casi automática. CDMX lo reformó desde 2009 y Edomex en 2022.</t>
+        </is>
+      </c>
+      <c r="T40" s="11" t="inlineStr">
+        <is>
+          <t>1a./J. 43/2015 (10a.)</t>
+        </is>
+      </c>
       <c r="U40" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032078</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2009407</t>
         </is>
       </c>
       <c r="V40" s="11" t="inlineStr">
         <is>
-          <t>alimentos · perspectiva de género · carga probatoria · menores</t>
+          <t>matrimonio igualitario · igualdad · no discriminación</t>
         </is>
       </c>
     </row>
     <row r="41" ht="80" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-001</t>
+          <t>sen-009</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
@@ -7302,17 +7404,17 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Pensión alimenticia y perspectiva de género</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Independencia respecto de normas urbanísticas</t>
+          <t>Amparo Directo en Revisión 1340/2015</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -7327,70 +7429,58 @@
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX y análogos</t>
+          <t>Federal — aplica CDMX/Edomex</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>USUCAPIÓN. PARA QUE OPERE, BASTA QUE SE SATISFAGAN LOS REQUISITOS PREVISTOS EN LA LEGISLACIÓN CIVIL, SIN QUE PUEDAN EXIGIRSE LOS CONTEMPLADOS EN LAS NORMAS DE DESARROLLO URBANO PARA FRACCIONAR PREDIOS.</t>
+          <t>Alimentos — perspectiva de género y carga procesal flexibilizada</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>2030500</t>
-        </is>
-      </c>
-      <c r="M41" s="13" t="inlineStr">
-        <is>
-          <t>Contradicción de tesis 168/2016</t>
-        </is>
-      </c>
+          <t>ADR 1340/2015 — Primera Sala</t>
+        </is>
+      </c>
+      <c r="M41" s="13" t="inlineStr"/>
       <c r="N41" s="13" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="O41" s="13" t="inlineStr">
-        <is>
-          <t>Gaceta del Semanario Judicial de la Federación</t>
-        </is>
-      </c>
-      <c r="P41" s="13" t="inlineStr">
-        <is>
-          <t>Mayoría (voto particular Ministra Olga Sánchez Cordero)</t>
-        </is>
-      </c>
+          <t>2015 y reiterada</t>
+        </is>
+      </c>
+      <c r="O41" s="13" t="inlineStr"/>
+      <c r="P41" s="13" t="inlineStr"/>
       <c r="Q41" s="13" t="inlineStr">
         <is>
-          <t>La prescripción positiva opera con el cumplimiento de los requisitos del derecho civil (posesión en concepto de propietario, pacífica, continua, pública y por el tiempo de ley); no le son aplicables las superficies mínimas, frentes ni demás limitaciones urbanísticas previstas en leyes de desarrollo urbano para fraccionar predios.</t>
+          <t>En juicios de alimentos, el juzgador debe aplicar perspectiva de género: relajar cargas probatorias respecto del demandante alimentista, requerir información patrimonial al deudor y suplir deficiencia. La doctrina de igualdad sustantiva compensa asimetrías estructurales.</t>
         </is>
       </c>
       <c r="R41" s="13" t="inlineStr">
         <is>
-          <t>Pieza decisiva para regularización de inmuebles irregulares, lotes CORETT/INSUS, predios desprendidos de superficies mayores y fraccionamientos no autorizados.</t>
+          <t>Refuerza estándar pro-alimentista, especialmente para madres con hijos menores.</t>
         </is>
       </c>
       <c r="S41" s="13" t="inlineStr">
         <is>
-          <t>En la práctica permite usucapir un lote aunque sea inferior al mínimo urbanístico municipal o no cumpla frentes mínimos. El juez no debe negar la prescripción por incumplimiento urbanístico; sólo verifica los elementos civiles. Esencial en CDMX, Edomex y zonas conurbadas con regularización pendiente.</t>
+          <t>Esencial cuando el deudor oculta ingresos. La sala obliga a auditar bienes, compulsar SAT y aplicar presunciones contra el contumaz.</t>
         </is>
       </c>
       <c r="T41" s="13" t="inlineStr"/>
       <c r="U41" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030500</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032078</t>
         </is>
       </c>
       <c r="V41" s="13" t="inlineStr">
         <is>
-          <t>regularización · lote mínimo · CORETT · INSUS · urbanístico</t>
+          <t>alimentos · perspectiva de género · carga probatoria · menores</t>
         </is>
       </c>
     </row>
     <row r="42" ht="80" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-002</t>
+          <t>civ-usu-001</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
@@ -7413,7 +7503,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Causa generadora de la posesión</t>
+          <t>Independencia respecto de normas urbanísticas</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
@@ -7423,7 +7513,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I42" s="11" t="inlineStr">
@@ -7433,62 +7523,70 @@
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta CCCDMX y análogos</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>PRESCRIPCIÓN ADQUISITIVA. PARA QUE SE ACTUALICE ES NECESARIO QUE LA PARTE ACTORA DEMUESTRE LA CAUSA GENERADORA DE SU POSESIÓN.</t>
+          <t>USUCAPIÓN. PARA QUE OPERE, BASTA QUE SE SATISFAGAN LOS REQUISITOS PREVISTOS EN LA LEGISLACIÓN CIVIL, SIN QUE PUEDAN EXIGIRSE LOS CONTEMPLADOS EN LAS NORMAS DE DESARROLLO URBANO PARA FRACCIONAR PREDIOS.</t>
         </is>
       </c>
       <c r="L42" s="11" t="inlineStr">
         <is>
-          <t>2024088 (relacionada) / 2008083</t>
-        </is>
-      </c>
-      <c r="M42" s="11" t="inlineStr"/>
-      <c r="N42" s="11" t="inlineStr"/>
+          <t>2030500</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>Contradicción de tesis 168/2016</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — 1a./J. 2/2022 (11a.), pub. 21-I-2022 — VERIFICADO</t>
-        </is>
-      </c>
-      <c r="P42" s="11" t="inlineStr"/>
+          <t>Gaceta del Semanario Judicial de la Federación</t>
+        </is>
+      </c>
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>Mayoría (voto particular Ministra Olga Sánchez Cordero)</t>
+        </is>
+      </c>
       <c r="Q42" s="11" t="inlineStr">
         <is>
-          <t>Quien pretende usucapir debe acreditar el hecho o acto jurídico por el cual entró en posesión del bien (compraventa privada, donación, cesión de derechos, etc.). Sin causa generadora demostrada, no se actualiza la posesión en concepto de propietario.</t>
+          <t>La prescripción positiva opera con el cumplimiento de los requisitos del derecho civil (posesión en concepto de propietario, pacífica, continua, pública y por el tiempo de ley); no le son aplicables las superficies mínimas, frentes ni demás limitaciones urbanísticas previstas en leyes de desarrollo urbano para fraccionar predios.</t>
         </is>
       </c>
       <c r="R42" s="11" t="inlineStr">
         <is>
-          <t>Estándar probatorio mínimo para acción de usucapión.</t>
+          <t>Pieza decisiva para regularización de inmuebles irregulares, lotes CORETT/INSUS, predios desprendidos de superficies mayores y fraccionamientos no autorizados.</t>
         </is>
       </c>
       <c r="S42" s="11" t="inlineStr">
         <is>
-          <t>En el escrito inicial DEBE narrarse con precisión la causa generadora y aportarse documental que la respalde (aunque sea contrato privado). Demandas sin causa generadora expresa fracasan en primera instancia.</t>
-        </is>
-      </c>
-      <c r="T42" s="11" t="inlineStr">
-        <is>
-          <t>1a./J. 2/2022 (11a.) y precedentes</t>
-        </is>
-      </c>
+          <t>En la práctica permite usucapir un lote aunque sea inferior al mínimo urbanístico municipal o no cumpla frentes mínimos. El juez no debe negar la prescripción por incumplimiento urbanístico; sólo verifica los elementos civiles. Esencial en CDMX, Edomex y zonas conurbadas con regularización pendiente.</t>
+        </is>
+      </c>
+      <c r="T42" s="11" t="inlineStr"/>
       <c r="U42" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024088</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030500</t>
         </is>
       </c>
       <c r="V42" s="11" t="inlineStr">
         <is>
-          <t>causa generadora · posesión · carga probatoria</t>
+          <t>regularización · lote mínimo · CORETT · INSUS · urbanístico</t>
         </is>
       </c>
     </row>
     <row r="43" ht="80" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-004</t>
+          <t>civ-usu-002</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
@@ -7511,17 +7609,17 @@
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>Suma de posesiones — herederos</t>
+          <t>Causa generadora de la posesión</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I43" s="13" t="inlineStr">
@@ -7536,49 +7634,57 @@
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>POSESIÓN. SUMA DE LA EJERCIDA POR EL CAUSANTE Y SUS HEREDEROS PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>PRESCRIPCIÓN ADQUISITIVA. PARA QUE SE ACTUALICE ES NECESARIO QUE LA PARTE ACTORA DEMUESTRE LA CAUSA GENERADORA DE SU POSESIÓN.</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>2021246</t>
+          <t>2024088 (relacionada) / 2008083</t>
         </is>
       </c>
       <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="13" t="inlineStr"/>
-      <c r="O43" s="13" t="inlineStr"/>
+      <c r="O43" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — 1a./J. 2/2022 (11a.), pub. 21-I-2022 — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P43" s="13" t="inlineStr"/>
       <c r="Q43" s="13" t="inlineStr">
         <is>
-          <t>Conforme al art. 1149 del CCCDMX, los herederos continúan la posesión del causante y pueden sumar a la suya el tiempo poseído por aquél, siempre que la posesión haya sido en concepto de propietario.</t>
+          <t>Quien pretende usucapir debe acreditar el hecho o acto jurídico por el cual entró en posesión del bien (compraventa privada, donación, cesión de derechos, etc.). Sin causa generadora demostrada, no se actualiza la posesión en concepto de propietario.</t>
         </is>
       </c>
       <c r="R43" s="13" t="inlineStr">
         <is>
-          <t>Permite acreditar usucapión consumada en vida del causante.</t>
+          <t>Estándar probatorio mínimo para acción de usucapión.</t>
         </is>
       </c>
       <c r="S43" s="13" t="inlineStr">
         <is>
-          <t>En sucesiones, cuando el padre/madre poseyó durante décadas, el heredero (o el albacea en representación de la masa) puede ejercer la acción computando ese tiempo. La sentencia se dicta a nombre del de cujus y la sucesión adjudica después.</t>
-        </is>
-      </c>
-      <c r="T43" s="13" t="inlineStr"/>
+          <t>En el escrito inicial DEBE narrarse con precisión la causa generadora y aportarse documental que la respalde (aunque sea contrato privado). Demandas sin causa generadora expresa fracasan en primera instancia.</t>
+        </is>
+      </c>
+      <c r="T43" s="13" t="inlineStr">
+        <is>
+          <t>1a./J. 2/2022 (11a.) y precedentes</t>
+        </is>
+      </c>
       <c r="U43" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021246</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024088</t>
         </is>
       </c>
       <c r="V43" s="13" t="inlineStr">
         <is>
-          <t>suma de posesiones · albacea · sucesión</t>
+          <t>causa generadora · posesión · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="44" ht="80" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>con-cuo-001</t>
+          <t>civ-usu-004</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
@@ -7591,22 +7697,22 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>Cuotas condominales — vía y ejecutividad</t>
+          <t>Suma de posesiones — herederos</t>
         </is>
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -7621,17 +7727,17 @@
       </c>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>CDMX (LPCI CDMX) — análogo Edomex</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>CUOTAS DE MANTENIMIENTO EN CONDOMINIO. SU COBRO PROCEDE POR LA VÍA EJECUTIVA CIVIL CUANDO ASÍ LO PREVÉ LA LEY LOCAL Y EXISTE CERTIFICACIÓN DEL ADMINISTRADOR.</t>
+          <t>POSESIÓN. SUMA DE LA EJERCIDA POR EL CAUSANTE Y SUS HEREDEROS PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L44" s="11" t="inlineStr">
         <is>
-          <t>Art. 56 LPCI CDMX</t>
+          <t>2021246</t>
         </is>
       </c>
       <c r="M44" s="11" t="inlineStr"/>
@@ -7640,35 +7746,35 @@
       <c r="P44" s="11" t="inlineStr"/>
       <c r="Q44" s="11" t="inlineStr">
         <is>
-          <t>Conforme a la Ley de Propiedad en Condominio CDMX (art. 56 y concordantes), las cuotas vencidas pueden cobrarse por vía ejecutiva civil cuando exista certificación del administrador, autorizada por el Comité de Vigilancia, que constituye documento que trae aparejada ejecución.</t>
+          <t>Conforme al art. 1149 del CCCDMX, los herederos continúan la posesión del causante y pueden sumar a la suya el tiempo poseído por aquél, siempre que la posesión haya sido en concepto de propietario.</t>
         </is>
       </c>
       <c r="R44" s="11" t="inlineStr">
         <is>
-          <t>Esencial para administración condominal.</t>
+          <t>Permite acreditar usucapión consumada en vida del causante.</t>
         </is>
       </c>
       <c r="S44" s="11" t="inlineStr">
         <is>
-          <t>Verificar formalidad de la certificación: firma del administrador, sello, autorización del comité, desglose mensual. Sin estos requisitos, la vía cae a ordinaria.</t>
+          <t>En sucesiones, cuando el padre/madre poseyó durante décadas, el heredero (o el albacea en representación de la masa) puede ejercer la acción computando ese tiempo. La sentencia se dicta a nombre del de cujus y la sucesión adjudica después.</t>
         </is>
       </c>
       <c r="T44" s="11" t="inlineStr"/>
       <c r="U44" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031361</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021246</t>
         </is>
       </c>
       <c r="V44" s="11" t="inlineStr">
         <is>
-          <t>cuotas condominales · LPCI CDMX · vía ejecutiva</t>
+          <t>suma de posesiones · albacea · sucesión</t>
         </is>
       </c>
     </row>
     <row r="45" ht="80" customHeight="1">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>fis-cad-001</t>
+          <t>con-cuo-001</t>
         </is>
       </c>
       <c r="B45" s="13" t="n">
@@ -7676,22 +7782,22 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>2ª Sala SCJN</t>
+          <t>1ª Sala SCJN</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>Caducidad de facultades del fisco</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Plazo y cómputo</t>
+          <t>Cuotas condominales — vía y ejecutividad</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
@@ -7711,17 +7817,17 @@
       </c>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX (LPCI CDMX) — análogo Edomex</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>CADUCIDAD DE LAS FACULTADES DE COMPROBACIÓN. EL PLAZO DEL ARTÍCULO 67 DEL CFF SE COMPUTA A PARTIR DEL DÍA SIGUIENTE A AQUÉL EN QUE DEBIÓ PRESENTARSE LA DECLARACIÓN.</t>
+          <t>CUOTAS DE MANTENIMIENTO EN CONDOMINIO. SU COBRO PROCEDE POR LA VÍA EJECUTIVA CIVIL CUANDO ASÍ LO PREVÉ LA LEY LOCAL Y EXISTE CERTIFICACIÓN DEL ADMINISTRADOR.</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>Art. 67 CFF</t>
+          <t>Art. 56 LPCI CDMX</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr"/>
@@ -7730,35 +7836,35 @@
       <c r="P45" s="13" t="inlineStr"/>
       <c r="Q45" s="13" t="inlineStr">
         <is>
-          <t>El plazo de 5 años (regla general) o 10 años (sin RFC o sin declaraciones) corre desde el día siguiente a aquel en que debió presentarse la declaración del ejercicio.</t>
+          <t>Conforme a la Ley de Propiedad en Condominio CDMX (art. 56 y concordantes), las cuotas vencidas pueden cobrarse por vía ejecutiva civil cuando exista certificación del administrador, autorizada por el Comité de Vigilancia, que constituye documento que trae aparejada ejecución.</t>
         </is>
       </c>
       <c r="R45" s="13" t="inlineStr">
         <is>
-          <t>Defensa esencial frente a revisiones tardías del SAT.</t>
+          <t>Esencial para administración condominal.</t>
         </is>
       </c>
       <c r="S45" s="13" t="inlineStr">
         <is>
-          <t>Hay que oponer la caducidad como excepción de previo y especial pronunciamiento. Cuidado con interrupciones por revisiones notificadas legalmente.</t>
+          <t>Verificar formalidad de la certificación: firma del administrador, sello, autorización del comité, desglose mensual. Sin estos requisitos, la vía cae a ordinaria.</t>
         </is>
       </c>
       <c r="T45" s="13" t="inlineStr"/>
       <c r="U45" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2023051</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031361</t>
         </is>
       </c>
       <c r="V45" s="13" t="inlineStr">
         <is>
-          <t>caducidad · art. 67 CFF · facultades de comprobación</t>
+          <t>cuotas condominales · LPCI CDMX · vía ejecutiva</t>
         </is>
       </c>
     </row>
     <row r="46" ht="80" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-001</t>
+          <t>fis-cad-001</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
@@ -7776,12 +7882,12 @@
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Caducidad de facultades del fisco</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>Operaciones inexistentes — art. 69-B CFF</t>
+          <t>Plazo y cómputo</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
@@ -7806,12 +7912,12 @@
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>OPERACIONES INEXISTENTES. EL PROCEDIMIENTO DEL ARTÍCULO 69-B DEL CFF CONSTITUYE UN ACTO DE MOLESTIA Y SU INCLUSIÓN EN LISTAS DEFINITIVAS ES ATACABLE POR AMPARO INDIRECTO.</t>
+          <t>CADUCIDAD DE LAS FACULTADES DE COMPROBACIÓN. EL PLAZO DEL ARTÍCULO 67 DEL CFF SE COMPUTA A PARTIR DEL DÍA SIGUIENTE A AQUÉL EN QUE DEBIÓ PRESENTARSE LA DECLARACIÓN.</t>
         </is>
       </c>
       <c r="L46" s="11" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>Art. 67 CFF</t>
         </is>
       </c>
       <c r="M46" s="11" t="inlineStr"/>
@@ -7820,35 +7926,35 @@
       <c r="P46" s="11" t="inlineStr"/>
       <c r="Q46" s="11" t="inlineStr">
         <is>
-          <t>El procedimiento de presunción de inexistencia de operaciones genera consecuencias graves (no deducibilidad de CFDI, listas públicas). Es acto de molestia que puede atacarse por amparo si se vulneran garantías de audiencia o fundamentación.</t>
+          <t>El plazo de 5 años (regla general) o 10 años (sin RFC o sin declaraciones) corre desde el día siguiente a aquel en que debió presentarse la declaración del ejercicio.</t>
         </is>
       </c>
       <c r="R46" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra inclusión en listas del 69-B.</t>
+          <t>Defensa esencial frente a revisiones tardías del SAT.</t>
         </is>
       </c>
       <c r="S46" s="11" t="inlineStr">
         <is>
-          <t>Plazo de 15 días para desvirtuar es estricto. Si no se atendió, queda amparo indirecto contra publicación definitiva. Para terceros que compraron a empresa listada: probar materialidad de la operación.</t>
+          <t>Hay que oponer la caducidad como excepción de previo y especial pronunciamiento. Cuidado con interrupciones por revisiones notificadas legalmente.</t>
         </is>
       </c>
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2023051</t>
         </is>
       </c>
       <c r="V46" s="11" t="inlineStr">
         <is>
-          <t>69-B CFF · CFDI · operaciones inexistentes · materialidad</t>
+          <t>caducidad · art. 67 CFF · facultades de comprobación</t>
         </is>
       </c>
     </row>
     <row r="47" ht="80" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>fis-dev-001</t>
+          <t>fis-cfd-001</t>
         </is>
       </c>
       <c r="B47" s="13" t="n">
@@ -7866,12 +7972,12 @@
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>Devolución de saldos a favor</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Negativa ficta y juicio contencioso</t>
+          <t>Operaciones inexistentes — art. 69-B CFF</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
@@ -7896,12 +8002,12 @@
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>DEVOLUCIÓN DE SALDOS A FAVOR. LA NEGATIVA FICTA POR FALTA DE RESPUESTA EN 40 DÍAS PERMITE ACUDIR AL JUICIO CONTENCIOSO ADMINISTRATIVO.</t>
+          <t>OPERACIONES INEXISTENTES. EL PROCEDIMIENTO DEL ARTÍCULO 69-B DEL CFF CONSTITUYE UN ACTO DE MOLESTIA Y SU INCLUSIÓN EN LISTAS DEFINITIVAS ES ATACABLE POR AMPARO INDIRECTO.</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
-          <t>Art. 22 CFF</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr"/>
@@ -7910,35 +8016,35 @@
       <c r="P47" s="13" t="inlineStr"/>
       <c r="Q47" s="13" t="inlineStr">
         <is>
-          <t>Si el SAT no resuelve la solicitud de devolución en el plazo del art. 22 CFF, opera negativa ficta. El contribuyente puede acudir al TFJA y solicitar también daños y perjuicios cuando proceda.</t>
+          <t>El procedimiento de presunción de inexistencia de operaciones genera consecuencias graves (no deducibilidad de CFDI, listas públicas). Es acto de molestia que puede atacarse por amparo si se vulneran garantías de audiencia o fundamentación.</t>
         </is>
       </c>
       <c r="R47" s="13" t="inlineStr">
         <is>
-          <t>Camino estándar contra demoras del SAT en devoluciones.</t>
+          <t>Defensa contra inclusión en listas del 69-B.</t>
         </is>
       </c>
       <c r="S47" s="13" t="inlineStr">
         <is>
-          <t>Conserva acuse de presentación y vence el plazo; presenta demanda de nulidad con actualización por INPC. Solicitar también recargos a favor del contribuyente.</t>
+          <t>Plazo de 15 días para desvirtuar es estricto. Si no se atendió, queda amparo indirecto contra publicación definitiva. Para terceros que compraron a empresa listada: probar materialidad de la operación.</t>
         </is>
       </c>
       <c r="T47" s="13" t="inlineStr"/>
       <c r="U47" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032008</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V47" s="13" t="inlineStr">
         <is>
-          <t>devolución · negativa ficta · art. 22 CFF</t>
+          <t>69-B CFF · CFDI · operaciones inexistentes · materialidad</t>
         </is>
       </c>
     </row>
     <row r="48" ht="80" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>lab-des-001</t>
+          <t>fis-dev-001</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
@@ -7951,17 +8057,17 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Devolución de saldos a favor</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>Carga probatoria</t>
+          <t>Negativa ficta y juicio contencioso</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -7986,12 +8092,12 @@
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>DESPIDO. LA CARGA DE PROBAR SU JUSTIFICACIÓN CORRESPONDE AL PATRÓN; LA EXISTENCIA DE LA RELACIÓN LABORAL Y EL DESPIDO MISMO, AL TRABAJADOR EN PRIMERA INSTANCIA.</t>
+          <t>DEVOLUCIÓN DE SALDOS A FAVOR. LA NEGATIVA FICTA POR FALTA DE RESPUESTA EN 40 DÍAS PERMITE ACUDIR AL JUICIO CONTENCIOSO ADMINISTRATIVO.</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>Art. 22 CFF</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr"/>
@@ -8000,35 +8106,35 @@
       <c r="P48" s="11" t="inlineStr"/>
       <c r="Q48" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido, debe acreditar la subsistencia de la relación o que el trabajador abandonó el trabajo. Si reconoce el despido, debe acreditar la causa justificada conforme al art. 47 LFT.</t>
+          <t>Si el SAT no resuelve la solicitud de devolución en el plazo del art. 22 CFF, opera negativa ficta. El contribuyente puede acudir al TFJA y solicitar también daños y perjuicios cuando proceda.</t>
         </is>
       </c>
       <c r="R48" s="11" t="inlineStr">
         <is>
-          <t>Principio probatorio nuclear en juicios laborales.</t>
+          <t>Camino estándar contra demoras del SAT en devoluciones.</t>
         </is>
       </c>
       <c r="S48" s="11" t="inlineStr">
         <is>
-          <t>Estrategia patronal: ofrecer reinstalación para evitar carga probatoria. Estrategia trabajador: presentar testigos del momento del despido y comunicaciones inmediatas.</t>
+          <t>Conserva acuse de presentación y vence el plazo; presenta demanda de nulidad con actualización por INPC. Solicitar también recargos a favor del contribuyente.</t>
         </is>
       </c>
       <c r="T48" s="11" t="inlineStr"/>
       <c r="U48" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032008</t>
         </is>
       </c>
       <c r="V48" s="11" t="inlineStr">
         <is>
-          <t>despido · carga probatoria · art. 47 LFT</t>
+          <t>devolución · negativa ficta · art. 22 CFF</t>
         </is>
       </c>
     </row>
     <row r="49" ht="80" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>lab-ref-001</t>
+          <t>lab-des-001</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
@@ -8046,12 +8152,12 @@
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>Reforma laboral 2019 — Justicia laboral</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>Competencia y vía</t>
+          <t>Carga probatoria</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -8061,7 +8167,7 @@
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
@@ -8076,12 +8182,12 @@
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>JUSTICIA LABORAL. LA REFORMA DE 2019 TRASLADA LA JURISDICCIÓN DE LAS JUNTAS DE CONCILIACIÓN Y ARBITRAJE A TRIBUNALES LABORALES DEL PODER JUDICIAL.</t>
+          <t>DESPIDO. LA CARGA DE PROBAR SU JUSTIFICACIÓN CORRESPONDE AL PATRÓN; LA EXISTENCIA DE LA RELACIÓN LABORAL Y EL DESPIDO MISMO, AL TRABAJADOR EN PRIMERA INSTANCIA.</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>Decreto DOF 1-V-2019</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr"/>
@@ -8090,35 +8196,35 @@
       <c r="P49" s="13" t="inlineStr"/>
       <c r="Q49" s="13" t="inlineStr">
         <is>
-          <t>A partir de la reforma constitucional 2017 y legal 2019, los conflictos individuales y colectivos se resuelven ante Tribunales Laborales del Poder Judicial (Federación, Estados o CDMX), con conciliación obligatoria previa en Centros de Conciliación.</t>
+          <t>Si el patrón niega el despido, debe acreditar la subsistencia de la relación o que el trabajador abandonó el trabajo. Si reconoce el despido, debe acreditar la causa justificada conforme al art. 47 LFT.</t>
         </is>
       </c>
       <c r="R49" s="13" t="inlineStr">
         <is>
-          <t>Marco competencial vigente.</t>
+          <t>Principio probatorio nuclear en juicios laborales.</t>
         </is>
       </c>
       <c r="S49" s="13" t="inlineStr">
         <is>
-          <t>Verificar fecha de conflicto y entidad para determinar si aplica régimen anterior (JCA) o nuevo (Tribunales Laborales). En CDMX, el Tribunal Laboral arrancó en 2021.</t>
+          <t>Estrategia patronal: ofrecer reinstalación para evitar carga probatoria. Estrategia trabajador: presentar testigos del momento del despido y comunicaciones inmediatas.</t>
         </is>
       </c>
       <c r="T49" s="13" t="inlineStr"/>
       <c r="U49" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031896</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V49" s="13" t="inlineStr">
         <is>
-          <t>reforma 2019 · Tribunales Laborales · conciliación previa</t>
+          <t>despido · carga probatoria · art. 47 LFT</t>
         </is>
       </c>
     </row>
     <row r="50" ht="80" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>lab-sub-001</t>
+          <t>lab-ref-001</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
@@ -8136,12 +8242,12 @@
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>Subcontratación / Outsourcing</t>
+          <t>Reforma laboral 2019 — Justicia laboral</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>Reforma 2021 — prohibición general</t>
+          <t>Competencia y vía</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
@@ -8166,12 +8272,12 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>SUBCONTRATACIÓN LABORAL. LA REFORMA DE 2021 PROHÍBE LA DE PERSONAL Y SÓLO PERMITE LA DE SERVICIOS U OBRAS ESPECIALIZADAS REGISTRADAS EN EL REPSE.</t>
+          <t>JUSTICIA LABORAL. LA REFORMA DE 2019 TRASLADA LA JURISDICCIÓN DE LAS JUNTAS DE CONCILIACIÓN Y ARBITRAJE A TRIBUNALES LABORALES DEL PODER JUDICIAL.</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>Reforma LFT 23-IV-2021</t>
+          <t>Decreto DOF 1-V-2019</t>
         </is>
       </c>
       <c r="M50" s="11" t="inlineStr"/>
@@ -8180,35 +8286,35 @@
       <c r="P50" s="11" t="inlineStr"/>
       <c r="Q50" s="11" t="inlineStr">
         <is>
-          <t>Tras la reforma de abril de 2021 a la LFT, queda prohibida la subcontratación de personal. Solo subsiste la subcontratación de servicios u obras especializadas ajenas al objeto social y actividad económica principal del contratante, registrada en el REPSE.</t>
+          <t>A partir de la reforma constitucional 2017 y legal 2019, los conflictos individuales y colectivos se resuelven ante Tribunales Laborales del Poder Judicial (Federación, Estados o CDMX), con conciliación obligatoria previa en Centros de Conciliación.</t>
         </is>
       </c>
       <c r="R50" s="11" t="inlineStr">
         <is>
-          <t>Reconfigura toda la contratación de servicios en México.</t>
+          <t>Marco competencial vigente.</t>
         </is>
       </c>
       <c r="S50" s="11" t="inlineStr">
         <is>
-          <t>Si la empresa subcontrata sin REPSE o subcontrata su actividad principal, se produce responsabilidad solidaria con multas y los trabajadores son legalmente del contratante. Verificación de REPSE es esencial en due diligence.</t>
+          <t>Verificar fecha de conflicto y entidad para determinar si aplica régimen anterior (JCA) o nuevo (Tribunales Laborales). En CDMX, el Tribunal Laboral arrancó en 2021.</t>
         </is>
       </c>
       <c r="T50" s="11" t="inlineStr"/>
       <c r="U50" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030759</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031896</t>
         </is>
       </c>
       <c r="V50" s="11" t="inlineStr">
         <is>
-          <t>outsourcing · REPSE · reforma 2021 · responsabilidad solidaria</t>
+          <t>reforma 2019 · Tribunales Laborales · conciliación previa</t>
         </is>
       </c>
     </row>
     <row r="51" ht="80" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>mer-con-001</t>
+          <t>lab-sub-001</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
@@ -8216,22 +8322,22 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>1ª Sala SCJN</t>
+          <t>2ª Sala SCJN</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Concursos mercantiles</t>
+          <t>Subcontratación / Outsourcing</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>Procedencia y supuestos</t>
+          <t>Reforma 2021 — prohibición general</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -8241,7 +8347,7 @@
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
@@ -8256,12 +8362,12 @@
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>CONCURSO MERCANTIL. SUPUESTOS DE INCUMPLIMIENTO GENERALIZADO DE OBLIGACIONES Y CARGA PROBATORIA DEL ACREEDOR DEMANDANTE.</t>
+          <t>SUBCONTRATACIÓN LABORAL. LA REFORMA DE 2021 PROHÍBE LA DE PERSONAL Y SÓLO PERMITE LA DE SERVICIOS U OBRAS ESPECIALIZADAS REGISTRADAS EN EL REPSE.</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>Ley de Concursos Mercantiles arts. 9-10</t>
+          <t>Reforma LFT 23-IV-2021</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr"/>
@@ -8270,35 +8376,35 @@
       <c r="P51" s="13" t="inlineStr"/>
       <c r="Q51" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que demande concurso debe acreditar (i) ser titular de crédito vencido no pagado por más de 30 días y (ii) que la comerciante incurrió en otros incumplimientos que representen al menos 35% de sus pasivos o que carece de activos líquidos suficientes.</t>
+          <t>Tras la reforma de abril de 2021 a la LFT, queda prohibida la subcontratación de personal. Solo subsiste la subcontratación de servicios u obras especializadas ajenas al objeto social y actividad económica principal del contratante, registrada en el REPSE.</t>
         </is>
       </c>
       <c r="R51" s="13" t="inlineStr">
         <is>
-          <t>Marco para acciones de acreedor según LCM.</t>
+          <t>Reconfigura toda la contratación de servicios en México.</t>
         </is>
       </c>
       <c r="S51" s="13" t="inlineStr">
         <is>
-          <t>Información financiera del deudor suele obtenerse vía RUG, CNBV o requerimientos fiscales. La acción de acreedor es difícil; lo común es solicitud propia del comerciante.</t>
+          <t>Si la empresa subcontrata sin REPSE o subcontrata su actividad principal, se produce responsabilidad solidaria con multas y los trabajadores son legalmente del contratante. Verificación de REPSE es esencial en due diligence.</t>
         </is>
       </c>
       <c r="T51" s="13" t="inlineStr"/>
       <c r="U51" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031788</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030759</t>
         </is>
       </c>
       <c r="V51" s="13" t="inlineStr">
         <is>
-          <t>concurso mercantil · LCM · incumplimiento generalizado</t>
+          <t>outsourcing · REPSE · reforma 2021 · responsabilidad solidaria</t>
         </is>
       </c>
     </row>
     <row r="52" ht="80" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-001</t>
+          <t>mer-con-001</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
@@ -8316,12 +8422,12 @@
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Concursos mercantiles</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Procedencia y documento base</t>
+          <t>Procedencia y supuestos</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -8346,12 +8452,12 @@
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>JUICIO EJECUTIVO MERCANTIL. PARA SU PROCEDENCIA SE REQUIERE QUE EL DOCUMENTO BASE TRAIGA APAREJADA EJECUCIÓN EN TÉRMINOS DEL ARTÍCULO 1391 DEL CÓDIGO DE COMERCIO.</t>
+          <t>CONCURSO MERCANTIL. SUPUESTOS DE INCUMPLIMIENTO GENERALIZADO DE OBLIGACIONES Y CARGA PROBATORIA DEL ACREEDOR DEMANDANTE.</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>Ley de Concursos Mercantiles arts. 9-10</t>
         </is>
       </c>
       <c r="M52" s="11" t="inlineStr"/>
@@ -8360,35 +8466,35 @@
       <c r="P52" s="11" t="inlineStr"/>
       <c r="Q52" s="11" t="inlineStr">
         <is>
-          <t>Sólo proceden por vía ejecutiva mercantil los documentos enlistados en el art. 1391 Cco: sentencias, instrumentos públicos, títulos de crédito, pólizas notariadas, convenios judiciales, decisiones arbitrales, entre otros.</t>
+          <t>El acreedor que demande concurso debe acreditar (i) ser titular de crédito vencido no pagado por más de 30 días y (ii) que la comerciante incurrió en otros incumplimientos que representen al menos 35% de sus pasivos o que carece de activos líquidos suficientes.</t>
         </is>
       </c>
       <c r="R52" s="11" t="inlineStr">
         <is>
-          <t>Filtra acciones ejecutivas improcedentes (ahorra tiempo y costas).</t>
+          <t>Marco para acciones de acreedor según LCM.</t>
         </is>
       </c>
       <c r="S52" s="11" t="inlineStr">
         <is>
-          <t>Antes de demandar en ejecutivo verifica si tu documento está en la lista del 1391. Si no, ve por vía ordinaria mercantil u oral mercantil según cuantía.</t>
+          <t>Información financiera del deudor suele obtenerse vía RUG, CNBV o requerimientos fiscales. La acción de acreedor es difícil; lo común es solicitud propia del comerciante.</t>
         </is>
       </c>
       <c r="T52" s="11" t="inlineStr"/>
       <c r="U52" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031788</t>
         </is>
       </c>
       <c r="V52" s="11" t="inlineStr">
         <is>
-          <t>ejecutivo mercantil · art. 1391 Cco · documento base</t>
+          <t>concurso mercantil · LCM · incumplimiento generalizado</t>
         </is>
       </c>
     </row>
     <row r="53" ht="80" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>mer-soc-001</t>
+          <t>mer-eje-001</t>
         </is>
       </c>
       <c r="B53" s="13" t="n">
@@ -8406,12 +8512,12 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Sociedades mercantiles</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>Levantamiento del velo corporativo</t>
+          <t>Procedencia y documento base</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -8436,12 +8542,12 @@
       </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>DESESTIMACIÓN DE LA PERSONALIDAD JURÍDICA (LEVANTAMIENTO DEL VELO CORPORATIVO). PROCEDE EXCEPCIONALMENTE ANTE ABUSO DE LA FORMA SOCIETARIA EN FRAUDE A TERCEROS.</t>
+          <t>JUICIO EJECUTIVO MERCANTIL. PARA SU PROCEDENCIA SE REQUIERE QUE EL DOCUMENTO BASE TRAIGA APAREJADA EJECUCIÓN EN TÉRMINOS DEL ARTÍCULO 1391 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>2029944</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr"/>
@@ -8450,35 +8556,35 @@
       <c r="P53" s="13" t="inlineStr"/>
       <c r="Q53" s="13" t="inlineStr">
         <is>
-          <t>El juez puede desconocer la personalidad de la sociedad cuando ésta se utiliza como instrumento para defraudar acreedores, evadir responsabilidades o eludir la ley. Procede excepcional y restrictivamente.</t>
+          <t>Sólo proceden por vía ejecutiva mercantil los documentos enlistados en el art. 1391 Cco: sentencias, instrumentos públicos, títulos de crédito, pólizas notariadas, convenios judiciales, decisiones arbitrales, entre otros.</t>
         </is>
       </c>
       <c r="R53" s="13" t="inlineStr">
         <is>
-          <t>Permite ir contra socios cuando hay simulación.</t>
+          <t>Filtra acciones ejecutivas improcedentes (ahorra tiempo y costas).</t>
         </is>
       </c>
       <c r="S53" s="13" t="inlineStr">
         <is>
-          <t>Hay que probar: confusión patrimonial entre sociedad y socios, infrapatrimonización deliberada, uso instrumental, daño a terceros. Tesis útil contra empresarios que vacían SA antes de litigios.</t>
+          <t>Antes de demandar en ejecutivo verifica si tu documento está en la lista del 1391. Si no, ve por vía ordinaria mercantil u oral mercantil según cuantía.</t>
         </is>
       </c>
       <c r="T53" s="13" t="inlineStr"/>
       <c r="U53" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029944</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V53" s="13" t="inlineStr">
         <is>
-          <t>velo corporativo · abuso societario · fraude</t>
+          <t>ejecutivo mercantil · art. 1391 Cco · documento base</t>
         </is>
       </c>
     </row>
     <row r="54" ht="80" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>mer-soc-002</t>
+          <t>mer-soc-001</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
@@ -8501,7 +8607,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Velo corporativo — supuestos y excepcionalidad</t>
+          <t>Levantamiento del velo corporativo</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -8511,7 +8617,7 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
@@ -8526,7 +8632,7 @@
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>VELO CORPORATIVO. PROCEDE LEVANTARLO COMO MEDIDA EXCEPCIONAL CUANDO SE ACREDITE QUE SE UTILIZA CON EL PROPÓSITO DE DEFRAUDAR A TERCEROS.</t>
+          <t>DESESTIMACIÓN DE LA PERSONALIDAD JURÍDICA (LEVANTAMIENTO DEL VELO CORPORATIVO). PROCEDE EXCEPCIONALMENTE ANTE ABUSO DE LA FORMA SOCIETARIA EN FRAUDE A TERCEROS.</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
@@ -8535,37 +8641,25 @@
         </is>
       </c>
       <c r="M54" s="11" t="inlineStr"/>
-      <c r="N54" s="11" t="inlineStr">
-        <is>
-          <t>14 de febrero de 2025</t>
-        </is>
-      </c>
-      <c r="O54" s="11" t="inlineStr">
-        <is>
-          <t>Gaceta SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N54" s="11" t="inlineStr"/>
+      <c r="O54" s="11" t="inlineStr"/>
       <c r="P54" s="11" t="inlineStr"/>
       <c r="Q54" s="11" t="inlineStr">
         <is>
-          <t>El levantamiento del velo corporativo es medida excepcional, procedente solo cuando se acredita el uso fraudulento de la personalidad jurídica para defraudar a terceros. La carga probatoria recae en quien lo solicita.</t>
+          <t>El juez puede desconocer la personalidad de la sociedad cuando ésta se utiliza como instrumento para defraudar acreedores, evadir responsabilidades o eludir la ley. Procede excepcional y restrictivamente.</t>
         </is>
       </c>
       <c r="R54" s="11" t="inlineStr">
         <is>
-          <t>Doctrina vigente más reciente de Primera Sala sobre velo corporativo.</t>
+          <t>Permite ir contra socios cuando hay simulación.</t>
         </is>
       </c>
       <c r="S54" s="11" t="inlineStr">
         <is>
-          <t>Para ganar levantamiento: probar (i) abuso de la forma societaria, (ii) intención fraudulenta, (iii) daño a tercero. Sin esos tres elementos, se niega.</t>
-        </is>
-      </c>
-      <c r="T54" s="11" t="inlineStr">
-        <is>
-          <t>1a. II/2025 (11a.)</t>
-        </is>
-      </c>
+          <t>Hay que probar: confusión patrimonial entre sociedad y socios, infrapatrimonización deliberada, uso instrumental, daño a terceros. Tesis útil contra empresarios que vacían SA antes de litigios.</t>
+        </is>
+      </c>
+      <c r="T54" s="11" t="inlineStr"/>
       <c r="U54" s="11" t="inlineStr">
         <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029944</t>
@@ -8573,14 +8667,14 @@
       </c>
       <c r="V54" s="11" t="inlineStr">
         <is>
-          <t>velo corporativo · 1a. II/2025 · fraude</t>
+          <t>velo corporativo · abuso societario · fraude</t>
         </is>
       </c>
     </row>
     <row r="55" ht="80" customHeight="1">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>mer-soc-003</t>
+          <t>mer-soc-002</t>
         </is>
       </c>
       <c r="B55" s="13" t="n">
@@ -8603,7 +8697,7 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>Velo corporativo en medida cautelar prejudicial</t>
+          <t>Velo corporativo — supuestos y excepcionalidad</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -8628,12 +8722,12 @@
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>VELO CORPORATIVO. POR REGLA GENERAL NO PUEDE ORDENARSE SU LEVANTAMIENTO COMO MEDIDA CAUTELAR EN UN PROCEDIMIENTO PREJUDICIAL.</t>
+          <t>VELO CORPORATIVO. PROCEDE LEVANTARLO COMO MEDIDA EXCEPCIONAL CUANDO SE ACREDITE QUE SE UTILIZA CON EL PROPÓSITO DE DEFRAUDAR A TERCEROS.</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>2029943</t>
+          <t>2029944</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr"/>
@@ -8650,39 +8744,39 @@
       <c r="P55" s="13" t="inlineStr"/>
       <c r="Q55" s="13" t="inlineStr">
         <is>
-          <t>El levantamiento del velo corporativo no procede como medida cautelar prejudicial. Requiere juicio de fondo con plena oportunidad probatoria, dado su carácter excepcional y la severidad de sus consecuencias.</t>
+          <t>El levantamiento del velo corporativo es medida excepcional, procedente solo cuando se acredita el uso fraudulento de la personalidad jurídica para defraudar a terceros. La carga probatoria recae en quien lo solicita.</t>
         </is>
       </c>
       <c r="R55" s="13" t="inlineStr">
         <is>
-          <t>Cierra la puerta a levantamientos cautelares de personalidad.</t>
+          <t>Doctrina vigente más reciente de Primera Sala sobre velo corporativo.</t>
         </is>
       </c>
       <c r="S55" s="13" t="inlineStr">
         <is>
-          <t>Acreedor no puede pedir embargo cautelar contra socios; debe esperar juicio de fondo.</t>
+          <t>Para ganar levantamiento: probar (i) abuso de la forma societaria, (ii) intención fraudulenta, (iii) daño a tercero. Sin esos tres elementos, se niega.</t>
         </is>
       </c>
       <c r="T55" s="13" t="inlineStr">
         <is>
-          <t>1a. I/2025 (11a.)</t>
+          <t>1a. II/2025 (11a.)</t>
         </is>
       </c>
       <c r="U55" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029943</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029944</t>
         </is>
       </c>
       <c r="V55" s="13" t="inlineStr">
         <is>
-          <t>velo corporativo · 1a. I/2025 · medida cautelar</t>
+          <t>velo corporativo · 1a. II/2025 · fraude</t>
         </is>
       </c>
     </row>
     <row r="56" ht="80" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>mer-tit-001</t>
+          <t>mer-soc-003</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
@@ -8700,12 +8794,12 @@
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito</t>
+          <t>Sociedades mercantiles</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr">
         <is>
-          <t>Pagaré — requisitos esenciales</t>
+          <t>Velo corporativo en medida cautelar prejudicial</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -8715,7 +8809,7 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
@@ -8730,49 +8824,61 @@
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>PAGARÉ. REQUISITOS ESENCIALES Y CONSECUENCIAS DE SU AUSENCIA CONFORME AL ARTÍCULO 170 DE LA LGTOC.</t>
+          <t>VELO CORPORATIVO. POR REGLA GENERAL NO PUEDE ORDENARSE SU LEVANTAMIENTO COMO MEDIDA CAUTELAR EN UN PROCEDIMIENTO PREJUDICIAL.</t>
         </is>
       </c>
       <c r="L56" s="11" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2029943</t>
         </is>
       </c>
       <c r="M56" s="11" t="inlineStr"/>
-      <c r="N56" s="11" t="inlineStr"/>
-      <c r="O56" s="11" t="inlineStr"/>
+      <c r="N56" s="11" t="inlineStr">
+        <is>
+          <t>14 de febrero de 2025</t>
+        </is>
+      </c>
+      <c r="O56" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P56" s="11" t="inlineStr"/>
       <c r="Q56" s="11" t="inlineStr">
         <is>
-          <t>El pagaré debe contener: mención de ser pagaré, promesa incondicional de pagar suma determinada, nombre del beneficiario, fecha y lugar de pago, fecha y lugar de suscripción y firma del suscriptor. Su ausencia priva al documento de eficacia ejecutiva, no de su valor como mero documento privado.</t>
+          <t>El levantamiento del velo corporativo no procede como medida cautelar prejudicial. Requiere juicio de fondo con plena oportunidad probatoria, dado su carácter excepcional y la severidad de sus consecuencias.</t>
         </is>
       </c>
       <c r="R56" s="11" t="inlineStr">
         <is>
-          <t>Determina si procede ejecutivo o solo ordinario.</t>
+          <t>Cierra la puerta a levantamientos cautelares de personalidad.</t>
         </is>
       </c>
       <c r="S56" s="11" t="inlineStr">
         <is>
-          <t>Si falta requisito esencial, no procede ejecutivo, pero sí acción causal por ordinario mercantil con el documento como prueba documental privada.</t>
-        </is>
-      </c>
-      <c r="T56" s="11" t="inlineStr"/>
+          <t>Acreedor no puede pedir embargo cautelar contra socios; debe esperar juicio de fondo.</t>
+        </is>
+      </c>
+      <c r="T56" s="11" t="inlineStr">
+        <is>
+          <t>1a. I/2025 (11a.)</t>
+        </is>
+      </c>
       <c r="U56" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029943</t>
         </is>
       </c>
       <c r="V56" s="11" t="inlineStr">
         <is>
-          <t>pagaré · art. 170 LGTOC · literalidad</t>
+          <t>velo corporativo · 1a. I/2025 · medida cautelar</t>
         </is>
       </c>
     </row>
     <row r="57" ht="80" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>mer-tit-002</t>
+          <t>mer-tit-001</t>
         </is>
       </c>
       <c r="B57" s="13" t="n">
@@ -8795,7 +8901,7 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>Pagaré en blanco</t>
+          <t>Pagaré — requisitos esenciales</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
@@ -8820,12 +8926,12 @@
       </c>
       <c r="K57" s="14" t="inlineStr">
         <is>
-          <t>PAGARÉ. EL DEUDOR PUEDE OPONER LA EXCEPCIÓN DE ALTERACIÓN CUANDO SE SUSCRIBIÓ EN BLANCO Y SE LLENÓ EN TÉRMINOS DISTINTOS A LOS PACTADOS.</t>
+          <t>PAGARÉ. REQUISITOS ESENCIALES Y CONSECUENCIAS DE SU AUSENCIA CONFORME AL ARTÍCULO 170 DE LA LGTOC.</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2019464</t>
         </is>
       </c>
       <c r="M57" s="13" t="inlineStr"/>
@@ -8834,35 +8940,35 @@
       <c r="P57" s="13" t="inlineStr"/>
       <c r="Q57" s="13" t="inlineStr">
         <is>
-          <t>Si el pagaré fue firmado en blanco, el suscriptor puede excepcionar que su llenado no se ajustó al pacto. La carga probatoria es alta: hay que demostrar el pacto y la alteración mediante medios externos al título.</t>
+          <t>El pagaré debe contener: mención de ser pagaré, promesa incondicional de pagar suma determinada, nombre del beneficiario, fecha y lugar de pago, fecha y lugar de suscripción y firma del suscriptor. Su ausencia priva al documento de eficacia ejecutiva, no de su valor como mero documento privado.</t>
         </is>
       </c>
       <c r="R57" s="13" t="inlineStr">
         <is>
-          <t>Defensa frecuente en pagarés con espacios alterados.</t>
+          <t>Determina si procede ejecutivo o solo ordinario.</t>
         </is>
       </c>
       <c r="S57" s="13" t="inlineStr">
         <is>
-          <t>Pericial caligráfica y testimoniales del momento de la firma son útiles. La excepción rara vez prospera por dificultad probatoria, pero es viable.</t>
+          <t>Si falta requisito esencial, no procede ejecutivo, pero sí acción causal por ordinario mercantil con el documento como prueba documental privada.</t>
         </is>
       </c>
       <c r="T57" s="13" t="inlineStr"/>
       <c r="U57" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
       <c r="V57" s="13" t="inlineStr">
         <is>
-          <t>pagaré en blanco · alteración · excepción</t>
+          <t>pagaré · art. 170 LGTOC · literalidad</t>
         </is>
       </c>
     </row>
     <row r="58" ht="80" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-001</t>
+          <t>mer-tit-002</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
@@ -8875,17 +8981,17 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Títulos de crédito</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr">
         <is>
-          <t>Estándar y consecuencias de su ruptura</t>
+          <t>Pagaré en blanco</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
@@ -8910,12 +9016,12 @@
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU INCUMPLIMIENTO AFECTA EL VALOR PROBATORIO DE LOS INDICIOS, AUNQUE NO NECESARIAMENTE CONDUCE A SU EXCLUSIÓN.</t>
+          <t>PAGARÉ. EL DEUDOR PUEDE OPONER LA EXCEPCIÓN DE ALTERACIÓN CUANDO SE SUSCRIBIÓ EN BLANCO Y SE LLENÓ EN TÉRMINOS DISTINTOS A LOS PACTADOS.</t>
         </is>
       </c>
       <c r="L58" s="11" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr"/>
@@ -8924,35 +9030,35 @@
       <c r="P58" s="11" t="inlineStr"/>
       <c r="Q58" s="11" t="inlineStr">
         <is>
-          <t>El incumplimiento de la cadena de custodia (art. 227 CNPP) no excluye automáticamente la evidencia, pero disminuye o anula su valor probatorio. Corresponde al juez ponderar la magnitud de la ruptura y si afecta la fiabilidad.</t>
+          <t>Si el pagaré fue firmado en blanco, el suscriptor puede excepcionar que su llenado no se ajustó al pacto. La carga probatoria es alta: hay que demostrar el pacto y la alteración mediante medios externos al título.</t>
         </is>
       </c>
       <c r="R58" s="11" t="inlineStr">
         <is>
-          <t>Margen para litigar valor de pruebas materiales.</t>
+          <t>Defensa frecuente en pagarés con espacios alterados.</t>
         </is>
       </c>
       <c r="S58" s="11" t="inlineStr">
         <is>
-          <t>En narcomenudeo y armas, atacar irregularidades en custodia (transporte sin sello, embalaje deficiente, omisiones en registro) reduce o anula el peso del indicio.</t>
+          <t>Pericial caligráfica y testimoniales del momento de la firma son útiles. La excepción rara vez prospera por dificultad probatoria, pero es viable.</t>
         </is>
       </c>
       <c r="T58" s="11" t="inlineStr"/>
       <c r="U58" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
         </is>
       </c>
       <c r="V58" s="11" t="inlineStr">
         <is>
-          <t>cadena de custodia · art. 227 CNPP · fiabilidad</t>
+          <t>pagaré en blanco · alteración · excepción</t>
         </is>
       </c>
     </row>
     <row r="59" ht="80" customHeight="1">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>pen-pru-001</t>
+          <t>pen-cad-001</t>
         </is>
       </c>
       <c r="B59" s="13" t="n">
@@ -8970,12 +9076,12 @@
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>Prueba ilícita</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Regla de exclusión</t>
+          <t>Estándar y consecuencias de su ruptura</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
@@ -9000,12 +9106,12 @@
       </c>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>PRUEBA ILÍCITA. LA OBTENIDA CON VIOLACIÓN A DERECHOS FUNDAMENTALES DEBE SER EXCLUIDA Y NO PUEDE FUNDAR SENTENCIA CONDENATORIA.</t>
+          <t>CADENA DE CUSTODIA. SU INCUMPLIMIENTO AFECTA EL VALOR PROBATORIO DE LOS INDICIOS, AUNQUE NO NECESARIAMENTE CONDUCE A SU EXCLUSIÓN.</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
         <is>
-          <t>2028424</t>
+          <t>2021845</t>
         </is>
       </c>
       <c r="M59" s="13" t="inlineStr"/>
@@ -9014,35 +9120,35 @@
       <c r="P59" s="13" t="inlineStr"/>
       <c r="Q59" s="13" t="inlineStr">
         <is>
-          <t>Toda prueba obtenida directa o indirectamente con violación de derechos humanos (detención ilegal, allanamiento sin orden, tortura, interceptación sin autorización judicial) debe ser excluida. Aplica también a la prueba derivada (fruto del árbol envenenado), salvo excepciones taxativas.</t>
+          <t>El incumplimiento de la cadena de custodia (art. 227 CNPP) no excluye automáticamente la evidencia, pero disminuye o anula su valor probatorio. Corresponde al juez ponderar la magnitud de la ruptura y si afecta la fiabilidad.</t>
         </is>
       </c>
       <c r="R59" s="13" t="inlineStr">
         <is>
-          <t>Defensa nuclear en casos con detenciones cuestionables.</t>
+          <t>Margen para litigar valor de pruebas materiales.</t>
         </is>
       </c>
       <c r="S59" s="13" t="inlineStr">
         <is>
-          <t>Atacar la legalidad de la detención inicial es muchas veces la mejor estrategia: si cae la detención, caen las pruebas derivadas. Audiencia de control de detención es el momento crítico.</t>
+          <t>En narcomenudeo y armas, atacar irregularidades en custodia (transporte sin sello, embalaje deficiente, omisiones en registro) reduce o anula el peso del indicio.</t>
         </is>
       </c>
       <c r="T59" s="13" t="inlineStr"/>
       <c r="U59" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028424</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
         </is>
       </c>
       <c r="V59" s="13" t="inlineStr">
         <is>
-          <t>prueba ilícita · exclusión · árbol envenenado</t>
+          <t>cadena de custodia · art. 227 CNPP · fiabilidad</t>
         </is>
       </c>
     </row>
     <row r="60" ht="80" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>pen-pru-002</t>
+          <t>pen-pru-001</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
@@ -9065,7 +9171,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>Exclusión por detención arbitraria del coimputado</t>
+          <t>Regla de exclusión</t>
         </is>
       </c>
       <c r="G60" s="11" t="inlineStr">
@@ -9075,7 +9181,7 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I60" s="11" t="inlineStr">
@@ -9090,7 +9196,7 @@
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>DERECHO A LA EXCLUSIÓN DE PRUEBA ILÍCITA. CUANDO EL QUEJOSO ALEGA QUE LA DECLARACIÓN INCRIMINATORIA DE SU COIMPUTADO FUE OBTENIDA COMO CONSECUENCIA DE QUE ÉSTE PADECIÓ UNA DETENCIÓN ARBITRARIA, PROCEDE ANALIZAR ESE ARGUMENTO EN EL JUICIO DE AMPARO.</t>
+          <t>PRUEBA ILÍCITA. LA OBTENIDA CON VIOLACIÓN A DERECHOS FUNDAMENTALES DEBE SER EXCLUIDA Y NO PUEDE FUNDAR SENTENCIA CONDENATORIA.</t>
         </is>
       </c>
       <c r="L60" s="11" t="inlineStr">
@@ -9099,30 +9205,22 @@
         </is>
       </c>
       <c r="M60" s="11" t="inlineStr"/>
-      <c r="N60" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="O60" s="11" t="inlineStr">
-        <is>
-          <t>Gaceta SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N60" s="11" t="inlineStr"/>
+      <c r="O60" s="11" t="inlineStr"/>
       <c r="P60" s="11" t="inlineStr"/>
       <c r="Q60" s="11" t="inlineStr">
         <is>
-          <t>El quejoso puede solicitar exclusión de declaración del coimputado cuando ésta deriva de detención arbitraria de aquél. El amparo debe analizar la legalidad de la detención del coimputado.</t>
+          <t>Toda prueba obtenida directa o indirectamente con violación de derechos humanos (detención ilegal, allanamiento sin orden, tortura, interceptación sin autorización judicial) debe ser excluida. Aplica también a la prueba derivada (fruto del árbol envenenado), salvo excepciones taxativas.</t>
         </is>
       </c>
       <c r="R60" s="11" t="inlineStr">
         <is>
-          <t>Línea expansiva de exclusión de prueba derivada.</t>
+          <t>Defensa nuclear en casos con detenciones cuestionables.</t>
         </is>
       </c>
       <c r="S60" s="11" t="inlineStr">
         <is>
-          <t>Fruto del árbol envenenado se extiende a declaraciones de terceros detenidos arbitrariamente.</t>
+          <t>Atacar la legalidad de la detención inicial es muchas veces la mejor estrategia: si cae la detención, caen las pruebas derivadas. Audiencia de control de detención es el momento crítico.</t>
         </is>
       </c>
       <c r="T60" s="11" t="inlineStr"/>
@@ -9133,14 +9231,14 @@
       </c>
       <c r="V60" s="11" t="inlineStr">
         <is>
-          <t>prueba ilícita · coimputado · detención arbitraria · árbol envenenado</t>
+          <t>prueba ilícita · exclusión · árbol envenenado</t>
         </is>
       </c>
     </row>
     <row r="61" ht="80" customHeight="1">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>pen-acu-001</t>
+          <t>pen-pru-002</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
@@ -9158,12 +9256,12 @@
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Sistema acusatorio</t>
+          <t>Prueba ilícita</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>Principios rectores</t>
+          <t>Exclusión por detención arbitraria del coimputado</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -9173,7 +9271,7 @@
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr">
@@ -9188,49 +9286,57 @@
       </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>SISTEMA PENAL ACUSATORIO. SUS PRINCIPIOS RECTORES SON DE OBSERVANCIA OBLIGATORIA PARA LOS OPERADORES JURÍDICOS.</t>
+          <t>DERECHO A LA EXCLUSIÓN DE PRUEBA ILÍCITA. CUANDO EL QUEJOSO ALEGA QUE LA DECLARACIÓN INCRIMINATORIA DE SU COIMPUTADO FUE OBTENIDA COMO CONSECUENCIA DE QUE ÉSTE PADECIÓ UNA DETENCIÓN ARBITRARIA, PROCEDE ANALIZAR ESE ARGUMENTO EN EL JUICIO DE AMPARO.</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
         <is>
-          <t>Art. 20 A CPEUM</t>
+          <t>2028424</t>
         </is>
       </c>
       <c r="M61" s="13" t="inlineStr"/>
-      <c r="N61" s="13" t="inlineStr"/>
-      <c r="O61" s="13" t="inlineStr"/>
+      <c r="N61" s="13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O61" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P61" s="13" t="inlineStr"/>
       <c r="Q61" s="13" t="inlineStr">
         <is>
-          <t>Publicidad, contradicción, concentración, continuidad e inmediación (art. 20 A CPEUM) rigen todo el proceso. Su violación constituye agravio de garantías procesales y puede conducir a nulidad.</t>
+          <t>El quejoso puede solicitar exclusión de declaración del coimputado cuando ésta deriva de detención arbitraria de aquél. El amparo debe analizar la legalidad de la detención del coimputado.</t>
         </is>
       </c>
       <c r="R61" s="13" t="inlineStr">
         <is>
-          <t>Eje de control de validez de actuaciones penales.</t>
+          <t>Línea expansiva de exclusión de prueba derivada.</t>
         </is>
       </c>
       <c r="S61" s="13" t="inlineStr">
         <is>
-          <t>Cuestionar audiencias en que el juez no estuvo presente continuamente, o donde se introdujo prueba sin contradicción, es estrategia recurrente del defensor.</t>
+          <t>Fruto del árbol envenenado se extiende a declaraciones de terceros detenidos arbitrariamente.</t>
         </is>
       </c>
       <c r="T61" s="13" t="inlineStr"/>
       <c r="U61" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032097</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028424</t>
         </is>
       </c>
       <c r="V61" s="13" t="inlineStr">
         <is>
-          <t>acusatorio · art. 20 CPEUM · principios</t>
+          <t>prueba ilícita · coimputado · detención arbitraria · árbol envenenado</t>
         </is>
       </c>
     </row>
     <row r="62" ht="80" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>pen-tor-001</t>
+          <t>pen-acu-001</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
@@ -9248,12 +9354,12 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>Tortura</t>
+          <t>Sistema acusatorio</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>Tortura de coimputado e investigación oficiosa</t>
+          <t>Principios rectores</t>
         </is>
       </c>
       <c r="G62" s="11" t="inlineStr">
@@ -9263,7 +9369,7 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I62" s="11" t="inlineStr">
@@ -9278,61 +9384,49 @@
       </c>
       <c r="K62" s="12" t="inlineStr">
         <is>
-          <t>TORTURA. OBLIGACIONES DE LA AUTORIDAD JUDICIAL CUANDO EL QUEJOSO ALEGA QUE SU COIMPUTADO FUE TORTURADO PARA HACER IMPUTACIONES EN SU CONTRA.</t>
+          <t>SISTEMA PENAL ACUSATORIO. SUS PRINCIPIOS RECTORES SON DE OBSERVANCIA OBLIGATORIA PARA LOS OPERADORES JURÍDICOS.</t>
         </is>
       </c>
       <c r="L62" s="11" t="inlineStr">
         <is>
-          <t>2029150</t>
+          <t>Art. 20 A CPEUM</t>
         </is>
       </c>
       <c r="M62" s="11" t="inlineStr"/>
-      <c r="N62" s="11" t="inlineStr">
-        <is>
-          <t>05 de julio de 2024</t>
-        </is>
-      </c>
-      <c r="O62" s="11" t="inlineStr">
-        <is>
-          <t>Gaceta SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N62" s="11" t="inlineStr"/>
+      <c r="O62" s="11" t="inlineStr"/>
       <c r="P62" s="11" t="inlineStr"/>
       <c r="Q62" s="11" t="inlineStr">
         <is>
-          <t>Cuando el quejoso alega que su coimputado fue torturado para incriminarlo, la autoridad judicial tiene obligación oficiosa de investigar, aunque la víctima directa de la tortura sea otra persona.</t>
+          <t>Publicidad, contradicción, concentración, continuidad e inmediación (art. 20 A CPEUM) rigen todo el proceso. Su violación constituye agravio de garantías procesales y puede conducir a nulidad.</t>
         </is>
       </c>
       <c r="R62" s="11" t="inlineStr">
         <is>
-          <t>Expande deber de investigar tortura a casos de coimputados.</t>
+          <t>Eje de control de validez de actuaciones penales.</t>
         </is>
       </c>
       <c r="S62" s="11" t="inlineStr">
         <is>
-          <t>Si tu cliente está siendo incriminado por coimputado torturado: invocar esta tesis para excluir prueba.</t>
-        </is>
-      </c>
-      <c r="T62" s="11" t="inlineStr">
-        <is>
-          <t>1a./J. 118/2024 (11a.)</t>
-        </is>
-      </c>
+          <t>Cuestionar audiencias en que el juez no estuvo presente continuamente, o donde se introdujo prueba sin contradicción, es estrategia recurrente del defensor.</t>
+        </is>
+      </c>
+      <c r="T62" s="11" t="inlineStr"/>
       <c r="U62" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029150</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032097</t>
         </is>
       </c>
       <c r="V62" s="11" t="inlineStr">
         <is>
-          <t>tortura · coimputado · 1a./J. 118/2024 · investigación oficiosa</t>
+          <t>acusatorio · art. 20 CPEUM · principios</t>
         </is>
       </c>
     </row>
     <row r="63" ht="80" customHeight="1">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>sen-003</t>
+          <t>auto-2032145</t>
         </is>
       </c>
       <c r="B63" s="13" t="n">
@@ -9340,7 +9434,7 @@
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>1ª Sala SCJN</t>
+          <t>2ª Sala SCJN</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
@@ -9350,22 +9444,22 @@
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>Uso lúdico de cannabis</t>
+          <t>Tortura</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>Amparos en revisión 237/2014 y siguientes</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I63" s="13" t="inlineStr">
@@ -9380,61 +9474,65 @@
       </c>
       <c r="K63" s="14" t="inlineStr">
         <is>
-          <t>Inconstitucionalidad de la prohibición absoluta de uso lúdico de cannabis</t>
+          <t>TORTURA Y OTROS TRATOS O PENAS CRUELES, INHUMANOS O DEGRADANTES EN EL ESTADO DE TAMAULIPAS. EL ARTÍCULO 3 DE LA LEY RELATIVA ES INCONSTITUCIONAL, AL ESTABLECER LA APLICACIÓN SUPLETORIA DE LA LEY GENERAL DE LA MATERIA.</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
         <is>
-          <t>Amparo en Revisión 237/2014</t>
+          <t>2032145</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr"/>
       <c r="N63" s="13" t="inlineStr">
         <is>
-          <t>2015 y reiteración 2018</t>
-        </is>
-      </c>
-      <c r="O63" s="13" t="inlineStr"/>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O63" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P63" s="13" t="inlineStr"/>
       <c r="Q63" s="13" t="inlineStr">
         <is>
-          <t>La prohibición absoluta del autoconsumo lúdico de cannabis viola el libre desarrollo de la personalidad (art. 1 CPEUM). El Estado no puede prohibir actos que no afectan a terceros bajo argumento paternalista.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R63" s="13" t="inlineStr">
         <is>
-          <t>Hito de libre desarrollo de la personalidad y autonomía individual.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S63" s="13" t="inlineStr">
         <is>
-          <t>Cinco sentencias en el mismo sentido configuraron declaratoria general de inconstitucionalidad en 2021. El Congreso aún no ha cumplido la orden de legislar regulando la sustancia.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T63" s="13" t="inlineStr"/>
       <c r="U63" s="13" t="inlineStr">
         <is>
-          <t>https://www.scjn.gob.mx/sites/default/files/proyectos_resolucion_scjn/documento/2018-11/AR-237-2014.pdf</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032145</t>
         </is>
       </c>
       <c r="V63" s="13" t="inlineStr">
         <is>
-          <t>cannabis · libre desarrollo personalidad · declaratoria general</t>
+          <t>Tortura · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="64" ht="80" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>pen-rep-001</t>
+          <t>pen-tor-001</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Plenos Regionales</t>
+          <t>1ª Sala SCJN</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -9444,12 +9542,12 @@
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Tortura</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Compensación directa como parte de reparación integral</t>
+          <t>Tortura de coimputado e investigación oficiosa</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
@@ -9459,7 +9557,7 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I64" s="11" t="inlineStr">
@@ -9474,89 +9572,89 @@
       </c>
       <c r="K64" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
+          <t>TORTURA. OBLIGACIONES DE LA AUTORIDAD JUDICIAL CUANDO EL QUEJOSO ALEGA QUE SU COIMPUTADO FUE TORTURADO PARA HACER IMPUTACIONES EN SU CONTRA.</t>
         </is>
       </c>
       <c r="L64" s="11" t="inlineStr">
         <is>
-          <t>2032030</t>
+          <t>2029150</t>
         </is>
       </c>
       <c r="M64" s="11" t="inlineStr"/>
       <c r="N64" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>05 de julio de 2024</t>
         </is>
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P64" s="11" t="inlineStr"/>
       <c r="Q64" s="11" t="inlineStr">
         <is>
-          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
+          <t>Cuando el quejoso alega que su coimputado fue torturado para incriminarlo, la autoridad judicial tiene obligación oficiosa de investigar, aunque la víctima directa de la tortura sea otra persona.</t>
         </is>
       </c>
       <c r="R64" s="11" t="inlineStr">
         <is>
-          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
+          <t>Expande deber de investigar tortura a casos de coimputados.</t>
         </is>
       </c>
       <c r="S64" s="11" t="inlineStr">
         <is>
-          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
+          <t>Si tu cliente está siendo incriminado por coimputado torturado: invocar esta tesis para excluir prueba.</t>
         </is>
       </c>
       <c r="T64" s="11" t="inlineStr">
         <is>
-          <t>PR.P.T.CN. J/8 P (12a.)</t>
+          <t>1a./J. 118/2024 (11a.)</t>
         </is>
       </c>
       <c r="U64" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029150</t>
         </is>
       </c>
       <c r="V64" s="11" t="inlineStr">
         <is>
-          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
+          <t>tortura · coimputado · 1a./J. 118/2024 · investigación oficiosa</t>
         </is>
       </c>
     </row>
     <row r="65" ht="80" customHeight="1">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>civ-agua-002</t>
+          <t>sen-003</t>
         </is>
       </c>
       <c r="B65" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>1ª Sala SCJN</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>Agua y servicios públicos</t>
+          <t>Uso lúdico de cannabis</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>Cobros excesivos y nulidad</t>
+          <t>Amparos en revisión 237/2014 y siguientes</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -9571,82 +9669,86 @@
       </c>
       <c r="J65" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K65" s="14" t="inlineStr">
         <is>
-          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
+          <t>Inconstitucionalidad de la prohibición absoluta de uso lúdico de cannabis</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr">
         <is>
-          <t>Criterio TJA</t>
+          <t>Amparo en Revisión 237/2014</t>
         </is>
       </c>
       <c r="M65" s="13" t="inlineStr"/>
-      <c r="N65" s="13" t="inlineStr"/>
+      <c r="N65" s="13" t="inlineStr">
+        <is>
+          <t>2015 y reiteración 2018</t>
+        </is>
+      </c>
       <c r="O65" s="13" t="inlineStr"/>
       <c r="P65" s="13" t="inlineStr"/>
       <c r="Q65" s="13" t="inlineStr">
         <is>
-          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
+          <t>La prohibición absoluta del autoconsumo lúdico de cannabis viola el libre desarrollo de la personalidad (art. 1 CPEUM). El Estado no puede prohibir actos que no afectan a terceros bajo argumento paternalista.</t>
         </is>
       </c>
       <c r="R65" s="13" t="inlineStr">
         <is>
-          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
+          <t>Hito de libre desarrollo de la personalidad y autonomía individual.</t>
         </is>
       </c>
       <c r="S65" s="13" t="inlineStr">
         <is>
-          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
+          <t>Cinco sentencias en el mismo sentido configuraron declaratoria general de inconstitucionalidad en 2021. El Congreso aún no ha cumplido la orden de legislar regulando la sustancia.</t>
         </is>
       </c>
       <c r="T65" s="13" t="inlineStr"/>
       <c r="U65" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
+          <t>https://www.scjn.gob.mx/sites/default/files/proyectos_resolucion_scjn/documento/2018-11/AR-237-2014.pdf</t>
         </is>
       </c>
       <c r="V65" s="13" t="inlineStr">
         <is>
-          <t>cobro excesivo · medidor · TJA</t>
+          <t>cannabis · libre desarrollo personalidad · declaratoria general</t>
         </is>
       </c>
     </row>
     <row r="66" ht="80" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-001</t>
+          <t>pen-rep-001</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>Plenos Regionales</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud</t>
+          <t>Reparación del daño</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Reasignación sexual — IMSS</t>
+          <t>Compensación directa como parte de reparación integral</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -9666,12 +9768,12 @@
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
+          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
-          <t>2032111</t>
+          <t>2032030</t>
         </is>
       </c>
       <c r="M66" s="11" t="inlineStr"/>
@@ -9682,41 +9784,45 @@
       </c>
       <c r="O66" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P66" s="11" t="inlineStr"/>
       <c r="Q66" s="11" t="inlineStr">
         <is>
-          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
+          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
         </is>
       </c>
       <c r="R66" s="11" t="inlineStr">
         <is>
-          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
+          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
         </is>
       </c>
       <c r="S66" s="11" t="inlineStr">
         <is>
-          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
-        </is>
-      </c>
-      <c r="T66" s="11" t="inlineStr"/>
+          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
+        </is>
+      </c>
+      <c r="T66" s="11" t="inlineStr">
+        <is>
+          <t>PR.P.T.CN. J/8 P (12a.)</t>
+        </is>
+      </c>
       <c r="U66" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
         <is>
-          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
+          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
         </is>
       </c>
     </row>
     <row r="67" ht="80" customHeight="1">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>amp-sal-002</t>
+          <t>civ-agua-002</t>
         </is>
       </c>
       <c r="B67" s="13" t="n">
@@ -9734,12 +9840,12 @@
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud</t>
+          <t>Agua y servicios públicos</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>Efectos del amparo contra negativa de cirugía</t>
+          <t>Cobros excesivos y nulidad</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
@@ -9749,7 +9855,7 @@
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I67" s="13" t="inlineStr">
@@ -9759,62 +9865,54 @@
       </c>
       <c r="J67" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
+          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
         </is>
       </c>
       <c r="L67" s="13" t="inlineStr">
         <is>
-          <t>2032110</t>
+          <t>Criterio TJA</t>
         </is>
       </c>
       <c r="M67" s="13" t="inlineStr"/>
-      <c r="N67" s="13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O67" s="13" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N67" s="13" t="inlineStr"/>
+      <c r="O67" s="13" t="inlineStr"/>
       <c r="P67" s="13" t="inlineStr"/>
       <c r="Q67" s="13" t="inlineStr">
         <is>
-          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
+          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
         </is>
       </c>
       <c r="R67" s="13" t="inlineStr">
         <is>
-          <t>Define alcance positivo del amparo en salud.</t>
+          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
         </is>
       </c>
       <c r="S67" s="13" t="inlineStr">
         <is>
-          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
+          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
         </is>
       </c>
       <c r="T67" s="13" t="inlineStr"/>
       <c r="U67" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
         </is>
       </c>
       <c r="V67" s="13" t="inlineStr">
         <is>
-          <t>amparo efectos · cirugía · salud · 12a Época</t>
+          <t>cobro excesivo · medidor · TJA</t>
         </is>
       </c>
     </row>
     <row r="68" ht="80" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-003</t>
+          <t>amp-sal-001</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
@@ -9837,7 +9935,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Autonomía IMSS limitada por DDHH</t>
+          <t>Reasignación sexual — IMSS</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
@@ -9862,12 +9960,12 @@
       </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
+          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>2032087</t>
+          <t>2032111</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr"/>
@@ -9884,35 +9982,35 @@
       <c r="P68" s="11" t="inlineStr"/>
       <c r="Q68" s="11" t="inlineStr">
         <is>
-          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
+          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
         </is>
       </c>
       <c r="R68" s="11" t="inlineStr">
         <is>
-          <t>Marco general contra negativas burocráticas del IMSS.</t>
+          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
         </is>
       </c>
       <c r="S68" s="11" t="inlineStr">
         <is>
-          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
+          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
         </is>
       </c>
       <c r="T68" s="11" t="inlineStr"/>
       <c r="U68" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
         <is>
-          <t>salud · IMSS · autonomía limitada · 12a Época</t>
+          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="69" ht="80" customHeight="1">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>amp-sal-002</t>
         </is>
       </c>
       <c r="B69" s="13" t="n">
@@ -9925,17 +10023,17 @@
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Efectos del amparo contra negativa de cirugía</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
@@ -9945,7 +10043,7 @@
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
@@ -9960,57 +10058,57 @@
       </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
         </is>
       </c>
       <c r="L69" s="13" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032110</t>
         </is>
       </c>
       <c r="M69" s="13" t="inlineStr"/>
       <c r="N69" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O69" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P69" s="13" t="inlineStr"/>
       <c r="Q69" s="13" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
         </is>
       </c>
       <c r="R69" s="13" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Define alcance positivo del amparo en salud.</t>
         </is>
       </c>
       <c r="S69" s="13" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
         </is>
       </c>
       <c r="T69" s="13" t="inlineStr"/>
       <c r="U69" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
         </is>
       </c>
       <c r="V69" s="13" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>amparo efectos · cirugía · salud · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="70" ht="80" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>amp-sal-003</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
@@ -10023,17 +10121,17 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Autonomía IMSS limitada por DDHH</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -10058,12 +10156,12 @@
       </c>
       <c r="K70" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2032087</t>
         </is>
       </c>
       <c r="M70" s="11" t="inlineStr"/>
@@ -10080,35 +10178,35 @@
       <c r="P70" s="11" t="inlineStr"/>
       <c r="Q70" s="11" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
         </is>
       </c>
       <c r="R70" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Marco general contra negativas burocráticas del IMSS.</t>
         </is>
       </c>
       <c r="S70" s="11" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
         </is>
       </c>
       <c r="T70" s="11" t="inlineStr"/>
       <c r="U70" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
         </is>
       </c>
       <c r="V70" s="11" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>salud · IMSS · autonomía limitada · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="71" ht="80" customHeight="1">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>auto-2032131</t>
         </is>
       </c>
       <c r="B71" s="13" t="n">
@@ -10121,17 +10219,17 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -10156,57 +10254,57 @@
       </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
         </is>
       </c>
       <c r="L71" s="13" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032131</t>
         </is>
       </c>
       <c r="M71" s="13" t="inlineStr"/>
       <c r="N71" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
         </is>
       </c>
       <c r="O71" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P71" s="13" t="inlineStr"/>
       <c r="Q71" s="13" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R71" s="13" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S71" s="13" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T71" s="13" t="inlineStr"/>
       <c r="U71" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
         </is>
       </c>
       <c r="V71" s="13" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="72" ht="80" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
@@ -10219,17 +10317,17 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
@@ -10239,7 +10337,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -10249,54 +10347,62 @@
       </c>
       <c r="J72" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M72" s="11" t="inlineStr"/>
-      <c r="N72" s="11" t="inlineStr"/>
-      <c r="O72" s="11" t="inlineStr"/>
+      <c r="N72" s="11" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="O72" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P72" s="11" t="inlineStr"/>
       <c r="Q72" s="11" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R72" s="11" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S72" s="11" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="73" ht="80" customHeight="1">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B73" s="13" t="n">
@@ -10309,17 +10415,17 @@
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -10344,57 +10450,57 @@
       </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L73" s="13" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M73" s="13" t="inlineStr"/>
       <c r="N73" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O73" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P73" s="13" t="inlineStr"/>
       <c r="Q73" s="13" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R73" s="13" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S73" s="13" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T73" s="13" t="inlineStr"/>
       <c r="U73" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V73" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="74" ht="80" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
@@ -10407,17 +10513,17 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
@@ -10427,7 +10533,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -10437,62 +10543,62 @@
       </c>
       <c r="J74" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M74" s="11" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P74" s="11" t="inlineStr"/>
       <c r="Q74" s="11" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R74" s="11" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S74" s="11" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="75" ht="80" customHeight="1">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B75" s="13" t="n">
@@ -10510,12 +10616,12 @@
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
@@ -10525,7 +10631,7 @@
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
@@ -10535,62 +10641,54 @@
       </c>
       <c r="J75" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L75" s="13" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M75" s="13" t="inlineStr"/>
-      <c r="N75" s="13" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O75" s="13" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N75" s="13" t="inlineStr"/>
+      <c r="O75" s="13" t="inlineStr"/>
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="13" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R75" s="13" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S75" s="13" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T75" s="13" t="inlineStr"/>
       <c r="U75" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V75" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="76" ht="80" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
@@ -10608,12 +10706,12 @@
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
@@ -10623,7 +10721,7 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -10638,57 +10736,57 @@
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P76" s="11" t="inlineStr"/>
       <c r="Q76" s="11" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S76" s="11" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="77" ht="80" customHeight="1">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B77" s="13" t="n">
@@ -10706,12 +10804,12 @@
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
@@ -10731,17 +10829,17 @@
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L77" s="13" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M77" s="13" t="inlineStr"/>
@@ -10752,41 +10850,41 @@
       </c>
       <c r="O77" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr"/>
       <c r="Q77" s="13" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R77" s="13" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S77" s="13" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T77" s="13" t="inlineStr"/>
       <c r="U77" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V77" s="13" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="78" ht="80" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
@@ -10804,12 +10902,12 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -10819,7 +10917,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -10829,62 +10927,62 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P78" s="11" t="inlineStr"/>
       <c r="Q78" s="11" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S78" s="11" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="79" ht="80" customHeight="1">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B79" s="13" t="n">
@@ -10902,12 +11000,12 @@
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -10917,7 +11015,7 @@
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr">
@@ -10927,54 +11025,62 @@
       </c>
       <c r="J79" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L79" s="13" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M79" s="13" t="inlineStr"/>
-      <c r="N79" s="13" t="inlineStr"/>
-      <c r="O79" s="13" t="inlineStr"/>
+      <c r="N79" s="13" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="O79" s="13" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P79" s="13" t="inlineStr"/>
       <c r="Q79" s="13" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R79" s="13" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S79" s="13" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T79" s="13" t="inlineStr"/>
       <c r="U79" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V79" s="13" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="80" ht="80" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
@@ -10992,12 +11098,12 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -11007,7 +11113,7 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -11017,62 +11123,62 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M80" s="11" t="inlineStr"/>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P80" s="11" t="inlineStr"/>
       <c r="Q80" s="11" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S80" s="11" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T80" s="11" t="inlineStr"/>
       <c r="U80" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V80" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="81" ht="80" customHeight="1">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B81" s="13" t="n">
@@ -11090,12 +11196,12 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
@@ -11105,7 +11211,7 @@
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I81" s="13" t="inlineStr">
@@ -11120,57 +11226,57 @@
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L81" s="13" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M81" s="13" t="inlineStr"/>
       <c r="N81" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O81" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P81" s="13" t="inlineStr"/>
       <c r="Q81" s="13" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R81" s="13" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S81" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T81" s="13" t="inlineStr"/>
       <c r="U81" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V81" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="82" ht="80" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
@@ -11188,22 +11294,22 @@
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -11213,58 +11319,62 @@
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M82" s="11" t="inlineStr"/>
       <c r="N82" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O82" s="11" t="inlineStr"/>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P82" s="11" t="inlineStr"/>
       <c r="Q82" s="11" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S82" s="11" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="83" ht="80" customHeight="1">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B83" s="13" t="n">
@@ -11282,12 +11392,12 @@
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
@@ -11297,7 +11407,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -11307,62 +11417,54 @@
       </c>
       <c r="J83" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L83" s="13" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M83" s="13" t="inlineStr"/>
-      <c r="N83" s="13" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O83" s="13" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N83" s="13" t="inlineStr"/>
+      <c r="O83" s="13" t="inlineStr"/>
       <c r="P83" s="13" t="inlineStr"/>
       <c r="Q83" s="13" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R83" s="13" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S83" s="13" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T83" s="13" t="inlineStr"/>
       <c r="U83" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V83" s="13" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="84" ht="80" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
@@ -11380,17 +11482,17 @@
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -11405,58 +11507,62 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M84" s="11" t="inlineStr"/>
-      <c r="N84" s="11" t="inlineStr"/>
+      <c r="N84" s="11" t="inlineStr">
+        <is>
+          <t>Novena Época</t>
+        </is>
+      </c>
       <c r="O84" s="11" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P84" s="11" t="inlineStr"/>
       <c r="Q84" s="11" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S84" s="11" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="85" ht="80" customHeight="1">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B85" s="13" t="n">
@@ -11474,22 +11580,22 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -11504,49 +11610,57 @@
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L85" s="13" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M85" s="13" t="inlineStr"/>
-      <c r="N85" s="13" t="inlineStr"/>
-      <c r="O85" s="13" t="inlineStr"/>
+      <c r="N85" s="13" t="inlineStr">
+        <is>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O85" s="13" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="13" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R85" s="13" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S85" s="13" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T85" s="13" t="inlineStr"/>
       <c r="U85" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V85" s="13" t="inlineStr">
         <is>
-          <t>posesión derivada · concepto de propietario · interversión</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="86" ht="80" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>con-asa-001</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
@@ -11559,22 +11673,22 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Asambleas — convocatoria y validez</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -11589,54 +11703,58 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta LPCI CDMX</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>Art. 32 LPCI CDMX</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr"/>
-      <c r="N86" s="11" t="inlineStr"/>
+      <c r="N86" s="11" t="inlineStr">
+        <is>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
       <c r="O86" s="11" t="inlineStr"/>
       <c r="P86" s="11" t="inlineStr"/>
       <c r="Q86" s="11" t="inlineStr">
         <is>
-          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>Defensa frecuente de minorías condominales.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S86" s="11" t="inlineStr">
         <is>
-          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
         <is>
-          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="87" ht="80" customHeight="1">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>amp-cui-001</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
@@ -11649,17 +11767,17 @@
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>Reconocimiento e interés legítimo</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
@@ -11684,57 +11802,57 @@
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
-          <t>2032085</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M87" s="13" t="inlineStr"/>
       <c r="N87" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O87" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P87" s="13" t="inlineStr"/>
       <c r="Q87" s="13" t="inlineStr">
         <is>
-          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R87" s="13" t="inlineStr">
         <is>
-          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S87" s="13" t="inlineStr">
         <is>
-          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T87" s="13" t="inlineStr"/>
       <c r="U87" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V87" s="13" t="inlineStr">
         <is>
-          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="88" ht="80" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>amp-cui-002</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
@@ -11747,27 +11865,27 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Interés legítimo para combatir omisiones legislativas</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -11777,62 +11895,58 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
-          <t>2032086</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M88" s="11" t="inlineStr"/>
-      <c r="N88" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="N88" s="11" t="inlineStr"/>
       <c r="O88" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
         </is>
       </c>
       <c r="P88" s="11" t="inlineStr"/>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S88" s="11" t="inlineStr">
         <is>
-          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
         <is>
-          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
+          <t>pericial · topografía · identidad del bien</t>
         </is>
       </c>
     </row>
     <row r="89" ht="80" customHeight="1">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>civ-usu-005</t>
         </is>
       </c>
       <c r="B89" s="13" t="n">
@@ -11845,27 +11959,27 @@
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Posesión derivada vs. originaria</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -11880,57 +11994,49 @@
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2030499</t>
         </is>
       </c>
       <c r="M89" s="13" t="inlineStr"/>
-      <c r="N89" s="13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O89" s="13" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N89" s="13" t="inlineStr"/>
+      <c r="O89" s="13" t="inlineStr"/>
       <c r="P89" s="13" t="inlineStr"/>
       <c r="Q89" s="13" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
         </is>
       </c>
       <c r="R89" s="13" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
         </is>
       </c>
       <c r="S89" s="13" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
         </is>
       </c>
       <c r="T89" s="13" t="inlineStr"/>
       <c r="U89" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
       <c r="V89" s="13" t="inlineStr">
         <is>
-          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
+          <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
     <row r="90" ht="80" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-002</t>
+          <t>con-asa-001</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
@@ -11943,27 +12049,27 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>69-B — recurso de revocación y buzón tributario</t>
+          <t>Asambleas — convocatoria y validez</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -11973,62 +12079,54 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta LPCI CDMX</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
+          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>2031931</t>
+          <t>Art. 32 LPCI CDMX</t>
         </is>
       </c>
       <c r="M90" s="11" t="inlineStr"/>
-      <c r="N90" s="11" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O90" s="11" t="inlineStr">
-        <is>
-          <t>Gaceta SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N90" s="11" t="inlineStr"/>
+      <c r="O90" s="11" t="inlineStr"/>
       <c r="P90" s="11" t="inlineStr"/>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
+          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
         </is>
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
+          <t>Defensa frecuente de minorías condominales.</t>
         </is>
       </c>
       <c r="S90" s="11" t="inlineStr">
         <is>
-          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
+          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
         </is>
       </c>
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
         <is>
-          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
+          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
         </is>
       </c>
     </row>
     <row r="91" ht="80" customHeight="1">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-003</t>
+          <t>amp-cui-001</t>
         </is>
       </c>
       <c r="B91" s="13" t="n">
@@ -12041,17 +12139,17 @@
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>Materialidad — fundar y motivar</t>
+          <t>Reconocimiento e interés legítimo</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
@@ -12076,57 +12174,57 @@
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L91" s="13" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>2032085</t>
         </is>
       </c>
       <c r="M91" s="13" t="inlineStr"/>
       <c r="N91" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O91" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P91" s="13" t="inlineStr"/>
       <c r="Q91" s="13" t="inlineStr">
         <is>
-          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
+          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
         </is>
       </c>
       <c r="R91" s="13" t="inlineStr">
         <is>
-          <t>Defensa fuerte para contribuyentes auditados.</t>
+          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
         </is>
       </c>
       <c r="S91" s="13" t="inlineStr">
         <is>
-          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
+          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
         </is>
       </c>
       <c r="T91" s="13" t="inlineStr"/>
       <c r="U91" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
         </is>
       </c>
       <c r="V91" s="13" t="inlineStr">
         <is>
-          <t>69-B · materialidad · fundamentación · 12a Época</t>
+          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
         </is>
       </c>
     </row>
     <row r="92" ht="80" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-004</t>
+          <t>amp-cui-002</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
@@ -12139,17 +12237,17 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Nulidad EFOS — efectos sobre proveedor</t>
+          <t>Interés legítimo para combatir omisiones legislativas</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -12174,57 +12272,57 @@
       </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
+          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
         </is>
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>2031349</t>
+          <t>2032086</t>
         </is>
       </c>
       <c r="M92" s="11" t="inlineStr"/>
       <c r="N92" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O92" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P92" s="11" t="inlineStr"/>
       <c r="Q92" s="11" t="inlineStr">
         <is>
-          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
+          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
         </is>
       </c>
       <c r="R92" s="11" t="inlineStr">
         <is>
-          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
+          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
         </is>
       </c>
       <c r="S92" s="11" t="inlineStr">
         <is>
-          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
+          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
         </is>
       </c>
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>EFOS · nulidad · deducciones · 12a Época</t>
+          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
         </is>
       </c>
     </row>
     <row r="93" ht="80" customHeight="1">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>lab-des-002</t>
+          <t>amp-gen-001</t>
         </is>
       </c>
       <c r="B93" s="13" t="n">
@@ -12237,17 +12335,17 @@
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Perspectiva de género interseccional</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>Carga patrón cuando alega rescisión justificada posterior</t>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -12257,7 +12355,7 @@
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I93" s="13" t="inlineStr">
@@ -12272,57 +12370,57 @@
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
         </is>
       </c>
       <c r="L93" s="13" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>2032067</t>
         </is>
       </c>
       <c r="M93" s="13" t="inlineStr"/>
       <c r="N93" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O93" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P93" s="13" t="inlineStr"/>
       <c r="Q93" s="13" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
         </is>
       </c>
       <c r="R93" s="13" t="inlineStr">
         <is>
-          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
         </is>
       </c>
       <c r="S93" s="13" t="inlineStr">
         <is>
-          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
         </is>
       </c>
       <c r="T93" s="13" t="inlineStr"/>
       <c r="U93" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
       <c r="V93" s="13" t="inlineStr">
         <is>
-          <t>despido · rescisión · carga probatoria patrón</t>
+          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="94" ht="80" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>lab-ren-001</t>
+          <t>fis-cfd-002</t>
         </is>
       </c>
       <c r="B94" s="11" t="n">
@@ -12335,27 +12433,27 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Hora de terminación — carga del patrón</t>
+          <t>69-B — recurso de revocación y buzón tributario</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I94" s="11" t="inlineStr">
@@ -12370,18 +12468,18 @@
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
+          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
         </is>
       </c>
       <c r="L94" s="11" t="inlineStr">
         <is>
-          <t>2028640</t>
+          <t>2031931</t>
         </is>
       </c>
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O94" s="11" t="inlineStr">
@@ -12392,35 +12490,35 @@
       <c r="P94" s="11" t="inlineStr"/>
       <c r="Q94" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
+          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
         </is>
       </c>
       <c r="R94" s="11" t="inlineStr">
         <is>
-          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
+          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
         </is>
       </c>
       <c r="S94" s="11" t="inlineStr">
         <is>
-          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
+          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
         </is>
       </c>
       <c r="T94" s="11" t="inlineStr"/>
       <c r="U94" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
         </is>
       </c>
       <c r="V94" s="11" t="inlineStr">
         <is>
-          <t>renuncia · hora despido · carga probatoria</t>
+          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
         </is>
       </c>
     </row>
     <row r="95" ht="80" customHeight="1">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>lab-ren-002</t>
+          <t>fis-cfd-003</t>
         </is>
       </c>
       <c r="B95" s="13" t="n">
@@ -12433,17 +12531,17 @@
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
+          <t>Materialidad — fundar y motivar</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -12453,7 +12551,7 @@
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I95" s="13" t="inlineStr">
@@ -12468,18 +12566,18 @@
       </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
-          <t>2027058</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M95" s="13" t="inlineStr"/>
       <c r="N95" s="13" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O95" s="13" t="inlineStr">
@@ -12490,35 +12588,35 @@
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="13" t="inlineStr">
         <is>
-          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
+          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
         </is>
       </c>
       <c r="R95" s="13" t="inlineStr">
         <is>
-          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
+          <t>Defensa fuerte para contribuyentes auditados.</t>
         </is>
       </c>
       <c r="S95" s="13" t="inlineStr">
         <is>
-          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
+          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
         </is>
       </c>
       <c r="T95" s="13" t="inlineStr"/>
       <c r="U95" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V95" s="13" t="inlineStr">
         <is>
-          <t>renuncia · jubilación · veracidad · carga reforzada</t>
+          <t>69-B · materialidad · fundamentación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="96" ht="80" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>sen-020</t>
+          <t>fis-cfd-004</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
@@ -12531,27 +12629,27 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Costas en juicio mercantil — tasación</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
+          <t>Nulidad EFOS — efectos sobre proveedor</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -12561,58 +12659,62 @@
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>Primer y Segundo Circuito</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
         </is>
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados — múltiples</t>
+          <t>2031349</t>
         </is>
       </c>
       <c r="M96" s="11" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O96" s="11" t="inlineStr"/>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="O96" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P96" s="11" t="inlineStr"/>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
+          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
         </is>
       </c>
       <c r="R96" s="11" t="inlineStr">
         <is>
-          <t>Marco práctico para pretensión y oposición a costas.</t>
+          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
         </is>
       </c>
       <c r="S96" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
+          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
         </is>
       </c>
       <c r="T96" s="11" t="inlineStr"/>
       <c r="U96" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
         </is>
       </c>
       <c r="V96" s="11" t="inlineStr">
         <is>
-          <t>costas · tasación · arancel · mercantil</t>
+          <t>EFOS · nulidad · deducciones · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="97" ht="80" customHeight="1">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>lab-des-002</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
@@ -12625,22 +12727,22 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Carga patrón cuando alega rescisión justificada posterior</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -12660,18 +12762,18 @@
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
         </is>
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M97" s="13" t="inlineStr"/>
       <c r="N97" s="13" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O97" s="13" t="inlineStr">
@@ -12682,35 +12784,35 @@
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="13" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
         </is>
       </c>
       <c r="R97" s="13" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
         </is>
       </c>
       <c r="S97" s="13" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
         </is>
       </c>
       <c r="T97" s="13" t="inlineStr"/>
       <c r="U97" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V97" s="13" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>despido · rescisión · carga probatoria patrón</t>
         </is>
       </c>
     </row>
     <row r="98" ht="80" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>lab-ren-001</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
@@ -12723,17 +12825,17 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Hora de terminación — carga del patrón</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -12743,7 +12845,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -12758,57 +12860,57 @@
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
         </is>
       </c>
       <c r="L98" s="11" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2028640</t>
         </is>
       </c>
       <c r="M98" s="11" t="inlineStr"/>
       <c r="N98" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O98" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P98" s="11" t="inlineStr"/>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
         </is>
       </c>
       <c r="R98" s="11" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
         </is>
       </c>
       <c r="S98" s="11" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
         </is>
       </c>
       <c r="T98" s="11" t="inlineStr"/>
       <c r="U98" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
         </is>
       </c>
       <c r="V98" s="11" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>renuncia · hora despido · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="99" ht="80" customHeight="1">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>lab-ren-002</t>
         </is>
       </c>
       <c r="B99" s="13" t="n">
@@ -12821,17 +12923,17 @@
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -12856,18 +12958,18 @@
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
         </is>
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2027058</t>
         </is>
       </c>
       <c r="M99" s="13" t="inlineStr"/>
       <c r="N99" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O99" s="13" t="inlineStr">
@@ -12878,35 +12980,35 @@
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
         </is>
       </c>
       <c r="R99" s="13" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
         </is>
       </c>
       <c r="S99" s="13" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
         </is>
       </c>
       <c r="T99" s="13" t="inlineStr"/>
       <c r="U99" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
         </is>
       </c>
       <c r="V99" s="13" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>renuncia · jubilación · veracidad · carga reforzada</t>
         </is>
       </c>
     </row>
     <row r="100" ht="80" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>sen-020</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
@@ -12924,17 +13026,17 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Costas en juicio mercantil — tasación</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -12949,62 +13051,58 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer y Segundo Circuito</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>Línea de Colegiados — múltiples</t>
         </is>
       </c>
       <c r="M100" s="11" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="O100" s="11" t="inlineStr">
-        <is>
-          <t>Gaceta SJF — VERIFICADO</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O100" s="11" t="inlineStr"/>
       <c r="P100" s="11" t="inlineStr"/>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
         </is>
       </c>
       <c r="R100" s="11" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Marco práctico para pretensión y oposición a costas.</t>
         </is>
       </c>
       <c r="S100" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
         </is>
       </c>
       <c r="T100" s="11" t="inlineStr"/>
       <c r="U100" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
         </is>
       </c>
       <c r="V100" s="11" t="inlineStr">
         <is>
-          <t>pagaré · pagarés seriados · lugar de pago</t>
+          <t>costas · tasación · arancel · mercantil</t>
         </is>
       </c>
     </row>
     <row r="101" ht="80" customHeight="1">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B101" s="13" t="n">
@@ -13017,17 +13115,17 @@
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -13052,18 +13150,18 @@
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M101" s="13" t="inlineStr"/>
       <c r="N101" s="13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O101" s="13" t="inlineStr">
@@ -13074,35 +13172,35 @@
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R101" s="13" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S101" s="13" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T101" s="13" t="inlineStr"/>
       <c r="U101" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V101" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="102" ht="80" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
@@ -13115,17 +13213,17 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -13135,7 +13233,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -13150,57 +13248,57 @@
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M102" s="11" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O102" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P102" s="11" t="inlineStr"/>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R102" s="11" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S102" s="11" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="103" ht="80" customHeight="1">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B103" s="13" t="n">
@@ -13213,17 +13311,17 @@
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
@@ -13233,7 +13331,7 @@
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr">
@@ -13248,57 +13346,57 @@
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L103" s="13" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M103" s="13" t="inlineStr"/>
       <c r="N103" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O103" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P103" s="13" t="inlineStr"/>
       <c r="Q103" s="13" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R103" s="13" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S103" s="13" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T103" s="13" t="inlineStr"/>
       <c r="U103" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
         </is>
       </c>
       <c r="V103" s="13" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>pagaré · acción causal · ordinario mercantil</t>
         </is>
       </c>
     </row>
     <row r="104" ht="80" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>mer-pag-003</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
@@ -13311,17 +13409,17 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Pagarés seriados — lugar de pago</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -13331,7 +13429,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -13346,55 +13444,447 @@
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2019464</t>
         </is>
       </c>
       <c r="M104" s="11" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="O104" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P104" s="11" t="inlineStr"/>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
         </is>
       </c>
       <c r="R104" s="11" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
         </is>
       </c>
       <c r="S104" s="11" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
         </is>
       </c>
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+        </is>
+      </c>
+      <c r="V104" s="11" t="inlineStr">
+        <is>
+          <t>pagaré · pagarés seriados · lugar de pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="80" customHeight="1">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>pen-cad-002</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>Cadena de custodia</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H105" s="13" t="inlineStr">
+        <is>
+          <t>Undécima Época</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J105" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K105" s="14" t="inlineStr">
+        <is>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+        </is>
+      </c>
+      <c r="L105" s="13" t="inlineStr">
+        <is>
+          <t>2027962</t>
+        </is>
+      </c>
+      <c r="M105" s="13" t="inlineStr"/>
+      <c r="N105" s="13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O105" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P105" s="13" t="inlineStr"/>
+      <c r="Q105" s="13" t="inlineStr">
+        <is>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+        </is>
+      </c>
+      <c r="R105" s="13" t="inlineStr">
+        <is>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+        </is>
+      </c>
+      <c r="S105" s="13" t="inlineStr">
+        <is>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+        </is>
+      </c>
+      <c r="T105" s="13" t="inlineStr"/>
+      <c r="U105" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+        </is>
+      </c>
+      <c r="V105" s="13" t="inlineStr">
+        <is>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="80" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>pen-cad-003</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>Cadena de custodia</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>Transgresión no torna ilícita la prueba</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H106" s="11" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+        </is>
+      </c>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>2021845</t>
+        </is>
+      </c>
+      <c r="M106" s="11" t="inlineStr"/>
+      <c r="N106" s="11" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P106" s="11" t="inlineStr"/>
+      <c r="Q106" s="11" t="inlineStr">
+        <is>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+        </is>
+      </c>
+      <c r="R106" s="11" t="inlineStr">
+        <is>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+        </is>
+      </c>
+      <c r="S106" s="11" t="inlineStr">
+        <is>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+        </is>
+      </c>
+      <c r="T106" s="11" t="inlineStr"/>
+      <c r="U106" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+        </is>
+      </c>
+      <c r="V106" s="11" t="inlineStr">
+        <is>
+          <t>cadena custodia · valor probatorio · exclusión</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="80" customHeight="1">
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t>pen-ppo-001</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="inlineStr">
+        <is>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J107" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K107" s="14" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+        </is>
+      </c>
+      <c r="L107" s="13" t="inlineStr">
+        <is>
+          <t>2032107</t>
+        </is>
+      </c>
+      <c r="M107" s="13" t="inlineStr"/>
+      <c r="N107" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O107" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P107" s="13" t="inlineStr"/>
+      <c r="Q107" s="13" t="inlineStr">
+        <is>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+        </is>
+      </c>
+      <c r="R107" s="13" t="inlineStr">
+        <is>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+        </is>
+      </c>
+      <c r="S107" s="13" t="inlineStr">
+        <is>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+        </is>
+      </c>
+      <c r="T107" s="13" t="inlineStr"/>
+      <c r="U107" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+        </is>
+      </c>
+      <c r="V107" s="13" t="inlineStr">
+        <is>
+          <t>PPO · víctima · legitimación · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="80" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>pen-ppo-002</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>Cese cuando MP no prueba prolongación</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J108" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K108" s="12" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>2032108</t>
+        </is>
+      </c>
+      <c r="M108" s="11" t="inlineStr"/>
+      <c r="N108" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P108" s="11" t="inlineStr"/>
+      <c r="Q108" s="11" t="inlineStr">
+        <is>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+        </is>
+      </c>
+      <c r="R108" s="11" t="inlineStr">
+        <is>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+        </is>
+      </c>
+      <c r="S108" s="11" t="inlineStr">
+        <is>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+        </is>
+      </c>
+      <c r="T108" s="11" t="inlineStr"/>
+      <c r="U108" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
         </is>
       </c>
-      <c r="V104" s="11" t="inlineStr">
+      <c r="V108" s="11" t="inlineStr">
         <is>
           <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V104"/>
+  <autoFilter ref="A1:V108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13405,7 +13895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13911,7 +14401,7 @@
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>civ-urb-002</t>
+          <t>auto-2032122</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
@@ -13929,12 +14419,12 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Urbanización y desarrollo urbano</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Licencia de construcción y derechos adquiridos</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -13944,7 +14434,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -13959,57 +14449,65 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>LICENCIA DE CONSTRUCCIÓN. SU NEGATIVA POR CAMBIO DE ZONIFICACIÓN POSTERIOR A LA SOLICITUD VIOLA EL DERECHO ADQUIRIDO DEL PARTICULAR.</t>
+          <t>CANCELACIÓN DE LICENCIA PARA CONDUCIR. LA PREVISTA EN LOS ARTÍCULOS 168 Y 26, FRACCIÓN XXX, DE LA LEY DE MOVILIDAD Y SEGURIDAD VIAL DEL ESTADO DE PUEBLA, ES INCONSTITUCIONAL.</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>Criterio administrativo</t>
+          <t>2032122</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="11" t="inlineStr">
         <is>
-          <t>Si el particular presentó solicitud completa de licencia bajo cierta zonificación, el cambio posterior de uso de suelo no puede aplicarse retroactivamente para negar la licencia, en respeto al principio de irretroactividad y derechos adquiridos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>Protege desarrollos inmobiliarios frente a cambios de zonificación.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
-          <t>Conserva siempre acuse sellado de recepción de solicitud. La fecha de presentación fija el régimen aplicable. Combatir negativas tardías por vía de amparo administrativo.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030153</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032122</t>
         </is>
       </c>
       <c r="V6" s="11" t="inlineStr">
         <is>
-          <t>licencia · zonificación · derechos adquiridos · irretroactividad</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>civ-agua-002</t>
+          <t>civ-urb-002</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>2ª Sala SCJN</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -14019,17 +14517,17 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Agua y servicios públicos</t>
+          <t>Urbanización y desarrollo urbano</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Cobros excesivos y nulidad</t>
+          <t>Licencia de construcción y derechos adquiridos</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -14044,17 +14542,17 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
+          <t>LICENCIA DE CONSTRUCCIÓN. SU NEGATIVA POR CAMBIO DE ZONIFICACIÓN POSTERIOR A LA SOLICITUD VIOLA EL DERECHO ADQUIRIDO DEL PARTICULAR.</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>Criterio TJA</t>
+          <t>Criterio administrativo</t>
         </is>
       </c>
       <c r="M7" s="13" t="inlineStr"/>
@@ -14063,35 +14561,35 @@
       <c r="P7" s="13" t="inlineStr"/>
       <c r="Q7" s="13" t="inlineStr">
         <is>
-          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
+          <t>Si el particular presentó solicitud completa de licencia bajo cierta zonificación, el cambio posterior de uso de suelo no puede aplicarse retroactivamente para negar la licencia, en respeto al principio de irretroactividad y derechos adquiridos.</t>
         </is>
       </c>
       <c r="R7" s="13" t="inlineStr">
         <is>
-          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
+          <t>Protege desarrollos inmobiliarios frente a cambios de zonificación.</t>
         </is>
       </c>
       <c r="S7" s="13" t="inlineStr">
         <is>
-          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
+          <t>Conserva siempre acuse sellado de recepción de solicitud. La fecha de presentación fija el régimen aplicable. Combatir negativas tardías por vía de amparo administrativo.</t>
         </is>
       </c>
       <c r="T7" s="13" t="inlineStr"/>
       <c r="U7" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030153</t>
         </is>
       </c>
       <c r="V7" s="13" t="inlineStr">
         <is>
-          <t>cobro excesivo · medidor · TJA</t>
+          <t>licencia · zonificación · derechos adquiridos · irretroactividad</t>
         </is>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-001</t>
+          <t>civ-agua-002</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
@@ -14109,12 +14607,12 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud</t>
+          <t>Agua y servicios públicos</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Reasignación sexual — IMSS</t>
+          <t>Cobros excesivos y nulidad</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -14124,7 +14622,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -14134,62 +14632,54 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
+          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>2032111</t>
+          <t>Criterio TJA</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N8" s="11" t="inlineStr"/>
+      <c r="O8" s="11" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="11" t="inlineStr">
         <is>
-          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
+          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
         </is>
       </c>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
+          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
         </is>
       </c>
       <c r="S8" s="11" t="inlineStr">
         <is>
-          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
+          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
         </is>
       </c>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
         </is>
       </c>
       <c r="V8" s="11" t="inlineStr">
         <is>
-          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
+          <t>cobro excesivo · medidor · TJA</t>
         </is>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>amp-sal-002</t>
+          <t>amp-sal-001</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
@@ -14212,7 +14702,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Efectos del amparo contra negativa de cirugía</t>
+          <t>Reasignación sexual — IMSS</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -14237,12 +14727,12 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
+          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>2032110</t>
+          <t>2032111</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr"/>
@@ -14259,35 +14749,35 @@
       <c r="P9" s="13" t="inlineStr"/>
       <c r="Q9" s="13" t="inlineStr">
         <is>
-          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
+          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
         </is>
       </c>
       <c r="R9" s="13" t="inlineStr">
         <is>
-          <t>Define alcance positivo del amparo en salud.</t>
+          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
         </is>
       </c>
       <c r="S9" s="13" t="inlineStr">
         <is>
-          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
+          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
         </is>
       </c>
       <c r="T9" s="13" t="inlineStr"/>
       <c r="U9" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
         </is>
       </c>
       <c r="V9" s="13" t="inlineStr">
         <is>
-          <t>amparo efectos · cirugía · salud · 12a Época</t>
+          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-003</t>
+          <t>amp-sal-002</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
@@ -14310,7 +14800,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Autonomía IMSS limitada por DDHH</t>
+          <t>Efectos del amparo contra negativa de cirugía</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -14335,12 +14825,12 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
+          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>2032087</t>
+          <t>2032110</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr"/>
@@ -14357,33 +14847,229 @@
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
+          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
         </is>
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>Marco general contra negativas burocráticas del IMSS.</t>
+          <t>Define alcance positivo del amparo en salud.</t>
         </is>
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
+          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>amparo efectos · cirugía · salud · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>amp-sal-003</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Derecho humano a la salud</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Autonomía IMSS limitada por DDHH</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>2032087</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr"/>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr"/>
+      <c r="Q11" s="13" t="inlineStr">
+        <is>
+          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
+        </is>
+      </c>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>Marco general contra negativas burocráticas del IMSS.</t>
+        </is>
+      </c>
+      <c r="S11" s="13" t="inlineStr">
+        <is>
+          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr"/>
+      <c r="U11" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
         </is>
       </c>
-      <c r="V10" s="11" t="inlineStr">
+      <c r="V11" s="13" t="inlineStr">
         <is>
           <t>salud · IMSS · autonomía limitada · 12a Época</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032131</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Derecho humano a la salud</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>2032131</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr"/>
+      <c r="Q12" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R12" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="inlineStr"/>
+      <c r="U12" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>Derecho humano a la salud · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V10"/>
+  <autoFilter ref="A1:V12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15109,7 +15795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17785,7 +18471,7 @@
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
@@ -17808,7 +18494,7 @@
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
@@ -17818,7 +18504,7 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -17828,54 +18514,62 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
-      <c r="N29" s="13" t="inlineStr"/>
-      <c r="O29" s="13" t="inlineStr"/>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P29" s="13" t="inlineStr"/>
       <c r="Q29" s="13" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R29" s="13" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S29" s="13" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T29" s="13" t="inlineStr"/>
       <c r="U29" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V29" s="13" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
@@ -17898,7 +18592,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -17908,7 +18602,7 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
@@ -17918,62 +18612,54 @@
       </c>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr"/>
-      <c r="N30" s="11" t="inlineStr">
-        <is>
-          <t>Novena Época</t>
-        </is>
-      </c>
-      <c r="O30" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N30" s="11" t="inlineStr"/>
+      <c r="O30" s="11" t="inlineStr"/>
       <c r="P30" s="11" t="inlineStr"/>
       <c r="Q30" s="11" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S30" s="11" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="31" ht="80" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
@@ -17996,7 +18682,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -18016,17 +18702,17 @@
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr"/>
@@ -18037,41 +18723,41 @@
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr"/>
       <c r="Q31" s="13" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R31" s="13" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S31" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T31" s="13" t="inlineStr"/>
       <c r="U31" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V31" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="32" ht="80" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
@@ -18089,22 +18775,22 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -18114,58 +18800,62 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O32" s="11" t="inlineStr"/>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P32" s="11" t="inlineStr"/>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R32" s="11" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S32" s="11" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="33" ht="80" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
@@ -18183,22 +18873,22 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -18208,62 +18898,58 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr"/>
       <c r="N33" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O33" s="13" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O33" s="13" t="inlineStr"/>
       <c r="P33" s="13" t="inlineStr"/>
       <c r="Q33" s="13" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R33" s="13" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S33" s="13" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T33" s="13" t="inlineStr"/>
       <c r="U33" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V33" s="13" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="34" ht="80" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
@@ -18281,22 +18967,22 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -18306,58 +18992,62 @@
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr"/>
-      <c r="N34" s="11" t="inlineStr"/>
+      <c r="N34" s="11" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr"/>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R34" s="11" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S34" s="11" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="35" ht="80" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
@@ -18380,7 +19070,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -18390,7 +19080,7 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
@@ -18400,52 +19090,146 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr"/>
       <c r="N35" s="13" t="inlineStr"/>
-      <c r="O35" s="13" t="inlineStr"/>
+      <c r="O35" s="13" t="inlineStr">
+        <is>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+        </is>
+      </c>
       <c r="P35" s="13" t="inlineStr"/>
       <c r="Q35" s="13" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R35" s="13" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S35" s="13" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T35" s="13" t="inlineStr"/>
       <c r="U35" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+        </is>
+      </c>
+      <c r="V35" s="13" t="inlineStr">
+        <is>
+          <t>pericial · topografía · identidad del bien</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>civ-usu-005</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Usucapión / Prescripción positiva</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Posesión derivada vs. originaria</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K36" s="12" t="inlineStr">
+        <is>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>2030499</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr"/>
+      <c r="N36" s="11" t="inlineStr"/>
+      <c r="O36" s="11" t="inlineStr"/>
+      <c r="P36" s="11" t="inlineStr"/>
+      <c r="Q36" s="11" t="inlineStr">
+        <is>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+        </is>
+      </c>
+      <c r="R36" s="11" t="inlineStr">
+        <is>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+        </is>
+      </c>
+      <c r="S36" s="11" t="inlineStr">
+        <is>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+        </is>
+      </c>
+      <c r="T36" s="11" t="inlineStr"/>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
-      <c r="V35" s="13" t="inlineStr">
+      <c r="V36" s="11" t="inlineStr">
         <is>
           <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V35"/>
+  <autoFilter ref="A1:V36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Acervo_Jurisprudencial.xlsx
+++ b/Acervo_Jurisprudencial.xlsx
@@ -20,12 +20,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penal" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Civil — Condominio'!$A$1:$V$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fiscal'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Laboral'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$13</definedName>
@@ -635,27 +635,27 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -665,11 +665,11 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3654,7 +3654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V108"/>
+  <dimension ref="A1:V111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10304,7 +10304,7 @@
     <row r="72" ht="80" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
@@ -10317,17 +10317,17 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G72" s="11" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -10352,57 +10352,57 @@
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M72" s="11" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P72" s="11" t="inlineStr"/>
       <c r="Q72" s="11" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R72" s="11" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S72" s="11" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="73" ht="80" customHeight="1">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B73" s="13" t="n">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I73" s="13" t="inlineStr">
@@ -10450,57 +10450,57 @@
       </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L73" s="13" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M73" s="13" t="inlineStr"/>
       <c r="N73" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O73" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P73" s="13" t="inlineStr"/>
       <c r="Q73" s="13" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R73" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S73" s="13" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T73" s="13" t="inlineStr"/>
       <c r="U73" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V73" s="13" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="74" ht="80" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M74" s="11" t="inlineStr"/>
@@ -10570,35 +10570,35 @@
       <c r="P74" s="11" t="inlineStr"/>
       <c r="Q74" s="11" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R74" s="11" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S74" s="11" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="75" ht="80" customHeight="1">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B75" s="13" t="n">
@@ -10611,17 +10611,17 @@
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I75" s="13" t="inlineStr">
@@ -10641,54 +10641,62 @@
       </c>
       <c r="J75" s="13" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L75" s="13" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M75" s="13" t="inlineStr"/>
-      <c r="N75" s="13" t="inlineStr"/>
-      <c r="O75" s="13" t="inlineStr"/>
+      <c r="N75" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O75" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="13" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R75" s="13" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S75" s="13" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T75" s="13" t="inlineStr"/>
       <c r="U75" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V75" s="13" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="76" ht="80" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
@@ -10711,7 +10719,7 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
@@ -10721,7 +10729,7 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -10731,62 +10739,54 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr"/>
-      <c r="N76" s="11" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O76" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N76" s="11" t="inlineStr"/>
+      <c r="O76" s="11" t="inlineStr"/>
       <c r="P76" s="11" t="inlineStr"/>
       <c r="Q76" s="11" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S76" s="11" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="77" ht="80" customHeight="1">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B77" s="13" t="n">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
@@ -10829,62 +10829,62 @@
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L77" s="13" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M77" s="13" t="inlineStr"/>
       <c r="N77" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O77" s="13" t="inlineStr">
         <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr"/>
       <c r="Q77" s="13" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R77" s="13" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S77" s="13" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T77" s="13" t="inlineStr"/>
       <c r="U77" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V77" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="78" ht="80" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -10932,57 +10932,57 @@
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P78" s="11" t="inlineStr"/>
       <c r="Q78" s="11" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S78" s="11" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="79" ht="80" customHeight="1">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B79" s="13" t="n">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr">
@@ -11025,23 +11025,23 @@
       </c>
       <c r="J79" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L79" s="13" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M79" s="13" t="inlineStr"/>
       <c r="N79" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O79" s="13" t="inlineStr">
@@ -11052,35 +11052,35 @@
       <c r="P79" s="13" t="inlineStr"/>
       <c r="Q79" s="13" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R79" s="13" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S79" s="13" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T79" s="13" t="inlineStr"/>
       <c r="U79" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V79" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="80" ht="80" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -11128,57 +11128,57 @@
       </c>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M80" s="11" t="inlineStr"/>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P80" s="11" t="inlineStr"/>
       <c r="Q80" s="11" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S80" s="11" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T80" s="11" t="inlineStr"/>
       <c r="U80" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V80" s="11" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="81" ht="80" customHeight="1">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B81" s="13" t="n">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
@@ -11226,18 +11226,18 @@
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L81" s="13" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M81" s="13" t="inlineStr"/>
       <c r="N81" s="13" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O81" s="13" t="inlineStr">
@@ -11248,35 +11248,35 @@
       <c r="P81" s="13" t="inlineStr"/>
       <c r="Q81" s="13" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R81" s="13" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S81" s="13" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T81" s="13" t="inlineStr"/>
       <c r="U81" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V81" s="13" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="82" ht="80" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>auto-2032124</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -11324,57 +11324,57 @@
       </c>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>2032124</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M82" s="11" t="inlineStr"/>
       <c r="N82" s="11" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O82" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P82" s="11" t="inlineStr"/>
       <c r="Q82" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S82" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="83" ht="80" customHeight="1">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B83" s="13" t="n">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -11417,54 +11417,62 @@
       </c>
       <c r="J83" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L83" s="13" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M83" s="13" t="inlineStr"/>
-      <c r="N83" s="13" t="inlineStr"/>
-      <c r="O83" s="13" t="inlineStr"/>
+      <c r="N83" s="13" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O83" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P83" s="13" t="inlineStr"/>
       <c r="Q83" s="13" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R83" s="13" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S83" s="13" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T83" s="13" t="inlineStr"/>
       <c r="U83" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V83" s="13" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="84" ht="80" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
@@ -11487,7 +11495,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -11497,7 +11505,7 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -11507,62 +11515,54 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M84" s="11" t="inlineStr"/>
-      <c r="N84" s="11" t="inlineStr">
-        <is>
-          <t>Novena Época</t>
-        </is>
-      </c>
-      <c r="O84" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N84" s="11" t="inlineStr"/>
+      <c r="O84" s="11" t="inlineStr"/>
       <c r="P84" s="11" t="inlineStr"/>
       <c r="Q84" s="11" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S84" s="11" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="85" ht="80" customHeight="1">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B85" s="13" t="n">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="J85" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L85" s="13" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M85" s="13" t="inlineStr"/>
@@ -11626,41 +11626,41 @@
       </c>
       <c r="O85" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="13" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R85" s="13" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S85" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T85" s="13" t="inlineStr"/>
       <c r="U85" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V85" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="86" ht="80" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
@@ -11678,22 +11678,22 @@
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I86" s="11" t="inlineStr">
@@ -11703,58 +11703,62 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr"/>
       <c r="N86" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O86" s="11" t="inlineStr"/>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O86" s="11" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P86" s="11" t="inlineStr"/>
       <c r="Q86" s="11" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S86" s="11" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="87" ht="80" customHeight="1">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
@@ -11772,22 +11776,22 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
@@ -11797,62 +11801,58 @@
       </c>
       <c r="J87" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M87" s="13" t="inlineStr"/>
       <c r="N87" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O87" s="13" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O87" s="13" t="inlineStr"/>
       <c r="P87" s="13" t="inlineStr"/>
       <c r="Q87" s="13" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R87" s="13" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S87" s="13" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T87" s="13" t="inlineStr"/>
       <c r="U87" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V87" s="13" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="88" ht="80" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
@@ -11870,22 +11870,22 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -11895,58 +11895,62 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M88" s="11" t="inlineStr"/>
-      <c r="N88" s="11" t="inlineStr"/>
+      <c r="N88" s="11" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
       <c r="O88" s="11" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P88" s="11" t="inlineStr"/>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S88" s="11" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="89" ht="80" customHeight="1">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B89" s="13" t="n">
@@ -11969,7 +11973,7 @@
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
@@ -11979,7 +11983,7 @@
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -11989,54 +11993,58 @@
       </c>
       <c r="J89" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M89" s="13" t="inlineStr"/>
       <c r="N89" s="13" t="inlineStr"/>
-      <c r="O89" s="13" t="inlineStr"/>
+      <c r="O89" s="13" t="inlineStr">
+        <is>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+        </is>
+      </c>
       <c r="P89" s="13" t="inlineStr"/>
       <c r="Q89" s="13" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R89" s="13" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S89" s="13" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T89" s="13" t="inlineStr"/>
       <c r="U89" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
         </is>
       </c>
       <c r="V89" s="13" t="inlineStr">
         <is>
-          <t>posesión derivada · concepto de propietario · interversión</t>
+          <t>pericial · topografía · identidad del bien</t>
         </is>
       </c>
     </row>
     <row r="90" ht="80" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>con-asa-001</t>
+          <t>civ-usu-005</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
@@ -12049,22 +12057,22 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Asambleas — convocatoria y validez</t>
+          <t>Posesión derivada vs. originaria</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -12079,17 +12087,17 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta LPCI CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>Art. 32 LPCI CDMX</t>
+          <t>2030499</t>
         </is>
       </c>
       <c r="M90" s="11" t="inlineStr"/>
@@ -12098,35 +12106,35 @@
       <c r="P90" s="11" t="inlineStr"/>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
         </is>
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>Defensa frecuente de minorías condominales.</t>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
         </is>
       </c>
       <c r="S90" s="11" t="inlineStr">
         <is>
-          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
         </is>
       </c>
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
         <is>
-          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
+          <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
     <row r="91" ht="80" customHeight="1">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>amp-cui-001</t>
+          <t>con-asa-001</t>
         </is>
       </c>
       <c r="B91" s="13" t="n">
@@ -12139,17 +12147,17 @@
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>Reconocimiento e interés legítimo</t>
+          <t>Asambleas — convocatoria y validez</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
@@ -12159,7 +12167,7 @@
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I91" s="13" t="inlineStr">
@@ -12169,62 +12177,54 @@
       </c>
       <c r="J91" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta LPCI CDMX</t>
         </is>
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
+          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
         </is>
       </c>
       <c r="L91" s="13" t="inlineStr">
         <is>
-          <t>2032085</t>
+          <t>Art. 32 LPCI CDMX</t>
         </is>
       </c>
       <c r="M91" s="13" t="inlineStr"/>
-      <c r="N91" s="13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O91" s="13" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N91" s="13" t="inlineStr"/>
+      <c r="O91" s="13" t="inlineStr"/>
       <c r="P91" s="13" t="inlineStr"/>
       <c r="Q91" s="13" t="inlineStr">
         <is>
-          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
+          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
         </is>
       </c>
       <c r="R91" s="13" t="inlineStr">
         <is>
-          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
+          <t>Defensa frecuente de minorías condominales.</t>
         </is>
       </c>
       <c r="S91" s="13" t="inlineStr">
         <is>
-          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
+          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
         </is>
       </c>
       <c r="T91" s="13" t="inlineStr"/>
       <c r="U91" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
         </is>
       </c>
       <c r="V91" s="13" t="inlineStr">
         <is>
-          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
+          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
         </is>
       </c>
     </row>
     <row r="92" ht="80" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>amp-cui-002</t>
+          <t>amp-cui-001</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Interés legítimo para combatir omisiones legislativas</t>
+          <t>Reconocimiento e interés legítimo</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
+          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>2032086</t>
+          <t>2032085</t>
         </is>
       </c>
       <c r="M92" s="11" t="inlineStr"/>
@@ -12294,35 +12294,35 @@
       <c r="P92" s="11" t="inlineStr"/>
       <c r="Q92" s="11" t="inlineStr">
         <is>
-          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
+          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
         </is>
       </c>
       <c r="R92" s="11" t="inlineStr">
         <is>
-          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
+          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
         </is>
       </c>
       <c r="S92" s="11" t="inlineStr">
         <is>
-          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
+          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
         </is>
       </c>
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
+          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
         </is>
       </c>
     </row>
     <row r="93" ht="80" customHeight="1">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>amp-cui-002</t>
         </is>
       </c>
       <c r="B93" s="13" t="n">
@@ -12340,12 +12340,12 @@
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Interés legítimo para combatir omisiones legislativas</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
         </is>
       </c>
       <c r="L93" s="13" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032086</t>
         </is>
       </c>
       <c r="M93" s="13" t="inlineStr"/>
@@ -12392,35 +12392,35 @@
       <c r="P93" s="13" t="inlineStr"/>
       <c r="Q93" s="13" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
         </is>
       </c>
       <c r="R93" s="13" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
         </is>
       </c>
       <c r="S93" s="13" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
         </is>
       </c>
       <c r="T93" s="13" t="inlineStr"/>
       <c r="U93" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
         </is>
       </c>
       <c r="V93" s="13" t="inlineStr">
         <is>
-          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
+          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
         </is>
       </c>
     </row>
     <row r="94" ht="80" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-002</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B94" s="11" t="n">
@@ -12433,22 +12433,22 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>69-B — recurso de revocación y buzón tributario</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -12468,57 +12468,57 @@
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L94" s="11" t="inlineStr">
         <is>
-          <t>2031931</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O94" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P94" s="11" t="inlineStr"/>
       <c r="Q94" s="11" t="inlineStr">
         <is>
-          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R94" s="11" t="inlineStr">
         <is>
-          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S94" s="11" t="inlineStr">
         <is>
-          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T94" s="11" t="inlineStr"/>
       <c r="U94" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V94" s="11" t="inlineStr">
         <is>
-          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="95" ht="80" customHeight="1">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-003</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B95" s="13" t="n">
@@ -12531,17 +12531,17 @@
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>Materialidad — fundar y motivar</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -12566,57 +12566,57 @@
       </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M95" s="13" t="inlineStr"/>
       <c r="N95" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O95" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="13" t="inlineStr">
         <is>
-          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R95" s="13" t="inlineStr">
         <is>
-          <t>Defensa fuerte para contribuyentes auditados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S95" s="13" t="inlineStr">
         <is>
-          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T95" s="13" t="inlineStr"/>
       <c r="U95" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
         </is>
       </c>
       <c r="V95" s="13" t="inlineStr">
         <is>
-          <t>69-B · materialidad · fundamentación · 12a Época</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="96" ht="80" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-004</t>
+          <t>amp-gen-001</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género interseccional</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Nulidad EFOS — efectos sobre proveedor</t>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
@@ -12664,57 +12664,57 @@
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
         </is>
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>2031349</t>
+          <t>2032067</t>
         </is>
       </c>
       <c r="M96" s="11" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O96" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P96" s="11" t="inlineStr"/>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
         </is>
       </c>
       <c r="R96" s="11" t="inlineStr">
         <is>
-          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
         </is>
       </c>
       <c r="S96" s="11" t="inlineStr">
         <is>
-          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
         </is>
       </c>
       <c r="T96" s="11" t="inlineStr"/>
       <c r="U96" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
       <c r="V96" s="11" t="inlineStr">
         <is>
-          <t>EFOS · nulidad · deducciones · 12a Época</t>
+          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="97" ht="80" customHeight="1">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>lab-des-002</t>
+          <t>fis-cfd-002</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
@@ -12727,27 +12727,27 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>Carga patrón cuando alega rescisión justificada posterior</t>
+          <t>69-B — recurso de revocación y buzón tributario</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
@@ -12762,18 +12762,18 @@
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
+          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
         </is>
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>2031931</t>
         </is>
       </c>
       <c r="M97" s="13" t="inlineStr"/>
       <c r="N97" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O97" s="13" t="inlineStr">
@@ -12784,35 +12784,35 @@
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="13" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
+          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
         </is>
       </c>
       <c r="R97" s="13" t="inlineStr">
         <is>
-          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
+          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
         </is>
       </c>
       <c r="S97" s="13" t="inlineStr">
         <is>
-          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
+          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
         </is>
       </c>
       <c r="T97" s="13" t="inlineStr"/>
       <c r="U97" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
         </is>
       </c>
       <c r="V97" s="13" t="inlineStr">
         <is>
-          <t>despido · rescisión · carga probatoria patrón</t>
+          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
         </is>
       </c>
     </row>
     <row r="98" ht="80" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>lab-ren-001</t>
+          <t>fis-cfd-003</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
@@ -12825,17 +12825,17 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Hora de terminación — carga del patrón</t>
+          <t>Materialidad — fundar y motivar</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -12860,18 +12860,18 @@
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L98" s="11" t="inlineStr">
         <is>
-          <t>2028640</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M98" s="11" t="inlineStr"/>
       <c r="N98" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O98" s="11" t="inlineStr">
@@ -12882,35 +12882,35 @@
       <c r="P98" s="11" t="inlineStr"/>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
+          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
         </is>
       </c>
       <c r="R98" s="11" t="inlineStr">
         <is>
-          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
+          <t>Defensa fuerte para contribuyentes auditados.</t>
         </is>
       </c>
       <c r="S98" s="11" t="inlineStr">
         <is>
-          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
+          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
         </is>
       </c>
       <c r="T98" s="11" t="inlineStr"/>
       <c r="U98" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V98" s="11" t="inlineStr">
         <is>
-          <t>renuncia · hora despido · carga probatoria</t>
+          <t>69-B · materialidad · fundamentación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="99" ht="80" customHeight="1">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>lab-ren-002</t>
+          <t>fis-cfd-004</t>
         </is>
       </c>
       <c r="B99" s="13" t="n">
@@ -12923,17 +12923,17 @@
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
+          <t>Nulidad EFOS — efectos sobre proveedor</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I99" s="13" t="inlineStr">
@@ -12958,18 +12958,18 @@
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
         </is>
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>2027058</t>
+          <t>2031349</t>
         </is>
       </c>
       <c r="M99" s="13" t="inlineStr"/>
       <c r="N99" s="13" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O99" s="13" t="inlineStr">
@@ -12980,35 +12980,35 @@
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr">
         <is>
-          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
+          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
         </is>
       </c>
       <c r="R99" s="13" t="inlineStr">
         <is>
-          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
+          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
         </is>
       </c>
       <c r="S99" s="13" t="inlineStr">
         <is>
-          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
+          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
         </is>
       </c>
       <c r="T99" s="13" t="inlineStr"/>
       <c r="U99" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
         </is>
       </c>
       <c r="V99" s="13" t="inlineStr">
         <is>
-          <t>renuncia · jubilación · veracidad · carga reforzada</t>
+          <t>EFOS · nulidad · deducciones · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="100" ht="80" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>sen-020</t>
+          <t>lab-des-002</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
@@ -13021,27 +13021,27 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Costas en juicio mercantil — tasación</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
+          <t>Carga patrón cuando alega rescisión justificada posterior</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -13051,58 +13051,62 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>Primer y Segundo Circuito</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
+          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados — múltiples</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M100" s="11" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O100" s="11" t="inlineStr"/>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="O100" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P100" s="11" t="inlineStr"/>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
+          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
         </is>
       </c>
       <c r="R100" s="11" t="inlineStr">
         <is>
-          <t>Marco práctico para pretensión y oposición a costas.</t>
+          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
         </is>
       </c>
       <c r="S100" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
+          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
         </is>
       </c>
       <c r="T100" s="11" t="inlineStr"/>
       <c r="U100" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V100" s="11" t="inlineStr">
         <is>
-          <t>costas · tasación · arancel · mercantil</t>
+          <t>despido · rescisión · carga probatoria patrón</t>
         </is>
       </c>
     </row>
     <row r="101" ht="80" customHeight="1">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>lab-ren-001</t>
         </is>
       </c>
       <c r="B101" s="13" t="n">
@@ -13115,22 +13119,22 @@
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Hora de terminación — carga del patrón</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -13150,18 +13154,18 @@
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
         </is>
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2028640</t>
         </is>
       </c>
       <c r="M101" s="13" t="inlineStr"/>
       <c r="N101" s="13" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O101" s="13" t="inlineStr">
@@ -13172,35 +13176,35 @@
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
         </is>
       </c>
       <c r="R101" s="13" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
         </is>
       </c>
       <c r="S101" s="13" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
         </is>
       </c>
       <c r="T101" s="13" t="inlineStr"/>
       <c r="U101" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
         </is>
       </c>
       <c r="V101" s="13" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>renuncia · hora despido · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="102" ht="80" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>lab-ren-002</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
@@ -13213,17 +13217,17 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -13233,7 +13237,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -13248,57 +13252,57 @@
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2027058</t>
         </is>
       </c>
       <c r="M102" s="11" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O102" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P102" s="11" t="inlineStr"/>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
         </is>
       </c>
       <c r="R102" s="11" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
         </is>
       </c>
       <c r="S102" s="11" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
         </is>
       </c>
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>renuncia · jubilación · veracidad · carga reforzada</t>
         </is>
       </c>
     </row>
     <row r="103" ht="80" customHeight="1">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>sen-020</t>
         </is>
       </c>
       <c r="B103" s="13" t="n">
@@ -13316,22 +13320,22 @@
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Costas en juicio mercantil — tasación</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr">
@@ -13341,62 +13345,58 @@
       </c>
       <c r="J103" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer y Segundo Circuito</t>
         </is>
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
         </is>
       </c>
       <c r="L103" s="13" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>Línea de Colegiados — múltiples</t>
         </is>
       </c>
       <c r="M103" s="13" t="inlineStr"/>
       <c r="N103" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="O103" s="13" t="inlineStr">
-        <is>
-          <t>Gaceta SJF — VERIFICADO</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O103" s="13" t="inlineStr"/>
       <c r="P103" s="13" t="inlineStr"/>
       <c r="Q103" s="13" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
         </is>
       </c>
       <c r="R103" s="13" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Marco práctico para pretensión y oposición a costas.</t>
         </is>
       </c>
       <c r="S103" s="13" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
         </is>
       </c>
       <c r="T103" s="13" t="inlineStr"/>
       <c r="U103" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
         </is>
       </c>
       <c r="V103" s="13" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>costas · tasación · arancel · mercantil</t>
         </is>
       </c>
     </row>
     <row r="104" ht="80" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
@@ -13414,22 +13414,22 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -13444,18 +13444,18 @@
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M104" s="11" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O104" s="11" t="inlineStr">
@@ -13466,35 +13466,35 @@
       <c r="P104" s="11" t="inlineStr"/>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R104" s="11" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S104" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V104" s="11" t="inlineStr">
         <is>
-          <t>pagaré · pagarés seriados · lugar de pago</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="105" ht="80" customHeight="1">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B105" s="13" t="n">
@@ -13507,27 +13507,27 @@
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I105" s="13" t="inlineStr">
@@ -13542,57 +13542,57 @@
       </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M105" s="13" t="inlineStr"/>
       <c r="N105" s="13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O105" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P105" s="13" t="inlineStr"/>
       <c r="Q105" s="13" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R105" s="13" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S105" s="13" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T105" s="13" t="inlineStr"/>
       <c r="U105" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V105" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="106" ht="80" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
@@ -13605,17 +13605,17 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -13640,18 +13640,18 @@
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M106" s="11" t="inlineStr"/>
       <c r="N106" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O106" s="11" t="inlineStr">
@@ -13662,35 +13662,35 @@
       <c r="P106" s="11" t="inlineStr"/>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R106" s="11" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S106" s="11" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>pagaré · acción causal · ordinario mercantil</t>
         </is>
       </c>
     </row>
     <row r="107" ht="80" customHeight="1">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>mer-pag-003</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
@@ -13703,17 +13703,17 @@
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Pagarés seriados — lugar de pago</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -13738,57 +13738,57 @@
       </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
         </is>
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2019464</t>
         </is>
       </c>
       <c r="M107" s="13" t="inlineStr"/>
       <c r="N107" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="O107" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
         </is>
       </c>
       <c r="R107" s="13" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
         </is>
       </c>
       <c r="S107" s="13" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
         </is>
       </c>
       <c r="T107" s="13" t="inlineStr"/>
       <c r="U107" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
       <c r="V107" s="13" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
     <row r="108" ht="80" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>pen-cad-002</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
@@ -13806,22 +13806,22 @@
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -13836,55 +13836,349 @@
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2027962</t>
         </is>
       </c>
       <c r="M108" s="11" t="inlineStr"/>
       <c r="N108" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O108" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P108" s="11" t="inlineStr"/>
       <c r="Q108" s="11" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
         </is>
       </c>
       <c r="R108" s="11" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
         </is>
       </c>
       <c r="S108" s="11" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
         </is>
       </c>
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+        </is>
+      </c>
+      <c r="V108" s="11" t="inlineStr">
+        <is>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="80" customHeight="1">
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>pen-cad-003</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>Cadena de custodia</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>Transgresión no torna ilícita la prueba</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H109" s="13" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J109" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K109" s="14" t="inlineStr">
+        <is>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+        </is>
+      </c>
+      <c r="L109" s="13" t="inlineStr">
+        <is>
+          <t>2021845</t>
+        </is>
+      </c>
+      <c r="M109" s="13" t="inlineStr"/>
+      <c r="N109" s="13" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O109" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P109" s="13" t="inlineStr"/>
+      <c r="Q109" s="13" t="inlineStr">
+        <is>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+        </is>
+      </c>
+      <c r="R109" s="13" t="inlineStr">
+        <is>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+        </is>
+      </c>
+      <c r="S109" s="13" t="inlineStr">
+        <is>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+        </is>
+      </c>
+      <c r="T109" s="13" t="inlineStr"/>
+      <c r="U109" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+        </is>
+      </c>
+      <c r="V109" s="13" t="inlineStr">
+        <is>
+          <t>cadena custodia · valor probatorio · exclusión</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="80" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>pen-ppo-001</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H110" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+        </is>
+      </c>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>2032107</t>
+        </is>
+      </c>
+      <c r="M110" s="11" t="inlineStr"/>
+      <c r="N110" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O110" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P110" s="11" t="inlineStr"/>
+      <c r="Q110" s="11" t="inlineStr">
+        <is>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+        </is>
+      </c>
+      <c r="R110" s="11" t="inlineStr">
+        <is>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+        </is>
+      </c>
+      <c r="S110" s="11" t="inlineStr">
+        <is>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+        </is>
+      </c>
+      <c r="T110" s="11" t="inlineStr"/>
+      <c r="U110" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+        </is>
+      </c>
+      <c r="V110" s="11" t="inlineStr">
+        <is>
+          <t>PPO · víctima · legitimación · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="80" customHeight="1">
+      <c r="A111" s="13" t="inlineStr">
+        <is>
+          <t>pen-ppo-002</t>
+        </is>
+      </c>
+      <c r="B111" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="inlineStr">
+        <is>
+          <t>Cese cuando MP no prueba prolongación</t>
+        </is>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J111" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K111" s="14" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+        </is>
+      </c>
+      <c r="L111" s="13" t="inlineStr">
+        <is>
+          <t>2032108</t>
+        </is>
+      </c>
+      <c r="M111" s="13" t="inlineStr"/>
+      <c r="N111" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O111" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P111" s="13" t="inlineStr"/>
+      <c r="Q111" s="13" t="inlineStr">
+        <is>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+        </is>
+      </c>
+      <c r="R111" s="13" t="inlineStr">
+        <is>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+        </is>
+      </c>
+      <c r="S111" s="13" t="inlineStr">
+        <is>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+        </is>
+      </c>
+      <c r="T111" s="13" t="inlineStr"/>
+      <c r="U111" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
         </is>
       </c>
-      <c r="V108" s="11" t="inlineStr">
+      <c r="V111" s="13" t="inlineStr">
         <is>
           <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V108"/>
+  <autoFilter ref="A1:V111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13895,7 +14189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15068,8 +15362,106 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032177</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K13" s="14" t="inlineStr">
+        <is>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>2032177</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr"/>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
+        </is>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="inlineStr"/>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S13" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T13" s="13" t="inlineStr"/>
+      <c r="U13" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+        </is>
+      </c>
+      <c r="V13" s="13" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V12"/>
+  <autoFilter ref="A1:V13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19571,7 +19963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20935,7 +21327,7 @@
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -20953,12 +21345,12 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -20983,55 +21375,251 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr"/>
       <c r="U15" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032184</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>2032184</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr"/>
+      <c r="Q16" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R16" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr"/>
+      <c r="U16" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+        </is>
+      </c>
+      <c r="V16" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>amp-gen-001</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género interseccional</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>2032067</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr"/>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="inlineStr"/>
+      <c r="Q17" s="13" t="inlineStr">
+        <is>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+        </is>
+      </c>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+        </is>
+      </c>
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+        </is>
+      </c>
+      <c r="T17" s="13" t="inlineStr"/>
+      <c r="U17" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
-      <c r="V15" s="13" t="inlineStr">
+      <c r="V17" s="13" t="inlineStr">
         <is>
           <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V15"/>
+  <autoFilter ref="A1:V17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Acervo_Jurisprudencial.xlsx
+++ b/Acervo_Jurisprudencial.xlsx
@@ -20,15 +20,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penal" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Civil — Condominio'!$A$1:$V$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fiscal'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Laboral'!$A$1:$V$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Penal'!$A$1:$V$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -655,17 +655,17 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1672,7 +1672,7 @@
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>auto-2032198</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -1720,57 +1720,57 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2032198</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
         </is>
       </c>
       <c r="V10" s="11" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
@@ -1793,17 +1793,17 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
@@ -1818,57 +1818,57 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr"/>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P11" s="13" t="inlineStr"/>
       <c r="Q11" s="13" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R11" s="13" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S11" s="13" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T11" s="13" t="inlineStr"/>
       <c r="U11" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V11" s="13" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1916,57 +1916,57 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
@@ -2014,18 +2014,18 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O13" s="13" t="inlineStr">
@@ -2036,33 +2036,131 @@
       <c r="P13" s="13" t="inlineStr"/>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S13" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr"/>
       <c r="U13" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+        </is>
+      </c>
+      <c r="V13" s="13" t="inlineStr">
+        <is>
+          <t>pagaré · acción causal · ordinario mercantil</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>mer-pag-003</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Títulos de crédito — pagaré</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Pagarés seriados — lugar de pago</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>2019464</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr"/>
+      <c r="Q14" s="11" t="inlineStr">
+        <is>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+        </is>
+      </c>
+      <c r="R14" s="11" t="inlineStr">
+        <is>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+        </is>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+        </is>
+      </c>
+      <c r="T14" s="11" t="inlineStr"/>
+      <c r="U14" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
-      <c r="V13" s="13" t="inlineStr">
+      <c r="V14" s="11" t="inlineStr">
         <is>
           <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V13"/>
+  <autoFilter ref="A1:V14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3654,7 +3752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V111"/>
+  <dimension ref="A1:V113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9720,7 +9818,7 @@
     <row r="66" ht="80" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>pen-rep-001</t>
+          <t>auto-2032212</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
@@ -9733,17 +9831,17 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
         <is>
-          <t>Compensación directa como parte de reparación integral</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G66" s="11" t="inlineStr">
@@ -9768,94 +9866,90 @@
       </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
+          <t>SUSPENSIÓN PROVISIONAL CON EFECTOS RESTITUTORIOS. ES IMPROCEDENTE CONTRA LA NEGATIVA MATERIAL A RECIBIR UNA SOLICITUD DE BASIFICACIÓN LABORAL, PORQUE SU CONCESIÓN IMPLICA UN BENEFICIO TOTAL QUE DEJA SIN MATERIA EL JUICIO DE AMPARO.</t>
         </is>
       </c>
       <c r="L66" s="11" t="inlineStr">
         <is>
-          <t>2032030</t>
+          <t>2032212</t>
         </is>
       </c>
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O66" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P66" s="11" t="inlineStr"/>
       <c r="Q66" s="11" t="inlineStr">
         <is>
-          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R66" s="11" t="inlineStr">
         <is>
-          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S66" s="11" t="inlineStr">
         <is>
-          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
-        </is>
-      </c>
-      <c r="T66" s="11" t="inlineStr">
-        <is>
-          <t>PR.P.T.CN. J/8 P (12a.)</t>
-        </is>
-      </c>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T66" s="11" t="inlineStr"/>
       <c r="U66" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032212</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
         <is>
-          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="67" ht="80" customHeight="1">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>civ-agua-002</t>
+          <t>pen-rep-001</t>
         </is>
       </c>
       <c r="B67" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>Plenos Regionales</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>Agua y servicios públicos</t>
+          <t>Reparación del daño</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>Cobros excesivos y nulidad</t>
+          <t>Compensación directa como parte de reparación integral</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I67" s="13" t="inlineStr">
@@ -9865,54 +9959,66 @@
       </c>
       <c r="J67" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
+          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
         </is>
       </c>
       <c r="L67" s="13" t="inlineStr">
         <is>
-          <t>Criterio TJA</t>
+          <t>2032030</t>
         </is>
       </c>
       <c r="M67" s="13" t="inlineStr"/>
-      <c r="N67" s="13" t="inlineStr"/>
-      <c r="O67" s="13" t="inlineStr"/>
+      <c r="N67" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O67" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P67" s="13" t="inlineStr"/>
       <c r="Q67" s="13" t="inlineStr">
         <is>
-          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
+          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
         </is>
       </c>
       <c r="R67" s="13" t="inlineStr">
         <is>
-          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
+          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
         </is>
       </c>
       <c r="S67" s="13" t="inlineStr">
         <is>
-          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
-        </is>
-      </c>
-      <c r="T67" s="13" t="inlineStr"/>
+          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
+        </is>
+      </c>
+      <c r="T67" s="13" t="inlineStr">
+        <is>
+          <t>PR.P.T.CN. J/8 P (12a.)</t>
+        </is>
+      </c>
       <c r="U67" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
         </is>
       </c>
       <c r="V67" s="13" t="inlineStr">
         <is>
-          <t>cobro excesivo · medidor · TJA</t>
+          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
         </is>
       </c>
     </row>
     <row r="68" ht="80" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-001</t>
+          <t>civ-agua-002</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
@@ -9930,12 +10036,12 @@
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud</t>
+          <t>Agua y servicios públicos</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Reasignación sexual — IMSS</t>
+          <t>Cobros excesivos y nulidad</t>
         </is>
       </c>
       <c r="G68" s="11" t="inlineStr">
@@ -9945,7 +10051,7 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -9955,62 +10061,54 @@
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
+          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
         </is>
       </c>
       <c r="L68" s="11" t="inlineStr">
         <is>
-          <t>2032111</t>
+          <t>Criterio TJA</t>
         </is>
       </c>
       <c r="M68" s="11" t="inlineStr"/>
-      <c r="N68" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N68" s="11" t="inlineStr"/>
+      <c r="O68" s="11" t="inlineStr"/>
       <c r="P68" s="11" t="inlineStr"/>
       <c r="Q68" s="11" t="inlineStr">
         <is>
-          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
+          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
         </is>
       </c>
       <c r="R68" s="11" t="inlineStr">
         <is>
-          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
+          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
         </is>
       </c>
       <c r="S68" s="11" t="inlineStr">
         <is>
-          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
+          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
         </is>
       </c>
       <c r="T68" s="11" t="inlineStr"/>
       <c r="U68" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
         <is>
-          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
+          <t>cobro excesivo · medidor · TJA</t>
         </is>
       </c>
     </row>
     <row r="69" ht="80" customHeight="1">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>amp-sal-002</t>
+          <t>amp-sal-001</t>
         </is>
       </c>
       <c r="B69" s="13" t="n">
@@ -10033,7 +10131,7 @@
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Efectos del amparo contra negativa de cirugía</t>
+          <t>Reasignación sexual — IMSS</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
@@ -10058,12 +10156,12 @@
       </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
+          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
         </is>
       </c>
       <c r="L69" s="13" t="inlineStr">
         <is>
-          <t>2032110</t>
+          <t>2032111</t>
         </is>
       </c>
       <c r="M69" s="13" t="inlineStr"/>
@@ -10080,35 +10178,35 @@
       <c r="P69" s="13" t="inlineStr"/>
       <c r="Q69" s="13" t="inlineStr">
         <is>
-          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
+          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
         </is>
       </c>
       <c r="R69" s="13" t="inlineStr">
         <is>
-          <t>Define alcance positivo del amparo en salud.</t>
+          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
         </is>
       </c>
       <c r="S69" s="13" t="inlineStr">
         <is>
-          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
+          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
         </is>
       </c>
       <c r="T69" s="13" t="inlineStr"/>
       <c r="U69" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
         </is>
       </c>
       <c r="V69" s="13" t="inlineStr">
         <is>
-          <t>amparo efectos · cirugía · salud · 12a Época</t>
+          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="70" ht="80" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-003</t>
+          <t>amp-sal-002</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
@@ -10131,7 +10229,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Autonomía IMSS limitada por DDHH</t>
+          <t>Efectos del amparo contra negativa de cirugía</t>
         </is>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -10156,12 +10254,12 @@
       </c>
       <c r="K70" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
+          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
         </is>
       </c>
       <c r="L70" s="11" t="inlineStr">
         <is>
-          <t>2032087</t>
+          <t>2032110</t>
         </is>
       </c>
       <c r="M70" s="11" t="inlineStr"/>
@@ -10178,35 +10276,35 @@
       <c r="P70" s="11" t="inlineStr"/>
       <c r="Q70" s="11" t="inlineStr">
         <is>
-          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
+          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
         </is>
       </c>
       <c r="R70" s="11" t="inlineStr">
         <is>
-          <t>Marco general contra negativas burocráticas del IMSS.</t>
+          <t>Define alcance positivo del amparo en salud.</t>
         </is>
       </c>
       <c r="S70" s="11" t="inlineStr">
         <is>
-          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
+          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
         </is>
       </c>
       <c r="T70" s="11" t="inlineStr"/>
       <c r="U70" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
         </is>
       </c>
       <c r="V70" s="11" t="inlineStr">
         <is>
-          <t>salud · IMSS · autonomía limitada · 12a Época</t>
+          <t>amparo efectos · cirugía · salud · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="71" ht="80" customHeight="1">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>auto-2032131</t>
+          <t>amp-sal-003</t>
         </is>
       </c>
       <c r="B71" s="13" t="n">
@@ -10229,7 +10327,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Autonomía IMSS limitada por DDHH</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -10254,57 +10352,57 @@
       </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
-          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
+          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
         </is>
       </c>
       <c r="L71" s="13" t="inlineStr">
         <is>
-          <t>2032131</t>
+          <t>2032087</t>
         </is>
       </c>
       <c r="M71" s="13" t="inlineStr"/>
       <c r="N71" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O71" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P71" s="13" t="inlineStr"/>
       <c r="Q71" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
         </is>
       </c>
       <c r="R71" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Marco general contra negativas burocráticas del IMSS.</t>
         </is>
       </c>
       <c r="S71" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
         </is>
       </c>
       <c r="T71" s="13" t="inlineStr"/>
       <c r="U71" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
         </is>
       </c>
       <c r="V71" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud · actualización automática</t>
+          <t>salud · IMSS · autonomía limitada · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="72" ht="80" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>auto-2032177</t>
+          <t>auto-2032131</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
@@ -10322,7 +10420,7 @@
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -10352,18 +10450,18 @@
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
         </is>
       </c>
       <c r="L72" s="11" t="inlineStr">
         <is>
-          <t>2032177</t>
+          <t>2032131</t>
         </is>
       </c>
       <c r="M72" s="11" t="inlineStr"/>
       <c r="N72" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
         </is>
       </c>
       <c r="O72" s="11" t="inlineStr">
@@ -10390,19 +10488,19 @@
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="73" ht="80" customHeight="1">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B73" s="13" t="n">
@@ -10415,17 +10513,17 @@
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
@@ -10435,7 +10533,7 @@
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I73" s="13" t="inlineStr">
@@ -10450,57 +10548,57 @@
       </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L73" s="13" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M73" s="13" t="inlineStr"/>
       <c r="N73" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O73" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P73" s="13" t="inlineStr"/>
       <c r="Q73" s="13" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R73" s="13" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S73" s="13" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T73" s="13" t="inlineStr"/>
       <c r="U73" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
         </is>
       </c>
       <c r="V73" s="13" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="74" ht="80" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
@@ -10518,12 +10616,12 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
@@ -10533,7 +10631,7 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -10548,57 +10646,57 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M74" s="11" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P74" s="11" t="inlineStr"/>
       <c r="Q74" s="11" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R74" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S74" s="11" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="75" ht="80" customHeight="1">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B75" s="13" t="n">
@@ -10621,7 +10719,7 @@
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
@@ -10646,12 +10744,12 @@
       </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L75" s="13" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M75" s="13" t="inlineStr"/>
@@ -10668,35 +10766,35 @@
       <c r="P75" s="13" t="inlineStr"/>
       <c r="Q75" s="13" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R75" s="13" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S75" s="13" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T75" s="13" t="inlineStr"/>
       <c r="U75" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V75" s="13" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="76" ht="80" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
@@ -10709,17 +10807,17 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
@@ -10729,7 +10827,7 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -10739,54 +10837,62 @@
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr"/>
-      <c r="N76" s="11" t="inlineStr"/>
-      <c r="O76" s="11" t="inlineStr"/>
+      <c r="N76" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O76" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P76" s="11" t="inlineStr"/>
       <c r="Q76" s="11" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S76" s="11" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="77" ht="80" customHeight="1">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B77" s="13" t="n">
@@ -10809,7 +10915,7 @@
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
@@ -10819,7 +10925,7 @@
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
@@ -10829,62 +10935,54 @@
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L77" s="13" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M77" s="13" t="inlineStr"/>
-      <c r="N77" s="13" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O77" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N77" s="13" t="inlineStr"/>
+      <c r="O77" s="13" t="inlineStr"/>
       <c r="P77" s="13" t="inlineStr"/>
       <c r="Q77" s="13" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R77" s="13" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S77" s="13" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T77" s="13" t="inlineStr"/>
       <c r="U77" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V77" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="78" ht="80" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
@@ -10907,7 +11005,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -10917,7 +11015,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -10927,62 +11025,62 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr"/>
       <c r="N78" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P78" s="11" t="inlineStr"/>
       <c r="Q78" s="11" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S78" s="11" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="79" ht="80" customHeight="1">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B79" s="13" t="n">
@@ -11000,12 +11098,12 @@
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -11015,7 +11113,7 @@
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr">
@@ -11030,57 +11128,57 @@
       </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L79" s="13" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M79" s="13" t="inlineStr"/>
       <c r="N79" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O79" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P79" s="13" t="inlineStr"/>
       <c r="Q79" s="13" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R79" s="13" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S79" s="13" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T79" s="13" t="inlineStr"/>
       <c r="U79" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V79" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="80" ht="80" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
@@ -11103,7 +11201,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -11113,7 +11211,7 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
@@ -11123,23 +11221,23 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M80" s="11" t="inlineStr"/>
       <c r="N80" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O80" s="11" t="inlineStr">
@@ -11150,35 +11248,35 @@
       <c r="P80" s="11" t="inlineStr"/>
       <c r="Q80" s="11" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S80" s="11" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T80" s="11" t="inlineStr"/>
       <c r="U80" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V80" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="81" ht="80" customHeight="1">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B81" s="13" t="n">
@@ -11196,12 +11294,12 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
@@ -11226,57 +11324,57 @@
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L81" s="13" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M81" s="13" t="inlineStr"/>
       <c r="N81" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O81" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P81" s="13" t="inlineStr"/>
       <c r="Q81" s="13" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R81" s="13" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S81" s="13" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T81" s="13" t="inlineStr"/>
       <c r="U81" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V81" s="13" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="82" ht="80" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
@@ -11294,12 +11392,12 @@
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -11324,18 +11422,18 @@
       </c>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M82" s="11" t="inlineStr"/>
       <c r="N82" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O82" s="11" t="inlineStr">
@@ -11346,35 +11444,35 @@
       <c r="P82" s="11" t="inlineStr"/>
       <c r="Q82" s="11" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R82" s="11" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S82" s="11" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="83" ht="80" customHeight="1">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>auto-2032124</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B83" s="13" t="n">
@@ -11392,12 +11490,12 @@
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
@@ -11407,7 +11505,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -11422,57 +11520,57 @@
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L83" s="13" t="inlineStr">
         <is>
-          <t>2032124</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M83" s="13" t="inlineStr"/>
       <c r="N83" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O83" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P83" s="13" t="inlineStr"/>
       <c r="Q83" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R83" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S83" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T83" s="13" t="inlineStr"/>
       <c r="U83" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V83" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="84" ht="80" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
@@ -11495,7 +11593,7 @@
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -11505,7 +11603,7 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I84" s="11" t="inlineStr">
@@ -11515,54 +11613,62 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M84" s="11" t="inlineStr"/>
-      <c r="N84" s="11" t="inlineStr"/>
-      <c r="O84" s="11" t="inlineStr"/>
+      <c r="N84" s="11" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P84" s="11" t="inlineStr"/>
       <c r="Q84" s="11" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S84" s="11" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="85" ht="80" customHeight="1">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B85" s="13" t="n">
@@ -11585,7 +11691,7 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
@@ -11595,7 +11701,7 @@
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -11605,62 +11711,54 @@
       </c>
       <c r="J85" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L85" s="13" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M85" s="13" t="inlineStr"/>
-      <c r="N85" s="13" t="inlineStr">
-        <is>
-          <t>Novena Época</t>
-        </is>
-      </c>
-      <c r="O85" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N85" s="13" t="inlineStr"/>
+      <c r="O85" s="13" t="inlineStr"/>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="13" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R85" s="13" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S85" s="13" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T85" s="13" t="inlineStr"/>
       <c r="U85" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V85" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="86" ht="80" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
@@ -11683,7 +11781,7 @@
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
@@ -11703,17 +11801,17 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr"/>
@@ -11724,41 +11822,41 @@
       </c>
       <c r="O86" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P86" s="11" t="inlineStr"/>
       <c r="Q86" s="11" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S86" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="87" ht="80" customHeight="1">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
@@ -11776,22 +11874,22 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
@@ -11801,58 +11899,62 @@
       </c>
       <c r="J87" s="13" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M87" s="13" t="inlineStr"/>
       <c r="N87" s="13" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O87" s="13" t="inlineStr"/>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O87" s="13" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P87" s="13" t="inlineStr"/>
       <c r="Q87" s="13" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R87" s="13" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S87" s="13" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T87" s="13" t="inlineStr"/>
       <c r="U87" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V87" s="13" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="88" ht="80" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
@@ -11870,22 +11972,22 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -11895,62 +11997,58 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M88" s="11" t="inlineStr"/>
       <c r="N88" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O88" s="11" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O88" s="11" t="inlineStr"/>
       <c r="P88" s="11" t="inlineStr"/>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S88" s="11" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="89" ht="80" customHeight="1">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B89" s="13" t="n">
@@ -11968,22 +12066,22 @@
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -11993,58 +12091,62 @@
       </c>
       <c r="J89" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M89" s="13" t="inlineStr"/>
-      <c r="N89" s="13" t="inlineStr"/>
+      <c r="N89" s="13" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
       <c r="O89" s="13" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P89" s="13" t="inlineStr"/>
       <c r="Q89" s="13" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R89" s="13" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S89" s="13" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T89" s="13" t="inlineStr"/>
       <c r="U89" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V89" s="13" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="90" ht="80" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
@@ -12067,7 +12169,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -12077,7 +12179,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -12087,54 +12189,58 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M90" s="11" t="inlineStr"/>
       <c r="N90" s="11" t="inlineStr"/>
-      <c r="O90" s="11" t="inlineStr"/>
+      <c r="O90" s="11" t="inlineStr">
+        <is>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+        </is>
+      </c>
       <c r="P90" s="11" t="inlineStr"/>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S90" s="11" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
         <is>
-          <t>posesión derivada · concepto de propietario · interversión</t>
+          <t>pericial · topografía · identidad del bien</t>
         </is>
       </c>
     </row>
     <row r="91" ht="80" customHeight="1">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>con-asa-001</t>
+          <t>civ-usu-005</t>
         </is>
       </c>
       <c r="B91" s="13" t="n">
@@ -12147,22 +12253,22 @@
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>Asambleas — convocatoria y validez</t>
+          <t>Posesión derivada vs. originaria</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -12177,17 +12283,17 @@
       </c>
       <c r="J91" s="13" t="inlineStr">
         <is>
-          <t>Federal — interpreta LPCI CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L91" s="13" t="inlineStr">
         <is>
-          <t>Art. 32 LPCI CDMX</t>
+          <t>2030499</t>
         </is>
       </c>
       <c r="M91" s="13" t="inlineStr"/>
@@ -12196,35 +12302,35 @@
       <c r="P91" s="13" t="inlineStr"/>
       <c r="Q91" s="13" t="inlineStr">
         <is>
-          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
         </is>
       </c>
       <c r="R91" s="13" t="inlineStr">
         <is>
-          <t>Defensa frecuente de minorías condominales.</t>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
         </is>
       </c>
       <c r="S91" s="13" t="inlineStr">
         <is>
-          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
         </is>
       </c>
       <c r="T91" s="13" t="inlineStr"/>
       <c r="U91" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
       <c r="V91" s="13" t="inlineStr">
         <is>
-          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
+          <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
     <row r="92" ht="80" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>amp-cui-001</t>
+          <t>con-asa-001</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
@@ -12237,17 +12343,17 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Reconocimiento e interés legítimo</t>
+          <t>Asambleas — convocatoria y validez</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -12257,7 +12363,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -12267,62 +12373,54 @@
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta LPCI CDMX</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
+          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
         </is>
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>2032085</t>
+          <t>Art. 32 LPCI CDMX</t>
         </is>
       </c>
       <c r="M92" s="11" t="inlineStr"/>
-      <c r="N92" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O92" s="11" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N92" s="11" t="inlineStr"/>
+      <c r="O92" s="11" t="inlineStr"/>
       <c r="P92" s="11" t="inlineStr"/>
       <c r="Q92" s="11" t="inlineStr">
         <is>
-          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
+          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
         </is>
       </c>
       <c r="R92" s="11" t="inlineStr">
         <is>
-          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
+          <t>Defensa frecuente de minorías condominales.</t>
         </is>
       </c>
       <c r="S92" s="11" t="inlineStr">
         <is>
-          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
+          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
         </is>
       </c>
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
+          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
         </is>
       </c>
     </row>
     <row r="93" ht="80" customHeight="1">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>amp-cui-002</t>
+          <t>amp-cui-001</t>
         </is>
       </c>
       <c r="B93" s="13" t="n">
@@ -12345,7 +12443,7 @@
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>Interés legítimo para combatir omisiones legislativas</t>
+          <t>Reconocimiento e interés legítimo</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -12370,12 +12468,12 @@
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
+          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L93" s="13" t="inlineStr">
         <is>
-          <t>2032086</t>
+          <t>2032085</t>
         </is>
       </c>
       <c r="M93" s="13" t="inlineStr"/>
@@ -12392,35 +12490,35 @@
       <c r="P93" s="13" t="inlineStr"/>
       <c r="Q93" s="13" t="inlineStr">
         <is>
-          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
+          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
         </is>
       </c>
       <c r="R93" s="13" t="inlineStr">
         <is>
-          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
+          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
         </is>
       </c>
       <c r="S93" s="13" t="inlineStr">
         <is>
-          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
+          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
         </is>
       </c>
       <c r="T93" s="13" t="inlineStr"/>
       <c r="U93" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
         </is>
       </c>
       <c r="V93" s="13" t="inlineStr">
         <is>
-          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
+          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
         </is>
       </c>
     </row>
     <row r="94" ht="80" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>auto-2032154</t>
+          <t>amp-cui-002</t>
         </is>
       </c>
       <c r="B94" s="11" t="n">
@@ -12438,12 +12536,12 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Interés legítimo para combatir omisiones legislativas</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
@@ -12468,57 +12566,57 @@
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
+          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
         </is>
       </c>
       <c r="L94" s="11" t="inlineStr">
         <is>
-          <t>2032154</t>
+          <t>2032086</t>
         </is>
       </c>
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O94" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P94" s="11" t="inlineStr"/>
       <c r="Q94" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
         </is>
       </c>
       <c r="R94" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
         </is>
       </c>
       <c r="S94" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
         </is>
       </c>
       <c r="T94" s="11" t="inlineStr"/>
       <c r="U94" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
         </is>
       </c>
       <c r="V94" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
         </is>
       </c>
     </row>
     <row r="95" ht="80" customHeight="1">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>auto-2032184</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B95" s="13" t="n">
@@ -12566,12 +12664,12 @@
       </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
-          <t>2032184</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M95" s="13" t="inlineStr"/>
@@ -12604,7 +12702,7 @@
       <c r="T95" s="13" t="inlineStr"/>
       <c r="U95" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V95" s="13" t="inlineStr">
@@ -12616,7 +12714,7 @@
     <row r="96" ht="80" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
@@ -12634,12 +12732,12 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
@@ -12664,57 +12762,57 @@
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M96" s="11" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O96" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P96" s="11" t="inlineStr"/>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R96" s="11" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S96" s="11" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T96" s="11" t="inlineStr"/>
       <c r="U96" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
         </is>
       </c>
       <c r="V96" s="11" t="inlineStr">
         <is>
-          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="97" ht="80" customHeight="1">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-002</t>
+          <t>amp-gen-001</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
@@ -12727,22 +12825,22 @@
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género interseccional</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>69-B — recurso de revocación y buzón tributario</t>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -12762,57 +12860,57 @@
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
         </is>
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>2031931</t>
+          <t>2032067</t>
         </is>
       </c>
       <c r="M97" s="13" t="inlineStr"/>
       <c r="N97" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O97" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="13" t="inlineStr">
         <is>
-          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
         </is>
       </c>
       <c r="R97" s="13" t="inlineStr">
         <is>
-          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
         </is>
       </c>
       <c r="S97" s="13" t="inlineStr">
         <is>
-          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
         </is>
       </c>
       <c r="T97" s="13" t="inlineStr"/>
       <c r="U97" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
       <c r="V97" s="13" t="inlineStr">
         <is>
-          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
+          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="98" ht="80" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-003</t>
+          <t>fis-cfd-002</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
@@ -12835,12 +12933,12 @@
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Materialidad — fundar y motivar</t>
+          <t>69-B — recurso de revocación y buzón tributario</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -12860,12 +12958,12 @@
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
         </is>
       </c>
       <c r="L98" s="11" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>2031931</t>
         </is>
       </c>
       <c r="M98" s="11" t="inlineStr"/>
@@ -12882,35 +12980,35 @@
       <c r="P98" s="11" t="inlineStr"/>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
+          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
         </is>
       </c>
       <c r="R98" s="11" t="inlineStr">
         <is>
-          <t>Defensa fuerte para contribuyentes auditados.</t>
+          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
         </is>
       </c>
       <c r="S98" s="11" t="inlineStr">
         <is>
-          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
+          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
         </is>
       </c>
       <c r="T98" s="11" t="inlineStr"/>
       <c r="U98" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
         </is>
       </c>
       <c r="V98" s="11" t="inlineStr">
         <is>
-          <t>69-B · materialidad · fundamentación · 12a Época</t>
+          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
         </is>
       </c>
     </row>
     <row r="99" ht="80" customHeight="1">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-004</t>
+          <t>fis-cfd-003</t>
         </is>
       </c>
       <c r="B99" s="13" t="n">
@@ -12933,7 +13031,7 @@
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>Nulidad EFOS — efectos sobre proveedor</t>
+          <t>Materialidad — fundar y motivar</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -12958,12 +13056,12 @@
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>2031349</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M99" s="13" t="inlineStr"/>
@@ -12980,35 +13078,35 @@
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr">
         <is>
-          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
+          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
         </is>
       </c>
       <c r="R99" s="13" t="inlineStr">
         <is>
-          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
+          <t>Defensa fuerte para contribuyentes auditados.</t>
         </is>
       </c>
       <c r="S99" s="13" t="inlineStr">
         <is>
-          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
+          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
         </is>
       </c>
       <c r="T99" s="13" t="inlineStr"/>
       <c r="U99" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V99" s="13" t="inlineStr">
         <is>
-          <t>EFOS · nulidad · deducciones · 12a Época</t>
+          <t>69-B · materialidad · fundamentación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="100" ht="80" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>lab-des-002</t>
+          <t>fis-cfd-004</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
@@ -13021,17 +13119,17 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Carga patrón cuando alega rescisión justificada posterior</t>
+          <t>Nulidad EFOS — efectos sobre proveedor</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
@@ -13041,7 +13139,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -13056,18 +13154,18 @@
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>2031349</t>
         </is>
       </c>
       <c r="M100" s="11" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O100" s="11" t="inlineStr">
@@ -13078,35 +13176,35 @@
       <c r="P100" s="11" t="inlineStr"/>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
+          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
         </is>
       </c>
       <c r="R100" s="11" t="inlineStr">
         <is>
-          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
+          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
         </is>
       </c>
       <c r="S100" s="11" t="inlineStr">
         <is>
-          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
+          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
         </is>
       </c>
       <c r="T100" s="11" t="inlineStr"/>
       <c r="U100" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
         </is>
       </c>
       <c r="V100" s="11" t="inlineStr">
         <is>
-          <t>despido · rescisión · carga probatoria patrón</t>
+          <t>EFOS · nulidad · deducciones · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="101" ht="80" customHeight="1">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>lab-ren-001</t>
+          <t>lab-des-002</t>
         </is>
       </c>
       <c r="B101" s="13" t="n">
@@ -13124,12 +13222,12 @@
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>Hora de terminación — carga del patrón</t>
+          <t>Carga patrón cuando alega rescisión justificada posterior</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -13154,18 +13252,18 @@
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
+          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
         </is>
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>2028640</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M101" s="13" t="inlineStr"/>
       <c r="N101" s="13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O101" s="13" t="inlineStr">
@@ -13176,35 +13274,35 @@
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr">
         <is>
-          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
+          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
         </is>
       </c>
       <c r="R101" s="13" t="inlineStr">
         <is>
-          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
+          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
         </is>
       </c>
       <c r="S101" s="13" t="inlineStr">
         <is>
-          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
+          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
         </is>
       </c>
       <c r="T101" s="13" t="inlineStr"/>
       <c r="U101" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V101" s="13" t="inlineStr">
         <is>
-          <t>renuncia · hora despido · carga probatoria</t>
+          <t>despido · rescisión · carga probatoria patrón</t>
         </is>
       </c>
     </row>
     <row r="102" ht="80" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>lab-ren-002</t>
+          <t>lab-ren-001</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
@@ -13227,7 +13325,7 @@
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
+          <t>Hora de terminación — carga del patrón</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -13252,18 +13350,18 @@
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
+          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>2027058</t>
+          <t>2028640</t>
         </is>
       </c>
       <c r="M102" s="11" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O102" s="11" t="inlineStr">
@@ -13274,35 +13372,35 @@
       <c r="P102" s="11" t="inlineStr"/>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
+          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
         </is>
       </c>
       <c r="R102" s="11" t="inlineStr">
         <is>
-          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
+          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
         </is>
       </c>
       <c r="S102" s="11" t="inlineStr">
         <is>
-          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
+          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
         </is>
       </c>
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>renuncia · jubilación · veracidad · carga reforzada</t>
+          <t>renuncia · hora despido · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="103" ht="80" customHeight="1">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>sen-020</t>
+          <t>lab-ren-002</t>
         </is>
       </c>
       <c r="B103" s="13" t="n">
@@ -13315,27 +13413,27 @@
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Costas en juicio mercantil — tasación</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
+          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr">
@@ -13345,58 +13443,62 @@
       </c>
       <c r="J103" s="13" t="inlineStr">
         <is>
-          <t>Primer y Segundo Circuito</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
+          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
         </is>
       </c>
       <c r="L103" s="13" t="inlineStr">
         <is>
-          <t>Línea de Colegiados — múltiples</t>
+          <t>2027058</t>
         </is>
       </c>
       <c r="M103" s="13" t="inlineStr"/>
       <c r="N103" s="13" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O103" s="13" t="inlineStr"/>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="O103" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P103" s="13" t="inlineStr"/>
       <c r="Q103" s="13" t="inlineStr">
         <is>
-          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
+          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
         </is>
       </c>
       <c r="R103" s="13" t="inlineStr">
         <is>
-          <t>Marco práctico para pretensión y oposición a costas.</t>
+          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
         </is>
       </c>
       <c r="S103" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
+          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
         </is>
       </c>
       <c r="T103" s="13" t="inlineStr"/>
       <c r="U103" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
         </is>
       </c>
       <c r="V103" s="13" t="inlineStr">
         <is>
-          <t>costas · tasación · arancel · mercantil</t>
+          <t>renuncia · jubilación · veracidad · carga reforzada</t>
         </is>
       </c>
     </row>
     <row r="104" ht="80" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>sen-020</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
@@ -13414,22 +13516,22 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Costas en juicio mercantil — tasación</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -13439,62 +13541,58 @@
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer y Segundo Circuito</t>
         </is>
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>Línea de Colegiados — múltiples</t>
         </is>
       </c>
       <c r="M104" s="11" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="O104" s="11" t="inlineStr">
-        <is>
-          <t>Gaceta SJF — VERIFICADO</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O104" s="11" t="inlineStr"/>
       <c r="P104" s="11" t="inlineStr"/>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
         </is>
       </c>
       <c r="R104" s="11" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Marco práctico para pretensión y oposición a costas.</t>
         </is>
       </c>
       <c r="S104" s="11" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
         </is>
       </c>
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
         </is>
       </c>
       <c r="V104" s="11" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>costas · tasación · arancel · mercantil</t>
         </is>
       </c>
     </row>
     <row r="105" ht="80" customHeight="1">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>auto-2032198</t>
         </is>
       </c>
       <c r="B105" s="13" t="n">
@@ -13517,7 +13615,7 @@
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -13542,57 +13640,57 @@
       </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
         </is>
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2032198</t>
         </is>
       </c>
       <c r="M105" s="13" t="inlineStr"/>
       <c r="N105" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O105" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P105" s="13" t="inlineStr"/>
       <c r="Q105" s="13" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R105" s="13" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S105" s="13" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T105" s="13" t="inlineStr"/>
       <c r="U105" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
         </is>
       </c>
       <c r="V105" s="13" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="106" ht="80" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
@@ -13610,17 +13708,17 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
@@ -13640,18 +13738,18 @@
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M106" s="11" t="inlineStr"/>
       <c r="N106" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O106" s="11" t="inlineStr">
@@ -13662,35 +13760,35 @@
       <c r="P106" s="11" t="inlineStr"/>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R106" s="11" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S106" s="11" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="107" ht="80" customHeight="1">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
@@ -13708,12 +13806,12 @@
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
@@ -13723,7 +13821,7 @@
       </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -13738,57 +13836,57 @@
       </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M107" s="13" t="inlineStr"/>
       <c r="N107" s="13" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O107" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R107" s="13" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S107" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T107" s="13" t="inlineStr"/>
       <c r="U107" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V107" s="13" t="inlineStr">
         <is>
-          <t>pagaré · pagarés seriados · lugar de pago</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="108" ht="80" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
@@ -13801,22 +13899,22 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -13836,18 +13934,18 @@
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M108" s="11" t="inlineStr"/>
       <c r="N108" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O108" s="11" t="inlineStr">
@@ -13858,35 +13956,35 @@
       <c r="P108" s="11" t="inlineStr"/>
       <c r="Q108" s="11" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R108" s="11" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S108" s="11" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>pagaré · acción causal · ordinario mercantil</t>
         </is>
       </c>
     </row>
     <row r="109" ht="80" customHeight="1">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>mer-pag-003</t>
         </is>
       </c>
       <c r="B109" s="13" t="n">
@@ -13899,17 +13997,17 @@
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Pagarés seriados — lugar de pago</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -13934,18 +14032,18 @@
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
         </is>
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2019464</t>
         </is>
       </c>
       <c r="M109" s="13" t="inlineStr"/>
       <c r="N109" s="13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="O109" s="13" t="inlineStr">
@@ -13956,35 +14054,35 @@
       <c r="P109" s="13" t="inlineStr"/>
       <c r="Q109" s="13" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
         </is>
       </c>
       <c r="R109" s="13" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
         </is>
       </c>
       <c r="S109" s="13" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
         </is>
       </c>
       <c r="T109" s="13" t="inlineStr"/>
       <c r="U109" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
       <c r="V109" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
     <row r="110" ht="80" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>pen-cad-002</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
@@ -14002,22 +14100,22 @@
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -14032,57 +14130,57 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
         </is>
       </c>
       <c r="L110" s="11" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2027962</t>
         </is>
       </c>
       <c r="M110" s="11" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O110" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P110" s="11" t="inlineStr"/>
       <c r="Q110" s="11" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
         </is>
       </c>
       <c r="R110" s="11" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
         </is>
       </c>
       <c r="S110" s="11" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
         </is>
       </c>
       <c r="T110" s="11" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
         </is>
       </c>
       <c r="V110" s="11" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
         </is>
       </c>
     </row>
     <row r="111" ht="80" customHeight="1">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>pen-cad-003</t>
         </is>
       </c>
       <c r="B111" s="13" t="n">
@@ -14100,12 +14198,12 @@
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Transgresión no torna ilícita la prueba</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -14115,7 +14213,7 @@
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I111" s="13" t="inlineStr">
@@ -14130,55 +14228,251 @@
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
         </is>
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2021845</t>
         </is>
       </c>
       <c r="M111" s="13" t="inlineStr"/>
       <c r="N111" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="O111" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P111" s="13" t="inlineStr"/>
       <c r="Q111" s="13" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
         </is>
       </c>
       <c r="R111" s="13" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
         </is>
       </c>
       <c r="S111" s="13" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
         </is>
       </c>
       <c r="T111" s="13" t="inlineStr"/>
       <c r="U111" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+        </is>
+      </c>
+      <c r="V111" s="13" t="inlineStr">
+        <is>
+          <t>cadena custodia · valor probatorio · exclusión</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="80" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>pen-ppo-001</t>
+        </is>
+      </c>
+      <c r="B112" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H112" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J112" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K112" s="12" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+        </is>
+      </c>
+      <c r="L112" s="11" t="inlineStr">
+        <is>
+          <t>2032107</t>
+        </is>
+      </c>
+      <c r="M112" s="11" t="inlineStr"/>
+      <c r="N112" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O112" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P112" s="11" t="inlineStr"/>
+      <c r="Q112" s="11" t="inlineStr">
+        <is>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+        </is>
+      </c>
+      <c r="R112" s="11" t="inlineStr">
+        <is>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+        </is>
+      </c>
+      <c r="S112" s="11" t="inlineStr">
+        <is>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+        </is>
+      </c>
+      <c r="T112" s="11" t="inlineStr"/>
+      <c r="U112" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+        </is>
+      </c>
+      <c r="V112" s="11" t="inlineStr">
+        <is>
+          <t>PPO · víctima · legitimación · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="80" customHeight="1">
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>pen-ppo-002</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>Cese cuando MP no prueba prolongación</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J113" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K113" s="14" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+        </is>
+      </c>
+      <c r="L113" s="13" t="inlineStr">
+        <is>
+          <t>2032108</t>
+        </is>
+      </c>
+      <c r="M113" s="13" t="inlineStr"/>
+      <c r="N113" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O113" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P113" s="13" t="inlineStr"/>
+      <c r="Q113" s="13" t="inlineStr">
+        <is>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+        </is>
+      </c>
+      <c r="R113" s="13" t="inlineStr">
+        <is>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+        </is>
+      </c>
+      <c r="S113" s="13" t="inlineStr">
+        <is>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+        </is>
+      </c>
+      <c r="T113" s="13" t="inlineStr"/>
+      <c r="U113" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
         </is>
       </c>
-      <c r="V111" s="13" t="inlineStr">
+      <c r="V113" s="13" t="inlineStr">
         <is>
           <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V111"/>
+  <autoFilter ref="A1:V113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15472,7 +15766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15884,15 +16178,15 @@
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>auto-2032212</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>Plenos Regionales</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -15902,22 +16196,22 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -15932,57 +16226,57 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>SUSPENSIÓN PROVISIONAL CON EFECTOS RESTITUTORIOS. ES IMPROCEDENTE CONTRA LA NEGATIVA MATERIAL A RECIBIR UNA SOLICITUD DE BASIFICACIÓN LABORAL, PORQUE SU CONCESIÓN IMPLICA UN BENEFICIO TOTAL QUE DEJA SIN MATERIA EL JUICIO DE AMPARO.</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032212</t>
         </is>
       </c>
       <c r="M5" s="13" t="inlineStr"/>
       <c r="N5" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O5" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P5" s="13" t="inlineStr"/>
       <c r="Q5" s="13" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R5" s="13" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S5" s="13" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T5" s="13" t="inlineStr"/>
       <c r="U5" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032212</t>
         </is>
       </c>
       <c r="V5" s="13" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
@@ -16000,12 +16294,12 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -16015,7 +16309,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -16030,57 +16324,57 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="11" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V6" s="11" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -16103,7 +16397,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -16128,12 +16422,12 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M7" s="13" t="inlineStr"/>
@@ -16150,33 +16444,131 @@
       <c r="P7" s="13" t="inlineStr"/>
       <c r="Q7" s="13" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R7" s="13" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S7" s="13" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T7" s="13" t="inlineStr"/>
       <c r="U7" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+        </is>
+      </c>
+      <c r="V7" s="13" t="inlineStr">
+        <is>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>amp-sus-003</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>2032066</t>
+        </is>
+      </c>
+      <c r="M8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr"/>
+      <c r="Q8" s="11" t="inlineStr">
+        <is>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+        </is>
+      </c>
+      <c r="R8" s="11" t="inlineStr">
+        <is>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+        </is>
+      </c>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+        </is>
+      </c>
+      <c r="T8" s="11" t="inlineStr"/>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
-      <c r="V7" s="13" t="inlineStr">
+      <c r="V8" s="11" t="inlineStr">
         <is>
           <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V7"/>
+  <autoFilter ref="A1:V8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Acervo_Jurisprudencial.xlsx
+++ b/Acervo_Jurisprudencial.xlsx
@@ -20,16 +20,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penal" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$130</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Civil — Condominio'!$A$1:$V$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fiscal'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Laboral'!$A$1:$V$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Penal'!$A$1:$V$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Penal'!$A$1:$V$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,37 +629,37 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2269,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4230,8 +4230,106 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032335</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>2032335</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr"/>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="inlineStr"/>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S21" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr"/>
+      <c r="U21" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+        </is>
+      </c>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V20"/>
+  <autoFilter ref="A1:V21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4242,7 +4340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V130"/>
+  <dimension ref="A1:V143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11774,7 +11872,7 @@
     <row r="81" ht="80" customHeight="1">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>auto-2032177</t>
+          <t>auto-2032353</t>
         </is>
       </c>
       <c r="B81" s="13" t="n">
@@ -11792,7 +11890,7 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -11822,18 +11920,18 @@
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>SUSPENSIÓN DE PLANO EN AMPARO INDIRECTO. PROCEDE PARA ORDENAR UNA VALORACIÓN MÉDICA EN EL DOMICILIO DE UNA PERSONA, CUANDO TIENE UNA MOVILIDAD RESTRINGIDA.</t>
         </is>
       </c>
       <c r="L81" s="13" t="inlineStr">
         <is>
-          <t>2032177</t>
+          <t>2032353</t>
         </is>
       </c>
       <c r="M81" s="13" t="inlineStr"/>
       <c r="N81" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O81" s="13" t="inlineStr">
@@ -11860,19 +11958,19 @@
       <c r="T81" s="13" t="inlineStr"/>
       <c r="U81" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032353</t>
         </is>
       </c>
       <c r="V81" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="82" ht="80" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>auto-2032233</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
@@ -11920,18 +12018,18 @@
       </c>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>2032233</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M82" s="11" t="inlineStr"/>
       <c r="N82" s="11" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O82" s="11" t="inlineStr">
@@ -11958,7 +12056,7 @@
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
@@ -11970,7 +12068,7 @@
     <row r="83" ht="80" customHeight="1">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>auto-2032233</t>
         </is>
       </c>
       <c r="B83" s="13" t="n">
@@ -11983,17 +12081,17 @@
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
@@ -12003,7 +12101,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr">
@@ -12018,57 +12116,57 @@
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
         </is>
       </c>
       <c r="L83" s="13" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032233</t>
         </is>
       </c>
       <c r="M83" s="13" t="inlineStr"/>
       <c r="N83" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 05 de junio de 2026 10:11</t>
         </is>
       </c>
       <c r="O83" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P83" s="13" t="inlineStr"/>
       <c r="Q83" s="13" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R83" s="13" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S83" s="13" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T83" s="13" t="inlineStr"/>
       <c r="U83" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
         </is>
       </c>
       <c r="V83" s="13" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="84" ht="80" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>auto-2032330</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
@@ -12081,22 +12179,22 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -12116,57 +12214,57 @@
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2032330</t>
         </is>
       </c>
       <c r="M84" s="11" t="inlineStr"/>
       <c r="N84" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O84" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P84" s="11" t="inlineStr"/>
       <c r="Q84" s="11" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R84" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S84" s="11" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="85" ht="80" customHeight="1">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B85" s="13" t="n">
@@ -12184,12 +12282,12 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
@@ -12199,7 +12297,7 @@
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I85" s="13" t="inlineStr">
@@ -12214,57 +12312,57 @@
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L85" s="13" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M85" s="13" t="inlineStr"/>
       <c r="N85" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O85" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P85" s="13" t="inlineStr"/>
       <c r="Q85" s="13" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R85" s="13" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S85" s="13" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T85" s="13" t="inlineStr"/>
       <c r="U85" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V85" s="13" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="86" ht="80" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>auto-2032235</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
@@ -12277,17 +12375,17 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr">
@@ -12312,57 +12410,57 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>2032235</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr"/>
       <c r="N86" s="11" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O86" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P86" s="11" t="inlineStr"/>
       <c r="Q86" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R86" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S86" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="87" ht="80" customHeight="1">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>auto-2032255</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
@@ -12375,17 +12473,17 @@
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
@@ -12410,57 +12508,57 @@
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
-          <t>2032255</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M87" s="13" t="inlineStr"/>
       <c r="N87" s="13" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O87" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P87" s="13" t="inlineStr"/>
       <c r="Q87" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R87" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S87" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T87" s="13" t="inlineStr"/>
       <c r="U87" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V87" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="88" ht="80" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>auto-2032354</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
@@ -12473,17 +12571,17 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
@@ -12493,7 +12591,7 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -12503,54 +12601,62 @@
       </c>
       <c r="J88" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2032354</t>
         </is>
       </c>
       <c r="M88" s="11" t="inlineStr"/>
-      <c r="N88" s="11" t="inlineStr"/>
-      <c r="O88" s="11" t="inlineStr"/>
+      <c r="N88" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:</t>
+        </is>
+      </c>
+      <c r="O88" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P88" s="11" t="inlineStr"/>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S88" s="11" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="89" ht="80" customHeight="1">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>auto-2032355</t>
         </is>
       </c>
       <c r="B89" s="13" t="n">
@@ -12563,17 +12669,17 @@
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
@@ -12598,57 +12704,57 @@
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2032355</t>
         </is>
       </c>
       <c r="M89" s="13" t="inlineStr"/>
       <c r="N89" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O89" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P89" s="13" t="inlineStr"/>
       <c r="Q89" s="13" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R89" s="13" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S89" s="13" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T89" s="13" t="inlineStr"/>
       <c r="U89" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
         </is>
       </c>
       <c r="V89" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="90" ht="80" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>auto-2032235</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
@@ -12671,7 +12777,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -12681,7 +12787,7 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I90" s="11" t="inlineStr">
@@ -12691,62 +12797,62 @@
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2032235</t>
         </is>
       </c>
       <c r="M90" s="11" t="inlineStr"/>
       <c r="N90" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>viernes 05 de junio de 2026 10:11 h</t>
         </is>
       </c>
       <c r="O90" s="11" t="inlineStr">
         <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P90" s="11" t="inlineStr"/>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S90" s="11" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="91" ht="80" customHeight="1">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>auto-2032255</t>
         </is>
       </c>
       <c r="B91" s="13" t="n">
@@ -12764,12 +12870,12 @@
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
@@ -12789,62 +12895,62 @@
       </c>
       <c r="J91" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
         </is>
       </c>
       <c r="L91" s="13" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2032255</t>
         </is>
       </c>
       <c r="M91" s="13" t="inlineStr"/>
       <c r="N91" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O91" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P91" s="13" t="inlineStr"/>
       <c r="Q91" s="13" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R91" s="13" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S91" s="13" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T91" s="13" t="inlineStr"/>
       <c r="U91" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
         </is>
       </c>
       <c r="V91" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="92" ht="80" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
@@ -12862,12 +12968,12 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -12877,7 +12983,7 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I92" s="11" t="inlineStr">
@@ -12887,62 +12993,54 @@
       </c>
       <c r="J92" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M92" s="11" t="inlineStr"/>
-      <c r="N92" s="11" t="inlineStr">
-        <is>
-          <t>2024-2025</t>
-        </is>
-      </c>
-      <c r="O92" s="11" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N92" s="11" t="inlineStr"/>
+      <c r="O92" s="11" t="inlineStr"/>
       <c r="P92" s="11" t="inlineStr"/>
       <c r="Q92" s="11" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R92" s="11" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S92" s="11" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="93" ht="80" customHeight="1">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B93" s="13" t="n">
@@ -12960,12 +13058,12 @@
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -12975,7 +13073,7 @@
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I93" s="13" t="inlineStr">
@@ -12990,57 +13088,57 @@
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L93" s="13" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M93" s="13" t="inlineStr"/>
       <c r="N93" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O93" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P93" s="13" t="inlineStr"/>
       <c r="Q93" s="13" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R93" s="13" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S93" s="13" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T93" s="13" t="inlineStr"/>
       <c r="U93" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V93" s="13" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="94" ht="80" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B94" s="11" t="n">
@@ -13058,12 +13156,12 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G94" s="11" t="inlineStr">
@@ -13083,62 +13181,62 @@
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L94" s="11" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O94" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P94" s="11" t="inlineStr"/>
       <c r="Q94" s="11" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R94" s="11" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S94" s="11" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T94" s="11" t="inlineStr"/>
       <c r="U94" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V94" s="11" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="95" ht="80" customHeight="1">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>auto-2032124</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B95" s="13" t="n">
@@ -13156,12 +13254,12 @@
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -13181,62 +13279,62 @@
       </c>
       <c r="J95" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
-          <t>2032124</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M95" s="13" t="inlineStr"/>
       <c r="N95" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O95" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R95" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S95" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T95" s="13" t="inlineStr"/>
       <c r="U95" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V95" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="96" ht="80" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
@@ -13254,12 +13352,12 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
@@ -13269,7 +13367,7 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
@@ -13279,54 +13377,62 @@
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M96" s="11" t="inlineStr"/>
-      <c r="N96" s="11" t="inlineStr"/>
-      <c r="O96" s="11" t="inlineStr"/>
+      <c r="N96" s="11" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="O96" s="11" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P96" s="11" t="inlineStr"/>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R96" s="11" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S96" s="11" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T96" s="11" t="inlineStr"/>
       <c r="U96" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V96" s="11" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="97" ht="80" customHeight="1">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
@@ -13344,12 +13450,12 @@
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
@@ -13359,7 +13465,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
@@ -13369,62 +13475,62 @@
       </c>
       <c r="J97" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M97" s="13" t="inlineStr"/>
       <c r="N97" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O97" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="13" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R97" s="13" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S97" s="13" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T97" s="13" t="inlineStr"/>
       <c r="U97" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V97" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="98" ht="80" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
@@ -13442,12 +13548,12 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -13457,7 +13563,7 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
@@ -13472,57 +13578,57 @@
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L98" s="11" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M98" s="11" t="inlineStr"/>
       <c r="N98" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O98" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P98" s="11" t="inlineStr"/>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R98" s="11" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S98" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T98" s="11" t="inlineStr"/>
       <c r="U98" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V98" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="99" ht="80" customHeight="1">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B99" s="13" t="n">
@@ -13540,22 +13646,22 @@
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I99" s="13" t="inlineStr">
@@ -13565,58 +13671,62 @@
       </c>
       <c r="J99" s="13" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M99" s="13" t="inlineStr"/>
       <c r="N99" s="13" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O99" s="13" t="inlineStr"/>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O99" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R99" s="13" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S99" s="13" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T99" s="13" t="inlineStr"/>
       <c r="U99" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V99" s="13" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="100" ht="80" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
@@ -13634,12 +13744,12 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
@@ -13649,7 +13759,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -13659,62 +13769,54 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M100" s="11" t="inlineStr"/>
-      <c r="N100" s="11" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O100" s="11" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N100" s="11" t="inlineStr"/>
+      <c r="O100" s="11" t="inlineStr"/>
       <c r="P100" s="11" t="inlineStr"/>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R100" s="11" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S100" s="11" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T100" s="11" t="inlineStr"/>
       <c r="U100" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V100" s="11" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="101" ht="80" customHeight="1">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B101" s="13" t="n">
@@ -13732,17 +13834,17 @@
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -13757,58 +13859,62 @@
       </c>
       <c r="J101" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M101" s="13" t="inlineStr"/>
-      <c r="N101" s="13" t="inlineStr"/>
+      <c r="N101" s="13" t="inlineStr">
+        <is>
+          <t>Novena Época</t>
+        </is>
+      </c>
       <c r="O101" s="13" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R101" s="13" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S101" s="13" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T101" s="13" t="inlineStr"/>
       <c r="U101" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V101" s="13" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="102" ht="80" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
@@ -13826,22 +13932,22 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -13856,49 +13962,57 @@
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M102" s="11" t="inlineStr"/>
-      <c r="N102" s="11" t="inlineStr"/>
-      <c r="O102" s="11" t="inlineStr"/>
+      <c r="N102" s="11" t="inlineStr">
+        <is>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O102" s="11" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P102" s="11" t="inlineStr"/>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R102" s="11" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S102" s="11" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>posesión derivada · concepto de propietario · interversión</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="103" ht="80" customHeight="1">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>con-asa-001</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B103" s="13" t="n">
@@ -13911,22 +14025,22 @@
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Asambleas — convocatoria y validez</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
@@ -13941,54 +14055,58 @@
       </c>
       <c r="J103" s="13" t="inlineStr">
         <is>
-          <t>Federal — interpreta LPCI CDMX</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L103" s="13" t="inlineStr">
         <is>
-          <t>Art. 32 LPCI CDMX</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M103" s="13" t="inlineStr"/>
-      <c r="N103" s="13" t="inlineStr"/>
+      <c r="N103" s="13" t="inlineStr">
+        <is>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
       <c r="O103" s="13" t="inlineStr"/>
       <c r="P103" s="13" t="inlineStr"/>
       <c r="Q103" s="13" t="inlineStr">
         <is>
-          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R103" s="13" t="inlineStr">
         <is>
-          <t>Defensa frecuente de minorías condominales.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S103" s="13" t="inlineStr">
         <is>
-          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T103" s="13" t="inlineStr"/>
       <c r="U103" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V103" s="13" t="inlineStr">
         <is>
-          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="104" ht="80" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>amp-cui-001</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
@@ -14001,17 +14119,17 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Reconocimiento e interés legítimo</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -14036,57 +14154,57 @@
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>2032085</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M104" s="11" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O104" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P104" s="11" t="inlineStr"/>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R104" s="11" t="inlineStr">
         <is>
-          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S104" s="11" t="inlineStr">
         <is>
-          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V104" s="11" t="inlineStr">
         <is>
-          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="105" ht="80" customHeight="1">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>amp-cui-002</t>
+          <t>auto-2032319</t>
         </is>
       </c>
       <c r="B105" s="13" t="n">
@@ -14099,17 +14217,17 @@
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Interés legítimo para combatir omisiones legislativas</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -14134,57 +14252,57 @@
       </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
+          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
         </is>
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>2032086</t>
+          <t>2032319</t>
         </is>
       </c>
       <c r="M105" s="13" t="inlineStr"/>
       <c r="N105" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O105" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P105" s="13" t="inlineStr"/>
       <c r="Q105" s="13" t="inlineStr">
         <is>
-          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R105" s="13" t="inlineStr">
         <is>
-          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S105" s="13" t="inlineStr">
         <is>
-          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T105" s="13" t="inlineStr"/>
       <c r="U105" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
         </is>
       </c>
       <c r="V105" s="13" t="inlineStr">
         <is>
-          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
+          <t>Usucapión / Prescripción positiva · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="106" ht="80" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>auto-2032154</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
@@ -14197,27 +14315,27 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -14227,62 +14345,58 @@
       </c>
       <c r="J106" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>2032154</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M106" s="11" t="inlineStr"/>
-      <c r="N106" s="11" t="inlineStr">
-        <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
-        </is>
-      </c>
+      <c r="N106" s="11" t="inlineStr"/>
       <c r="O106" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
         </is>
       </c>
       <c r="P106" s="11" t="inlineStr"/>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R106" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S106" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>pericial · topografía · identidad del bien</t>
         </is>
       </c>
     </row>
     <row r="107" ht="80" customHeight="1">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>auto-2032184</t>
+          <t>civ-usu-005</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
@@ -14295,27 +14409,27 @@
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Posesión derivada vs. originaria</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -14330,57 +14444,49 @@
       </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>2032184</t>
+          <t>2030499</t>
         </is>
       </c>
       <c r="M107" s="13" t="inlineStr"/>
-      <c r="N107" s="13" t="inlineStr">
-        <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
-        </is>
-      </c>
-      <c r="O107" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+      <c r="N107" s="13" t="inlineStr"/>
+      <c r="O107" s="13" t="inlineStr"/>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
         </is>
       </c>
       <c r="R107" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
         </is>
       </c>
       <c r="S107" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
         </is>
       </c>
       <c r="T107" s="13" t="inlineStr"/>
       <c r="U107" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
       <c r="V107" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
     <row r="108" ht="80" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>auto-2032279</t>
+          <t>con-asa-001</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
@@ -14393,17 +14499,17 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Asambleas — convocatoria y validez</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
@@ -14413,7 +14519,7 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -14423,62 +14529,54 @@
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta LPCI CDMX</t>
         </is>
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
+          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>2032279</t>
+          <t>Art. 32 LPCI CDMX</t>
         </is>
       </c>
       <c r="M108" s="11" t="inlineStr"/>
-      <c r="N108" s="11" t="inlineStr">
-        <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
-        </is>
-      </c>
-      <c r="O108" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+      <c r="N108" s="11" t="inlineStr"/>
+      <c r="O108" s="11" t="inlineStr"/>
       <c r="P108" s="11" t="inlineStr"/>
       <c r="Q108" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
         </is>
       </c>
       <c r="R108" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa frecuente de minorías condominales.</t>
         </is>
       </c>
       <c r="S108" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
         </is>
       </c>
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
         </is>
       </c>
     </row>
     <row r="109" ht="80" customHeight="1">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>amp-cui-001</t>
         </is>
       </c>
       <c r="B109" s="13" t="n">
@@ -14496,12 +14594,12 @@
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Reconocimiento e interés legítimo</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
@@ -14526,12 +14624,12 @@
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032085</t>
         </is>
       </c>
       <c r="M109" s="13" t="inlineStr"/>
@@ -14548,35 +14646,35 @@
       <c r="P109" s="13" t="inlineStr"/>
       <c r="Q109" s="13" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
         </is>
       </c>
       <c r="R109" s="13" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
         </is>
       </c>
       <c r="S109" s="13" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
         </is>
       </c>
       <c r="T109" s="13" t="inlineStr"/>
       <c r="U109" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
         </is>
       </c>
       <c r="V109" s="13" t="inlineStr">
         <is>
-          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
+          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
         </is>
       </c>
     </row>
     <row r="110" ht="80" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-002</t>
+          <t>amp-cui-002</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
@@ -14589,22 +14687,22 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>69-B — recurso de revocación y buzón tributario</t>
+          <t>Interés legítimo para combatir omisiones legislativas</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -14624,57 +14722,57 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
+          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
         </is>
       </c>
       <c r="L110" s="11" t="inlineStr">
         <is>
-          <t>2031931</t>
+          <t>2032086</t>
         </is>
       </c>
       <c r="M110" s="11" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O110" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P110" s="11" t="inlineStr"/>
       <c r="Q110" s="11" t="inlineStr">
         <is>
-          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
+          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
         </is>
       </c>
       <c r="R110" s="11" t="inlineStr">
         <is>
-          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
+          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
         </is>
       </c>
       <c r="S110" s="11" t="inlineStr">
         <is>
-          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
+          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
         </is>
       </c>
       <c r="T110" s="11" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
         </is>
       </c>
       <c r="V110" s="11" t="inlineStr">
         <is>
-          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
+          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
         </is>
       </c>
     </row>
     <row r="111" ht="80" customHeight="1">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-003</t>
+          <t>auto-2032312</t>
         </is>
       </c>
       <c r="B111" s="13" t="n">
@@ -14687,17 +14785,17 @@
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>Materialidad — fundar y motivar</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
@@ -14722,57 +14820,57 @@
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>2032312</t>
         </is>
       </c>
       <c r="M111" s="13" t="inlineStr"/>
       <c r="N111" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O111" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P111" s="13" t="inlineStr"/>
       <c r="Q111" s="13" t="inlineStr">
         <is>
-          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R111" s="13" t="inlineStr">
         <is>
-          <t>Defensa fuerte para contribuyentes auditados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S111" s="13" t="inlineStr">
         <is>
-          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T111" s="13" t="inlineStr"/>
       <c r="U111" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
         </is>
       </c>
       <c r="V111" s="13" t="inlineStr">
         <is>
-          <t>69-B · materialidad · fundamentación · 12a Época</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="112" ht="80" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-004</t>
+          <t>auto-2032313</t>
         </is>
       </c>
       <c r="B112" s="11" t="n">
@@ -14785,17 +14883,17 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Nulidad EFOS — efectos sobre proveedor</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
@@ -14820,57 +14918,57 @@
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L112" s="11" t="inlineStr">
         <is>
-          <t>2031349</t>
+          <t>2032313</t>
         </is>
       </c>
       <c r="M112" s="11" t="inlineStr"/>
       <c r="N112" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O112" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P112" s="11" t="inlineStr"/>
       <c r="Q112" s="11" t="inlineStr">
         <is>
-          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R112" s="11" t="inlineStr">
         <is>
-          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S112" s="11" t="inlineStr">
         <is>
-          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T112" s="11" t="inlineStr"/>
       <c r="U112" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
         </is>
       </c>
       <c r="V112" s="11" t="inlineStr">
         <is>
-          <t>EFOS · nulidad · deducciones · 12a Época</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="113" ht="80" customHeight="1">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>auto-2032254</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B113" s="13" t="n">
@@ -14883,12 +14981,12 @@
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F113" s="13" t="inlineStr">
@@ -14918,18 +15016,18 @@
       </c>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
-          <t>2032254</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M113" s="13" t="inlineStr"/>
       <c r="N113" s="13" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O113" s="13" t="inlineStr">
@@ -14956,19 +15054,19 @@
       <c r="T113" s="13" t="inlineStr"/>
       <c r="U113" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V113" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado · actualización automática</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="114" ht="80" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>lab-des-002</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B114" s="11" t="n">
@@ -14981,17 +15079,17 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Carga patrón cuando alega rescisión justificada posterior</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
@@ -15001,7 +15099,7 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -15016,57 +15114,57 @@
       </c>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L114" s="11" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M114" s="11" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O114" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P114" s="11" t="inlineStr"/>
       <c r="Q114" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R114" s="11" t="inlineStr">
         <is>
-          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S114" s="11" t="inlineStr">
         <is>
-          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T114" s="11" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
         </is>
       </c>
       <c r="V114" s="11" t="inlineStr">
         <is>
-          <t>despido · rescisión · carga probatoria patrón</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="115" ht="80" customHeight="1">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>lab-ren-001</t>
+          <t>auto-2032279</t>
         </is>
       </c>
       <c r="B115" s="13" t="n">
@@ -15079,17 +15177,17 @@
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>Hora de terminación — carga del patrón</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
@@ -15099,7 +15197,7 @@
       </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I115" s="13" t="inlineStr">
@@ -15114,57 +15212,57 @@
       </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
+          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
         </is>
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
-          <t>2028640</t>
+          <t>2032279</t>
         </is>
       </c>
       <c r="M115" s="13" t="inlineStr"/>
       <c r="N115" s="13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O115" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P115" s="13" t="inlineStr"/>
       <c r="Q115" s="13" t="inlineStr">
         <is>
-          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R115" s="13" t="inlineStr">
         <is>
-          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S115" s="13" t="inlineStr">
         <is>
-          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T115" s="13" t="inlineStr"/>
       <c r="U115" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
         </is>
       </c>
       <c r="V115" s="13" t="inlineStr">
         <is>
-          <t>renuncia · hora despido · carga probatoria</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="116" ht="80" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>lab-ren-002</t>
+          <t>auto-2032302</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
@@ -15177,17 +15275,17 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
@@ -15197,7 +15295,7 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -15212,57 +15310,57 @@
       </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
         </is>
       </c>
       <c r="L116" s="11" t="inlineStr">
         <is>
-          <t>2027058</t>
+          <t>2032302</t>
         </is>
       </c>
       <c r="M116" s="11" t="inlineStr"/>
       <c r="N116" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O116" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P116" s="11" t="inlineStr"/>
       <c r="Q116" s="11" t="inlineStr">
         <is>
-          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R116" s="11" t="inlineStr">
         <is>
-          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S116" s="11" t="inlineStr">
         <is>
-          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>renuncia · jubilación · veracidad · carga reforzada</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="117" ht="80" customHeight="1">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>sen-020</t>
+          <t>auto-2032309</t>
         </is>
       </c>
       <c r="B117" s="13" t="n">
@@ -15275,27 +15373,27 @@
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Costas en juicio mercantil — tasación</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I117" s="13" t="inlineStr">
@@ -15305,58 +15403,62 @@
       </c>
       <c r="J117" s="13" t="inlineStr">
         <is>
-          <t>Primer y Segundo Circuito</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
+          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
         </is>
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>Línea de Colegiados — múltiples</t>
+          <t>2032309</t>
         </is>
       </c>
       <c r="M117" s="13" t="inlineStr"/>
       <c r="N117" s="13" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O117" s="13" t="inlineStr"/>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O117" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P117" s="13" t="inlineStr"/>
       <c r="Q117" s="13" t="inlineStr">
         <is>
-          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R117" s="13" t="inlineStr">
         <is>
-          <t>Marco práctico para pretensión y oposición a costas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S117" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T117" s="13" t="inlineStr"/>
       <c r="U117" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
         </is>
       </c>
       <c r="V117" s="13" t="inlineStr">
         <is>
-          <t>costas · tasación · arancel · mercantil</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="118" ht="80" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>auto-2032198</t>
+          <t>auto-2032326</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
@@ -15369,12 +15471,12 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -15404,18 +15506,18 @@
       </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L118" s="11" t="inlineStr">
         <is>
-          <t>2032198</t>
+          <t>2032326</t>
         </is>
       </c>
       <c r="M118" s="11" t="inlineStr"/>
       <c r="N118" s="11" t="inlineStr">
         <is>
-          <t>viernes 29 de mayo de 2026 10:34 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O118" s="11" t="inlineStr">
@@ -15442,19 +15544,19 @@
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="119" ht="80" customHeight="1">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>auto-2032274</t>
+          <t>auto-2032338</t>
         </is>
       </c>
       <c r="B119" s="13" t="n">
@@ -15467,12 +15569,12 @@
       </c>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F119" s="13" t="inlineStr">
@@ -15502,18 +15604,18 @@
       </c>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
+          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
         </is>
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
-          <t>2032274</t>
+          <t>2032338</t>
         </is>
       </c>
       <c r="M119" s="13" t="inlineStr"/>
       <c r="N119" s="13" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O119" s="13" t="inlineStr">
@@ -15540,19 +15642,19 @@
       <c r="T119" s="13" t="inlineStr"/>
       <c r="U119" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
         </is>
       </c>
       <c r="V119" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="120" ht="80" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>auto-2032347</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
@@ -15565,27 +15667,27 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
@@ -15600,57 +15702,57 @@
       </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
         </is>
       </c>
       <c r="L120" s="11" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2032347</t>
         </is>
       </c>
       <c r="M120" s="11" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O120" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P120" s="11" t="inlineStr"/>
       <c r="Q120" s="11" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R120" s="11" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S120" s="11" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="121" ht="80" customHeight="1">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>amp-gen-001</t>
         </is>
       </c>
       <c r="B121" s="13" t="n">
@@ -15663,17 +15765,17 @@
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Perspectiva de género interseccional</t>
         </is>
       </c>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
@@ -15698,18 +15800,18 @@
       </c>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
         </is>
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2032067</t>
         </is>
       </c>
       <c r="M121" s="13" t="inlineStr"/>
       <c r="N121" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O121" s="13" t="inlineStr">
@@ -15720,35 +15822,35 @@
       <c r="P121" s="13" t="inlineStr"/>
       <c r="Q121" s="13" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
         </is>
       </c>
       <c r="R121" s="13" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
         </is>
       </c>
       <c r="S121" s="13" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
         </is>
       </c>
       <c r="T121" s="13" t="inlineStr"/>
       <c r="U121" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
       <c r="V121" s="13" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="122" ht="80" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>fis-cfd-002</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
@@ -15761,27 +15863,27 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>69-B — recurso de revocación y buzón tributario</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
@@ -15796,18 +15898,18 @@
       </c>
       <c r="K122" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
         </is>
       </c>
       <c r="L122" s="11" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2031931</t>
         </is>
       </c>
       <c r="M122" s="11" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O122" s="11" t="inlineStr">
@@ -15818,35 +15920,35 @@
       <c r="P122" s="11" t="inlineStr"/>
       <c r="Q122" s="11" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
         </is>
       </c>
       <c r="R122" s="11" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
         </is>
       </c>
       <c r="S122" s="11" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
         </is>
       </c>
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
         </is>
       </c>
     </row>
     <row r="123" ht="80" customHeight="1">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>fis-cfd-003</t>
         </is>
       </c>
       <c r="B123" s="13" t="n">
@@ -15859,17 +15961,17 @@
       </c>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Materialidad — fundar y motivar</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
@@ -15879,7 +15981,7 @@
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I123" s="13" t="inlineStr">
@@ -15894,18 +15996,18 @@
       </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M123" s="13" t="inlineStr"/>
       <c r="N123" s="13" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O123" s="13" t="inlineStr">
@@ -15916,35 +16018,35 @@
       <c r="P123" s="13" t="inlineStr"/>
       <c r="Q123" s="13" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
         </is>
       </c>
       <c r="R123" s="13" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Defensa fuerte para contribuyentes auditados.</t>
         </is>
       </c>
       <c r="S123" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
         </is>
       </c>
       <c r="T123" s="13" t="inlineStr"/>
       <c r="U123" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V123" s="13" t="inlineStr">
         <is>
-          <t>pagaré · pagarés seriados · lugar de pago</t>
+          <t>69-B · materialidad · fundamentación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="124" ht="80" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>fis-cfd-004</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
@@ -15957,27 +16059,27 @@
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Nulidad EFOS — efectos sobre proveedor</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -15992,18 +16094,18 @@
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
         </is>
       </c>
       <c r="L124" s="11" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2031349</t>
         </is>
       </c>
       <c r="M124" s="11" t="inlineStr"/>
       <c r="N124" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O124" s="11" t="inlineStr">
@@ -16014,35 +16116,35 @@
       <c r="P124" s="11" t="inlineStr"/>
       <c r="Q124" s="11" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
         </is>
       </c>
       <c r="R124" s="11" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
         </is>
       </c>
       <c r="S124" s="11" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
         </is>
       </c>
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>EFOS · nulidad · deducciones · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="125" ht="80" customHeight="1">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>auto-2032254</t>
         </is>
       </c>
       <c r="B125" s="13" t="n">
@@ -16055,17 +16157,17 @@
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
@@ -16075,7 +16177,7 @@
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -16090,57 +16192,57 @@
       </c>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
         </is>
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2032254</t>
         </is>
       </c>
       <c r="M125" s="13" t="inlineStr"/>
       <c r="N125" s="13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O125" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P125" s="13" t="inlineStr"/>
       <c r="Q125" s="13" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R125" s="13" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S125" s="13" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T125" s="13" t="inlineStr"/>
       <c r="U125" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
         </is>
       </c>
       <c r="V125" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>Despido injustificado · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="126" ht="80" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>lab-des-002</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
@@ -16153,17 +16255,17 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Carga patrón cuando alega rescisión justificada posterior</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr">
@@ -16173,7 +16275,7 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -16188,57 +16290,57 @@
       </c>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
         </is>
       </c>
       <c r="L126" s="11" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M126" s="11" t="inlineStr"/>
       <c r="N126" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O126" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P126" s="11" t="inlineStr"/>
       <c r="Q126" s="11" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
         </is>
       </c>
       <c r="R126" s="11" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
         </is>
       </c>
       <c r="S126" s="11" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
         </is>
       </c>
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>despido · rescisión · carga probatoria patrón</t>
         </is>
       </c>
     </row>
     <row r="127" ht="80" customHeight="1">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>lab-ren-001</t>
         </is>
       </c>
       <c r="B127" s="13" t="n">
@@ -16251,17 +16353,17 @@
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Hora de terminación — carga del patrón</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
@@ -16271,7 +16373,7 @@
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I127" s="13" t="inlineStr">
@@ -16286,57 +16388,57 @@
       </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
         </is>
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2028640</t>
         </is>
       </c>
       <c r="M127" s="13" t="inlineStr"/>
       <c r="N127" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O127" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P127" s="13" t="inlineStr"/>
       <c r="Q127" s="13" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
         </is>
       </c>
       <c r="R127" s="13" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
         </is>
       </c>
       <c r="S127" s="13" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
         </is>
       </c>
       <c r="T127" s="13" t="inlineStr"/>
       <c r="U127" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
         </is>
       </c>
       <c r="V127" s="13" t="inlineStr">
         <is>
-          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
+          <t>renuncia · hora despido · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="128" ht="80" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>auto-2032300</t>
+          <t>lab-ren-002</t>
         </is>
       </c>
       <c r="B128" s="11" t="n">
@@ -16349,17 +16451,17 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr">
@@ -16369,7 +16471,7 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -16384,57 +16486,57 @@
       </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
+          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
         </is>
       </c>
       <c r="L128" s="11" t="inlineStr">
         <is>
-          <t>2032300</t>
+          <t>2027058</t>
         </is>
       </c>
       <c r="M128" s="11" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O128" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P128" s="11" t="inlineStr"/>
       <c r="Q128" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
         </is>
       </c>
       <c r="R128" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
         </is>
       </c>
       <c r="S128" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
         </is>
       </c>
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>renuncia · jubilación · veracidad · carga reforzada</t>
         </is>
       </c>
     </row>
     <row r="129" ht="80" customHeight="1">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>auto-2032301</t>
+          <t>sen-020</t>
         </is>
       </c>
       <c r="B129" s="13" t="n">
@@ -16447,27 +16549,27 @@
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Costas en juicio mercantil — tasación</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I129" s="13" t="inlineStr">
@@ -16477,62 +16579,58 @@
       </c>
       <c r="J129" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer y Segundo Circuito</t>
         </is>
       </c>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
+          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
         </is>
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
-          <t>2032301</t>
+          <t>Línea de Colegiados — múltiples</t>
         </is>
       </c>
       <c r="M129" s="13" t="inlineStr"/>
       <c r="N129" s="13" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
-        </is>
-      </c>
-      <c r="O129" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O129" s="13" t="inlineStr"/>
       <c r="P129" s="13" t="inlineStr"/>
       <c r="Q129" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
         </is>
       </c>
       <c r="R129" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Marco práctico para pretensión y oposición a costas.</t>
         </is>
       </c>
       <c r="S129" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
         </is>
       </c>
       <c r="T129" s="13" t="inlineStr"/>
       <c r="U129" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
         </is>
       </c>
       <c r="V129" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>costas · tasación · arancel · mercantil</t>
         </is>
       </c>
     </row>
     <row r="130" ht="80" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>auto-2032304</t>
+          <t>auto-2032198</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
@@ -16545,12 +16643,12 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
@@ -16580,18 +16678,18 @@
       </c>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
+          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
         </is>
       </c>
       <c r="L130" s="11" t="inlineStr">
         <is>
-          <t>2032304</t>
+          <t>2032198</t>
         </is>
       </c>
       <c r="M130" s="11" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O130" s="11" t="inlineStr">
@@ -16618,17 +16716,1291 @@
       <c r="T130" s="11" t="inlineStr"/>
       <c r="U130" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
+        </is>
+      </c>
+      <c r="V130" s="11" t="inlineStr">
+        <is>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="80" customHeight="1">
+      <c r="A131" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032274</t>
+        </is>
+      </c>
+      <c r="B131" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>Juicio ejecutivo mercantil</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J131" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K131" s="14" t="inlineStr">
+        <is>
+          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
+        </is>
+      </c>
+      <c r="L131" s="13" t="inlineStr">
+        <is>
+          <t>2032274</t>
+        </is>
+      </c>
+      <c r="M131" s="13" t="inlineStr"/>
+      <c r="N131" s="13" t="inlineStr">
+        <is>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
+        </is>
+      </c>
+      <c r="O131" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P131" s="13" t="inlineStr"/>
+      <c r="Q131" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R131" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S131" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T131" s="13" t="inlineStr"/>
+      <c r="U131" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
+        </is>
+      </c>
+      <c r="V131" s="13" t="inlineStr">
+        <is>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="80" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>mer-eje-002</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>Juicio ejecutivo mercantil</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
+        </is>
+      </c>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>Undécima Época</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K132" s="12" t="inlineStr">
+        <is>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+        </is>
+      </c>
+      <c r="L132" s="11" t="inlineStr">
+        <is>
+          <t>2025924</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="inlineStr"/>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P132" s="11" t="inlineStr"/>
+      <c r="Q132" s="11" t="inlineStr">
+        <is>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+        </is>
+      </c>
+      <c r="R132" s="11" t="inlineStr">
+        <is>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+        </is>
+      </c>
+      <c r="S132" s="11" t="inlineStr">
+        <is>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+        </is>
+      </c>
+      <c r="T132" s="11" t="inlineStr"/>
+      <c r="U132" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+        </is>
+      </c>
+      <c r="V132" s="11" t="inlineStr">
+        <is>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="80" customHeight="1">
+      <c r="A133" s="13" t="inlineStr">
+        <is>
+          <t>mer-eje-003</t>
+        </is>
+      </c>
+      <c r="B133" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C133" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>Juicio ejecutivo mercantil</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr">
+        <is>
+          <t>Mora — fecha de actualización</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J133" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K133" s="14" t="inlineStr">
+        <is>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+        </is>
+      </c>
+      <c r="L133" s="13" t="inlineStr">
+        <is>
+          <t>2031591</t>
+        </is>
+      </c>
+      <c r="M133" s="13" t="inlineStr"/>
+      <c r="N133" s="13" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="O133" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P133" s="13" t="inlineStr"/>
+      <c r="Q133" s="13" t="inlineStr">
+        <is>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+        </is>
+      </c>
+      <c r="R133" s="13" t="inlineStr">
+        <is>
+          <t>Define desde cuándo corren intereses moratorios.</t>
+        </is>
+      </c>
+      <c r="S133" s="13" t="inlineStr">
+        <is>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+        </is>
+      </c>
+      <c r="T133" s="13" t="inlineStr"/>
+      <c r="U133" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+        </is>
+      </c>
+      <c r="V133" s="13" t="inlineStr">
+        <is>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="80" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>mer-pag-002</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>Títulos de crédito — pagaré</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>Acción causal — pagaré como prueba del contrato</t>
+        </is>
+      </c>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>Undécima Época</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K134" s="12" t="inlineStr">
+        <is>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+        </is>
+      </c>
+      <c r="L134" s="11" t="inlineStr">
+        <is>
+          <t>2024056</t>
+        </is>
+      </c>
+      <c r="M134" s="11" t="inlineStr"/>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P134" s="11" t="inlineStr"/>
+      <c r="Q134" s="11" t="inlineStr">
+        <is>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+        </is>
+      </c>
+      <c r="R134" s="11" t="inlineStr">
+        <is>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+        </is>
+      </c>
+      <c r="S134" s="11" t="inlineStr">
+        <is>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+        </is>
+      </c>
+      <c r="T134" s="11" t="inlineStr"/>
+      <c r="U134" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+        </is>
+      </c>
+      <c r="V134" s="11" t="inlineStr">
+        <is>
+          <t>pagaré · acción causal · ordinario mercantil</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="80" customHeight="1">
+      <c r="A135" s="13" t="inlineStr">
+        <is>
+          <t>mer-pag-003</t>
+        </is>
+      </c>
+      <c r="B135" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D135" s="13" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>Títulos de crédito — pagaré</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="inlineStr">
+        <is>
+          <t>Pagarés seriados — lugar de pago</t>
+        </is>
+      </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J135" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K135" s="14" t="inlineStr">
+        <is>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+        </is>
+      </c>
+      <c r="L135" s="13" t="inlineStr">
+        <is>
+          <t>2019464</t>
+        </is>
+      </c>
+      <c r="M135" s="13" t="inlineStr"/>
+      <c r="N135" s="13" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="O135" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P135" s="13" t="inlineStr"/>
+      <c r="Q135" s="13" t="inlineStr">
+        <is>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+        </is>
+      </c>
+      <c r="R135" s="13" t="inlineStr">
+        <is>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+        </is>
+      </c>
+      <c r="S135" s="13" t="inlineStr">
+        <is>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+        </is>
+      </c>
+      <c r="T135" s="13" t="inlineStr"/>
+      <c r="U135" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+        </is>
+      </c>
+      <c r="V135" s="13" t="inlineStr">
+        <is>
+          <t>pagaré · pagarés seriados · lugar de pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="80" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>pen-cad-002</t>
+        </is>
+      </c>
+      <c r="B136" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>Cadena de custodia</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+        </is>
+      </c>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>Undécima Época</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J136" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K136" s="12" t="inlineStr">
+        <is>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+        </is>
+      </c>
+      <c r="L136" s="11" t="inlineStr">
+        <is>
+          <t>2027962</t>
+        </is>
+      </c>
+      <c r="M136" s="11" t="inlineStr"/>
+      <c r="N136" s="11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P136" s="11" t="inlineStr"/>
+      <c r="Q136" s="11" t="inlineStr">
+        <is>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+        </is>
+      </c>
+      <c r="R136" s="11" t="inlineStr">
+        <is>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+        </is>
+      </c>
+      <c r="S136" s="11" t="inlineStr">
+        <is>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+        </is>
+      </c>
+      <c r="T136" s="11" t="inlineStr"/>
+      <c r="U136" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+        </is>
+      </c>
+      <c r="V136" s="11" t="inlineStr">
+        <is>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="80" customHeight="1">
+      <c r="A137" s="13" t="inlineStr">
+        <is>
+          <t>pen-cad-003</t>
+        </is>
+      </c>
+      <c r="B137" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C137" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>Cadena de custodia</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="inlineStr">
+        <is>
+          <t>Transgresión no torna ilícita la prueba</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J137" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K137" s="14" t="inlineStr">
+        <is>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+        </is>
+      </c>
+      <c r="L137" s="13" t="inlineStr">
+        <is>
+          <t>2021845</t>
+        </is>
+      </c>
+      <c r="M137" s="13" t="inlineStr"/>
+      <c r="N137" s="13" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="O137" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P137" s="13" t="inlineStr"/>
+      <c r="Q137" s="13" t="inlineStr">
+        <is>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+        </is>
+      </c>
+      <c r="R137" s="13" t="inlineStr">
+        <is>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+        </is>
+      </c>
+      <c r="S137" s="13" t="inlineStr">
+        <is>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+        </is>
+      </c>
+      <c r="T137" s="13" t="inlineStr"/>
+      <c r="U137" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+        </is>
+      </c>
+      <c r="V137" s="13" t="inlineStr">
+        <is>
+          <t>cadena custodia · valor probatorio · exclusión</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="80" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>pen-ppo-001</t>
+        </is>
+      </c>
+      <c r="B138" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
+        </is>
+      </c>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>2032107</t>
+        </is>
+      </c>
+      <c r="M138" s="11" t="inlineStr"/>
+      <c r="N138" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P138" s="11" t="inlineStr"/>
+      <c r="Q138" s="11" t="inlineStr">
+        <is>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+        </is>
+      </c>
+      <c r="R138" s="11" t="inlineStr">
+        <is>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+        </is>
+      </c>
+      <c r="S138" s="11" t="inlineStr">
+        <is>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+        </is>
+      </c>
+      <c r="T138" s="11" t="inlineStr"/>
+      <c r="U138" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+        </is>
+      </c>
+      <c r="V138" s="11" t="inlineStr">
+        <is>
+          <t>PPO · víctima · legitimación · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="80" customHeight="1">
+      <c r="A139" s="13" t="inlineStr">
+        <is>
+          <t>pen-ppo-002</t>
+        </is>
+      </c>
+      <c r="B139" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D139" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>Prisión preventiva oficiosa</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="inlineStr">
+        <is>
+          <t>Cese cuando MP no prueba prolongación</t>
+        </is>
+      </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J139" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K139" s="14" t="inlineStr">
+        <is>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+        </is>
+      </c>
+      <c r="L139" s="13" t="inlineStr">
+        <is>
+          <t>2032108</t>
+        </is>
+      </c>
+      <c r="M139" s="13" t="inlineStr"/>
+      <c r="N139" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O139" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P139" s="13" t="inlineStr"/>
+      <c r="Q139" s="13" t="inlineStr">
+        <is>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+        </is>
+      </c>
+      <c r="R139" s="13" t="inlineStr">
+        <is>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+        </is>
+      </c>
+      <c r="S139" s="13" t="inlineStr">
+        <is>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+        </is>
+      </c>
+      <c r="T139" s="13" t="inlineStr"/>
+      <c r="U139" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
+        </is>
+      </c>
+      <c r="V139" s="13" t="inlineStr">
+        <is>
+          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="80" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032300</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K140" s="12" t="inlineStr">
+        <is>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
+        </is>
+      </c>
+      <c r="L140" s="11" t="inlineStr">
+        <is>
+          <t>2032300</t>
+        </is>
+      </c>
+      <c r="M140" s="11" t="inlineStr"/>
+      <c r="N140" s="11" t="inlineStr">
+        <is>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P140" s="11" t="inlineStr"/>
+      <c r="Q140" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R140" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S140" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T140" s="11" t="inlineStr"/>
+      <c r="U140" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
+        </is>
+      </c>
+      <c r="V140" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="80" customHeight="1">
+      <c r="A141" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032301</t>
+        </is>
+      </c>
+      <c r="B141" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C141" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J141" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K141" s="14" t="inlineStr">
+        <is>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
+        </is>
+      </c>
+      <c r="L141" s="13" t="inlineStr">
+        <is>
+          <t>2032301</t>
+        </is>
+      </c>
+      <c r="M141" s="13" t="inlineStr"/>
+      <c r="N141" s="13" t="inlineStr">
+        <is>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
+        </is>
+      </c>
+      <c r="O141" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P141" s="13" t="inlineStr"/>
+      <c r="Q141" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R141" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S141" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T141" s="13" t="inlineStr"/>
+      <c r="U141" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
+        </is>
+      </c>
+      <c r="V141" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="80" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032304</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J142" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr">
+        <is>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
+        </is>
+      </c>
+      <c r="L142" s="11" t="inlineStr">
+        <is>
+          <t>2032304</t>
+        </is>
+      </c>
+      <c r="M142" s="11" t="inlineStr"/>
+      <c r="N142" s="11" t="inlineStr">
+        <is>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
+        </is>
+      </c>
+      <c r="O142" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P142" s="11" t="inlineStr"/>
+      <c r="Q142" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R142" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S142" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T142" s="11" t="inlineStr"/>
+      <c r="U142" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032304</t>
         </is>
       </c>
-      <c r="V130" s="11" t="inlineStr">
+      <c r="V142" s="11" t="inlineStr">
         <is>
           <t>Reparación del daño · actualización automática</t>
         </is>
       </c>
     </row>
+    <row r="143" ht="80" customHeight="1">
+      <c r="A143" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032335</t>
+        </is>
+      </c>
+      <c r="B143" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C143" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D143" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G143" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J143" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K143" s="14" t="inlineStr">
+        <is>
+          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
+        </is>
+      </c>
+      <c r="L143" s="13" t="inlineStr">
+        <is>
+          <t>2032335</t>
+        </is>
+      </c>
+      <c r="M143" s="13" t="inlineStr"/>
+      <c r="N143" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O143" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P143" s="13" t="inlineStr"/>
+      <c r="Q143" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R143" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S143" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T143" s="13" t="inlineStr"/>
+      <c r="U143" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+        </is>
+      </c>
+      <c r="V143" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V130"/>
+  <autoFilter ref="A1:V143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16639,7 +18011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18403,7 +19775,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>auto-2032177</t>
+          <t>auto-2032353</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -18421,7 +19793,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -18451,18 +19823,18 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>SUSPENSIÓN DE PLANO EN AMPARO INDIRECTO. PROCEDE PARA ORDENAR UNA VALORACIÓN MÉDICA EN EL DOMICILIO DE UNA PERSONA, CUANDO TIENE UNA MOVILIDAD RESTRINGIDA.</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>2032177</t>
+          <t>2032353</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O19" s="13" t="inlineStr">
@@ -18489,19 +19861,19 @@
       <c r="T19" s="13" t="inlineStr"/>
       <c r="U19" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032353</t>
         </is>
       </c>
       <c r="V19" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>auto-2032233</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
@@ -18549,18 +19921,18 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>2032233</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
@@ -18587,17 +19959,213 @@
       <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032233</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>2032233</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr"/>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>viernes 05 de junio de 2026 10:11</t>
+        </is>
+      </c>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="inlineStr"/>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S21" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr"/>
+      <c r="U21" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
         </is>
       </c>
-      <c r="V20" s="11" t="inlineStr">
+      <c r="V21" s="13" t="inlineStr">
         <is>
           <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032330</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>2032330</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr"/>
+      <c r="Q22" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr"/>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V20"/>
+  <autoFilter ref="A1:V22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18608,7 +20176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19409,8 +20977,204 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032354</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Suspensión</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
+        <is>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>2032354</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr"/>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr"/>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S9" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T9" s="13" t="inlineStr"/>
+      <c r="U9" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
+        </is>
+      </c>
+      <c r="V9" s="13" t="inlineStr">
+        <is>
+          <t>Suspensión · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032355</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>2032355</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="inlineStr"/>
+      <c r="Q10" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R10" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="inlineStr"/>
+      <c r="U10" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V8"/>
+  <autoFilter ref="A1:V10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19421,7 +21185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22869,7 +24633,7 @@
     <row r="37" ht="80" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>auto-2032319</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
@@ -22892,17 +24656,17 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -22912,58 +24676,62 @@
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>2032319</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr"/>
-      <c r="N37" s="13" t="inlineStr"/>
+      <c r="N37" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
       <c r="O37" s="13" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P37" s="13" t="inlineStr"/>
       <c r="Q37" s="13" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R37" s="13" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S37" s="13" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T37" s="13" t="inlineStr"/>
       <c r="U37" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
         </is>
       </c>
       <c r="V37" s="13" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>Usucapión / Prescripción positiva · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="38" ht="80" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
@@ -22986,7 +24754,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -22996,7 +24764,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -23006,52 +24774,146 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr"/>
       <c r="N38" s="11" t="inlineStr"/>
-      <c r="O38" s="11" t="inlineStr"/>
+      <c r="O38" s="11" t="inlineStr">
+        <is>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+        </is>
+      </c>
       <c r="P38" s="11" t="inlineStr"/>
       <c r="Q38" s="11" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R38" s="11" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S38" s="11" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>pericial · topografía · identidad del bien</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>civ-usu-005</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Usucapión / Prescripción positiva</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>Posesión derivada vs. originaria</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+        </is>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>2030499</t>
+        </is>
+      </c>
+      <c r="M39" s="13" t="inlineStr"/>
+      <c r="N39" s="13" t="inlineStr"/>
+      <c r="O39" s="13" t="inlineStr"/>
+      <c r="P39" s="13" t="inlineStr"/>
+      <c r="Q39" s="13" t="inlineStr">
+        <is>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+        </is>
+      </c>
+      <c r="R39" s="13" t="inlineStr">
+        <is>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+        </is>
+      </c>
+      <c r="S39" s="13" t="inlineStr">
+        <is>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+        </is>
+      </c>
+      <c r="T39" s="13" t="inlineStr"/>
+      <c r="U39" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
-      <c r="V38" s="11" t="inlineStr">
+      <c r="V39" s="13" t="inlineStr">
         <is>
           <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V38"/>
+  <autoFilter ref="A1:V39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23393,7 +25255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24855,7 +26717,7 @@
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>auto-2032154</t>
+          <t>auto-2032312</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
@@ -24873,7 +26735,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -24903,18 +26765,18 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>2032154</t>
+          <t>2032312</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
@@ -24941,19 +26803,19 @@
       <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
         </is>
       </c>
       <c r="V16" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>auto-2032184</t>
+          <t>auto-2032313</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -24971,7 +26833,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -25001,18 +26863,18 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>2032184</t>
+          <t>2032313</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr"/>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O17" s="13" t="inlineStr">
@@ -25039,19 +26901,19 @@
       <c r="T17" s="13" t="inlineStr"/>
       <c r="U17" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
         </is>
       </c>
       <c r="V17" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>auto-2032279</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
@@ -25099,18 +26961,18 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>2032279</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
@@ -25137,7 +26999,7 @@
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V18" s="11" t="inlineStr">
@@ -25149,7 +27011,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -25167,12 +27029,12 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -25197,55 +27059,741 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr"/>
       <c r="Q19" s="13" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R19" s="13" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S19" s="13" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T19" s="13" t="inlineStr"/>
       <c r="U19" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+        </is>
+      </c>
+      <c r="V19" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032279</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>2032279</t>
+        </is>
+      </c>
+      <c r="M20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr"/>
+      <c r="Q20" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R20" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T20" s="11" t="inlineStr"/>
+      <c r="U20" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032302</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>2032302</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr"/>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
+        </is>
+      </c>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="inlineStr"/>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S21" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T21" s="13" t="inlineStr"/>
+      <c r="U21" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
+        </is>
+      </c>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032309</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>2032309</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr"/>
+      <c r="Q22" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr"/>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032326</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>2032326</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr"/>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="inlineStr"/>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S23" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr"/>
+      <c r="U23" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
+        </is>
+      </c>
+      <c r="V23" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032338</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>2032338</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr"/>
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr"/>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
+        </is>
+      </c>
+      <c r="V24" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032347</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>2032347</t>
+        </is>
+      </c>
+      <c r="M25" s="13" t="inlineStr"/>
+      <c r="N25" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O25" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P25" s="13" t="inlineStr"/>
+      <c r="Q25" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S25" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T25" s="13" t="inlineStr"/>
+      <c r="U25" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>amp-gen-001</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género interseccional</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>2032067</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr"/>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P26" s="11" t="inlineStr"/>
+      <c r="Q26" s="11" t="inlineStr">
+        <is>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+        </is>
+      </c>
+      <c r="R26" s="11" t="inlineStr">
+        <is>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+        </is>
+      </c>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr"/>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
-      <c r="V19" s="13" t="inlineStr">
+      <c r="V26" s="11" t="inlineStr">
         <is>
           <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V19"/>
+  <autoFilter ref="A1:V26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Acervo_Jurisprudencial.xlsx
+++ b/Acervo_Jurisprudencial.xlsx
@@ -20,15 +20,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penal" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Civil — Condominio'!$A$1:$V$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fiscal'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Laboral'!$A$1:$V$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Penal'!$A$1:$V$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1868,7 +1868,7 @@
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>auto-2032414</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1916,57 +1916,57 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>INCIDENTE DE LIQUIDACIÓN DE GASTOS Y COSTAS EN EL JUICIO EJECUTIVO MERCANTIL ORAL. SU ADMISIÓN DEBE NOTIFICARSE DE MANERA PERSONAL, AL CONSTITUIR UN PROCEDIMIENTO CONTENCIOSO AUTÓNOMO E INDEPENDIENTE, Y EQUIPARARSE CON EL EMPLAZAMIENTO A JUICIO.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2032414</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032414</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
@@ -1989,17 +1989,17 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
@@ -2014,57 +2014,57 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr"/>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S13" s="13" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr"/>
       <c r="U13" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V13" s="13" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -2112,57 +2112,57 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
@@ -2210,18 +2210,18 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O15" s="13" t="inlineStr">
@@ -2232,33 +2232,131 @@
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr"/>
       <c r="U15" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+        </is>
+      </c>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>pagaré · acción causal · ordinario mercantil</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>mer-pag-003</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Títulos de crédito — pagaré</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Pagarés seriados — lugar de pago</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>2019464</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr"/>
+      <c r="Q16" s="11" t="inlineStr">
+        <is>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+        </is>
+      </c>
+      <c r="R16" s="11" t="inlineStr">
+        <is>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+        </is>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr"/>
+      <c r="U16" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
-      <c r="V15" s="13" t="inlineStr">
+      <c r="V16" s="11" t="inlineStr">
         <is>
           <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V15"/>
+  <autoFilter ref="A1:V16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4732,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V153"/>
+  <dimension ref="A1:V156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11582,7 +11680,7 @@
     <row r="74" ht="80" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>auto-2032278</t>
+          <t>auto-2032420</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
@@ -11600,7 +11698,7 @@
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr">
@@ -11610,7 +11708,7 @@
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -11630,18 +11728,18 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>ABUSO DE FUNCIONES. PARA QUE SE CONFIGURE ESE TIPO ADMINISTRATIVO BASTA LA MATERIALIZACIÓN DE CUALQUIERA DE LOS SUPUESTOS ESTABLECIDOS POR EL ARTÍCULO 57 DE LA LEY GENERAL DE RESPONSABILIDADES ADMINISTRATIVAS.</t>
+          <t>PENSIÓN DE CESANTÍA EN EDAD AVANZADA. INTERPRETACIÓN DEL SISTEMA NORMATIVO QUE LA REGULA.</t>
         </is>
       </c>
       <c r="L74" s="11" t="inlineStr">
         <is>
-          <t>2032278</t>
+          <t>2032420</t>
         </is>
       </c>
       <c r="M74" s="11" t="inlineStr"/>
       <c r="N74" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O74" s="11" t="inlineStr">
@@ -11668,19 +11766,19 @@
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032278</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032420</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="75" ht="80" customHeight="1">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>auto-2032212</t>
+          <t>auto-2032278</t>
         </is>
       </c>
       <c r="B75" s="13" t="n">
@@ -11693,12 +11791,12 @@
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
@@ -11728,18 +11826,18 @@
       </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL CON EFECTOS RESTITUTORIOS. ES IMPROCEDENTE CONTRA LA NEGATIVA MATERIAL A RECIBIR UNA SOLICITUD DE BASIFICACIÓN LABORAL, PORQUE SU CONCESIÓN IMPLICA UN BENEFICIO TOTAL QUE DEJA SIN MATERIA EL JUICIO DE AMPARO.</t>
+          <t>ABUSO DE FUNCIONES. PARA QUE SE CONFIGURE ESE TIPO ADMINISTRATIVO BASTA LA MATERIALIZACIÓN DE CUALQUIERA DE LOS SUPUESTOS ESTABLECIDOS POR EL ARTÍCULO 57 DE LA LEY GENERAL DE RESPONSABILIDADES ADMINISTRATIVAS.</t>
         </is>
       </c>
       <c r="L75" s="13" t="inlineStr">
         <is>
-          <t>2032212</t>
+          <t>2032278</t>
         </is>
       </c>
       <c r="M75" s="13" t="inlineStr"/>
       <c r="N75" s="13" t="inlineStr">
         <is>
-          <t>viernes 29 de mayo de 2026 10:34 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O75" s="13" t="inlineStr">
@@ -11766,19 +11864,19 @@
       <c r="T75" s="13" t="inlineStr"/>
       <c r="U75" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032212</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032278</t>
         </is>
       </c>
       <c r="V75" s="13" t="inlineStr">
         <is>
-          <t>Suspensión · actualización automática</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="76" ht="80" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>pen-rep-001</t>
+          <t>auto-2032212</t>
         </is>
       </c>
       <c r="B76" s="11" t="n">
@@ -11791,17 +11889,17 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>Compensación directa como parte de reparación integral</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
@@ -11826,94 +11924,90 @@
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
+          <t>SUSPENSIÓN PROVISIONAL CON EFECTOS RESTITUTORIOS. ES IMPROCEDENTE CONTRA LA NEGATIVA MATERIAL A RECIBIR UNA SOLICITUD DE BASIFICACIÓN LABORAL, PORQUE SU CONCESIÓN IMPLICA UN BENEFICIO TOTAL QUE DEJA SIN MATERIA EL JUICIO DE AMPARO.</t>
         </is>
       </c>
       <c r="L76" s="11" t="inlineStr">
         <is>
-          <t>2032030</t>
+          <t>2032212</t>
         </is>
       </c>
       <c r="M76" s="11" t="inlineStr"/>
       <c r="N76" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P76" s="11" t="inlineStr"/>
       <c r="Q76" s="11" t="inlineStr">
         <is>
-          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R76" s="11" t="inlineStr">
         <is>
-          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S76" s="11" t="inlineStr">
         <is>
-          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
-        </is>
-      </c>
-      <c r="T76" s="11" t="inlineStr">
-        <is>
-          <t>PR.P.T.CN. J/8 P (12a.)</t>
-        </is>
-      </c>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032212</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
         <is>
-          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="77" ht="80" customHeight="1">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>civ-agua-002</t>
+          <t>pen-rep-001</t>
         </is>
       </c>
       <c r="B77" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>Plenos Regionales</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>Agua y servicios públicos</t>
+          <t>Reparación del daño</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>Cobros excesivos y nulidad</t>
+          <t>Compensación directa como parte de reparación integral</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr">
@@ -11923,54 +12017,66 @@
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
+          <t>COMPENSACIÓN DIRECTA. PROCEDE CONDENAR AL SENTENCIADO A SU PAGO COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO.</t>
         </is>
       </c>
       <c r="L77" s="13" t="inlineStr">
         <is>
-          <t>Criterio TJA</t>
+          <t>2032030</t>
         </is>
       </c>
       <c r="M77" s="13" t="inlineStr"/>
-      <c r="N77" s="13" t="inlineStr"/>
-      <c r="O77" s="13" t="inlineStr"/>
+      <c r="N77" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O77" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación 12a Época — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P77" s="13" t="inlineStr"/>
       <c r="Q77" s="13" t="inlineStr">
         <is>
-          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
+          <t>En sentencias condenatorias, el juez puede y debe condenar a compensación directa al sentenciado como componente autónomo de la reparación integral del daño, adicional a indemnización y otras medidas.</t>
         </is>
       </c>
       <c r="R77" s="13" t="inlineStr">
         <is>
-          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
+          <t>Marca tendencia hacia reparación robusta a víctimas de delito.</t>
         </is>
       </c>
       <c r="S77" s="13" t="inlineStr">
         <is>
-          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
-        </is>
-      </c>
-      <c r="T77" s="13" t="inlineStr"/>
+          <t>La víctima puede pedir expresamente compensación directa además de indemnización. El juez tiene base jurisprudencial para ordenarla.</t>
+        </is>
+      </c>
+      <c r="T77" s="13" t="inlineStr">
+        <is>
+          <t>PR.P.T.CN. J/8 P (12a.)</t>
+        </is>
+      </c>
       <c r="U77" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032030</t>
         </is>
       </c>
       <c r="V77" s="13" t="inlineStr">
         <is>
-          <t>cobro excesivo · medidor · TJA</t>
+          <t>reparación del daño · compensación · víctima · Plenos Regionales</t>
         </is>
       </c>
     </row>
     <row r="78" ht="80" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-001</t>
+          <t>civ-agua-002</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
@@ -11988,12 +12094,12 @@
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud</t>
+          <t>Agua y servicios públicos</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>Reasignación sexual — IMSS</t>
+          <t>Cobros excesivos y nulidad</t>
         </is>
       </c>
       <c r="G78" s="11" t="inlineStr">
@@ -12003,7 +12109,7 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
@@ -12013,62 +12119,54 @@
       </c>
       <c r="J78" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
+          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
         </is>
       </c>
       <c r="L78" s="11" t="inlineStr">
         <is>
-          <t>2032111</t>
+          <t>Criterio TJA</t>
         </is>
       </c>
       <c r="M78" s="11" t="inlineStr"/>
-      <c r="N78" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O78" s="11" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N78" s="11" t="inlineStr"/>
+      <c r="O78" s="11" t="inlineStr"/>
       <c r="P78" s="11" t="inlineStr"/>
       <c r="Q78" s="11" t="inlineStr">
         <is>
-          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
+          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
         </is>
       </c>
       <c r="R78" s="11" t="inlineStr">
         <is>
-          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
+          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
         </is>
       </c>
       <c r="S78" s="11" t="inlineStr">
         <is>
-          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
+          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
         </is>
       </c>
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
         <is>
-          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
+          <t>cobro excesivo · medidor · TJA</t>
         </is>
       </c>
     </row>
     <row r="79" ht="80" customHeight="1">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>amp-sal-002</t>
+          <t>amp-sal-001</t>
         </is>
       </c>
       <c r="B79" s="13" t="n">
@@ -12091,7 +12189,7 @@
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>Efectos del amparo contra negativa de cirugía</t>
+          <t>Reasignación sexual — IMSS</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -12116,12 +12214,12 @@
       </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
+          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
         </is>
       </c>
       <c r="L79" s="13" t="inlineStr">
         <is>
-          <t>2032110</t>
+          <t>2032111</t>
         </is>
       </c>
       <c r="M79" s="13" t="inlineStr"/>
@@ -12138,35 +12236,35 @@
       <c r="P79" s="13" t="inlineStr"/>
       <c r="Q79" s="13" t="inlineStr">
         <is>
-          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
+          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
         </is>
       </c>
       <c r="R79" s="13" t="inlineStr">
         <is>
-          <t>Define alcance positivo del amparo en salud.</t>
+          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
         </is>
       </c>
       <c r="S79" s="13" t="inlineStr">
         <is>
-          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
+          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
         </is>
       </c>
       <c r="T79" s="13" t="inlineStr"/>
       <c r="U79" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
         </is>
       </c>
       <c r="V79" s="13" t="inlineStr">
         <is>
-          <t>amparo efectos · cirugía · salud · 12a Época</t>
+          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="80" ht="80" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-003</t>
+          <t>amp-sal-002</t>
         </is>
       </c>
       <c r="B80" s="11" t="n">
@@ -12189,7 +12287,7 @@
       </c>
       <c r="F80" s="11" t="inlineStr">
         <is>
-          <t>Autonomía IMSS limitada por DDHH</t>
+          <t>Efectos del amparo contra negativa de cirugía</t>
         </is>
       </c>
       <c r="G80" s="11" t="inlineStr">
@@ -12214,12 +12312,12 @@
       </c>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
+          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
         </is>
       </c>
       <c r="L80" s="11" t="inlineStr">
         <is>
-          <t>2032087</t>
+          <t>2032110</t>
         </is>
       </c>
       <c r="M80" s="11" t="inlineStr"/>
@@ -12236,35 +12334,35 @@
       <c r="P80" s="11" t="inlineStr"/>
       <c r="Q80" s="11" t="inlineStr">
         <is>
-          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
+          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
         </is>
       </c>
       <c r="R80" s="11" t="inlineStr">
         <is>
-          <t>Marco general contra negativas burocráticas del IMSS.</t>
+          <t>Define alcance positivo del amparo en salud.</t>
         </is>
       </c>
       <c r="S80" s="11" t="inlineStr">
         <is>
-          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
+          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
         </is>
       </c>
       <c r="T80" s="11" t="inlineStr"/>
       <c r="U80" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
         </is>
       </c>
       <c r="V80" s="11" t="inlineStr">
         <is>
-          <t>salud · IMSS · autonomía limitada · 12a Época</t>
+          <t>amparo efectos · cirugía · salud · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="81" ht="80" customHeight="1">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>auto-2032131</t>
+          <t>amp-sal-003</t>
         </is>
       </c>
       <c r="B81" s="13" t="n">
@@ -12287,7 +12385,7 @@
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Autonomía IMSS limitada por DDHH</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
@@ -12312,57 +12410,57 @@
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
+          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
         </is>
       </c>
       <c r="L81" s="13" t="inlineStr">
         <is>
-          <t>2032131</t>
+          <t>2032087</t>
         </is>
       </c>
       <c r="M81" s="13" t="inlineStr"/>
       <c r="N81" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O81" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P81" s="13" t="inlineStr"/>
       <c r="Q81" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
         </is>
       </c>
       <c r="R81" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Marco general contra negativas burocráticas del IMSS.</t>
         </is>
       </c>
       <c r="S81" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
         </is>
       </c>
       <c r="T81" s="13" t="inlineStr"/>
       <c r="U81" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
         </is>
       </c>
       <c r="V81" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud · actualización automática</t>
+          <t>salud · IMSS · autonomía limitada · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="82" ht="80" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>auto-2032246</t>
+          <t>auto-2032131</t>
         </is>
       </c>
       <c r="B82" s="11" t="n">
@@ -12410,18 +12508,18 @@
       </c>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>ALIMENTOS A PERSONAS MENORES DE EDAD CON DISCAPACIDAD. SU CONTENIDO COMPRENDE MEDIDAS DE HABILITACIÓN, REHABILITACIÓN Y DESARROLLO INTEGRAL QUE PERMITAN ELIMINAR BARRERAS Y PARTICIPAR DE MANERA PLENA Y EFECTIVA EN LA SOCIEDAD EN CONDICIONES DE IGUALDAD.</t>
+          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
         </is>
       </c>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>2032246</t>
+          <t>2032131</t>
         </is>
       </c>
       <c r="M82" s="11" t="inlineStr"/>
       <c r="N82" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
         </is>
       </c>
       <c r="O82" s="11" t="inlineStr">
@@ -12448,7 +12546,7 @@
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032246</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
@@ -12460,7 +12558,7 @@
     <row r="83" ht="80" customHeight="1">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>auto-2032262</t>
+          <t>auto-2032246</t>
         </is>
       </c>
       <c r="B83" s="13" t="n">
@@ -12508,12 +12606,12 @@
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DEL AMPARO POR CESACIÓN DE EFECTOS. NO SE ACTUALIZA CUANDO SE RECLAMA LA OMISIÓN DE UNA INSTITUCIÓN DE SALUD PÚBLICA DE ENTREGAR UN MEDICAMENTO A UNA PERSONA POR EL HECHO DE SUMINISTRARLO EN UNA OCASIÓN, SI DEBE SER CONSTANTE Y CONTINUO.</t>
+          <t>ALIMENTOS A PERSONAS MENORES DE EDAD CON DISCAPACIDAD. SU CONTENIDO COMPRENDE MEDIDAS DE HABILITACIÓN, REHABILITACIÓN Y DESARROLLO INTEGRAL QUE PERMITAN ELIMINAR BARRERAS Y PARTICIPAR DE MANERA PLENA Y EFECTIVA EN LA SOCIEDAD EN CONDICIONES DE IGUALDAD.</t>
         </is>
       </c>
       <c r="L83" s="13" t="inlineStr">
         <is>
-          <t>2032262</t>
+          <t>2032246</t>
         </is>
       </c>
       <c r="M83" s="13" t="inlineStr"/>
@@ -12546,7 +12644,7 @@
       <c r="T83" s="13" t="inlineStr"/>
       <c r="U83" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032262</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032246</t>
         </is>
       </c>
       <c r="V83" s="13" t="inlineStr">
@@ -12558,7 +12656,7 @@
     <row r="84" ht="80" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>auto-2032353</t>
+          <t>auto-2032262</t>
         </is>
       </c>
       <c r="B84" s="11" t="n">
@@ -12606,18 +12704,18 @@
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN DE PLANO EN AMPARO INDIRECTO. PROCEDE PARA ORDENAR UNA VALORACIÓN MÉDICA EN EL DOMICILIO DE UNA PERSONA, CUANDO TIENE UNA MOVILIDAD RESTRINGIDA.</t>
+          <t>IMPROCEDENCIA DEL AMPARO POR CESACIÓN DE EFECTOS. NO SE ACTUALIZA CUANDO SE RECLAMA LA OMISIÓN DE UNA INSTITUCIÓN DE SALUD PÚBLICA DE ENTREGAR UN MEDICAMENTO A UNA PERSONA POR EL HECHO DE SUMINISTRARLO EN UNA OCASIÓN, SI DEBE SER CONSTANTE Y CONTINUO.</t>
         </is>
       </c>
       <c r="L84" s="11" t="inlineStr">
         <is>
-          <t>2032353</t>
+          <t>2032262</t>
         </is>
       </c>
       <c r="M84" s="11" t="inlineStr"/>
       <c r="N84" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O84" s="11" t="inlineStr">
@@ -12644,7 +12742,7 @@
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032353</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032262</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
@@ -12656,7 +12754,7 @@
     <row r="85" ht="80" customHeight="1">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>auto-2032177</t>
+          <t>auto-2032353</t>
         </is>
       </c>
       <c r="B85" s="13" t="n">
@@ -12674,7 +12772,7 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -12704,18 +12802,18 @@
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>SUSPENSIÓN DE PLANO EN AMPARO INDIRECTO. PROCEDE PARA ORDENAR UNA VALORACIÓN MÉDICA EN EL DOMICILIO DE UNA PERSONA, CUANDO TIENE UNA MOVILIDAD RESTRINGIDA.</t>
         </is>
       </c>
       <c r="L85" s="13" t="inlineStr">
         <is>
-          <t>2032177</t>
+          <t>2032353</t>
         </is>
       </c>
       <c r="M85" s="13" t="inlineStr"/>
       <c r="N85" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O85" s="13" t="inlineStr">
@@ -12742,19 +12840,19 @@
       <c r="T85" s="13" t="inlineStr"/>
       <c r="U85" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032353</t>
         </is>
       </c>
       <c r="V85" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="86" ht="80" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>auto-2032233</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B86" s="11" t="n">
@@ -12802,18 +12900,18 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>2032233</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr"/>
       <c r="N86" s="11" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O86" s="11" t="inlineStr">
@@ -12840,7 +12938,7 @@
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
@@ -12852,7 +12950,7 @@
     <row r="87" ht="80" customHeight="1">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>auto-2032330</t>
+          <t>auto-2032233</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
@@ -12880,7 +12978,7 @@
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -12900,18 +12998,18 @@
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
+          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
         </is>
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
-          <t>2032330</t>
+          <t>2032233</t>
         </is>
       </c>
       <c r="M87" s="13" t="inlineStr"/>
       <c r="N87" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 05 de junio de 2026 10:11</t>
         </is>
       </c>
       <c r="O87" s="13" t="inlineStr">
@@ -12938,7 +13036,7 @@
       <c r="T87" s="13" t="inlineStr"/>
       <c r="U87" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
         </is>
       </c>
       <c r="V87" s="13" t="inlineStr">
@@ -12950,7 +13048,7 @@
     <row r="88" ht="80" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>auto-2032330</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
@@ -12963,27 +13061,27 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -12998,57 +13096,57 @@
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032330</t>
         </is>
       </c>
       <c r="M88" s="11" t="inlineStr"/>
       <c r="N88" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O88" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P88" s="11" t="inlineStr"/>
       <c r="Q88" s="11" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R88" s="11" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S88" s="11" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="89" ht="80" customHeight="1">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B89" s="13" t="n">
@@ -13066,12 +13164,12 @@
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
@@ -13081,7 +13179,7 @@
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -13096,57 +13194,57 @@
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M89" s="13" t="inlineStr"/>
       <c r="N89" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O89" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P89" s="13" t="inlineStr"/>
       <c r="Q89" s="13" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R89" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S89" s="13" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T89" s="13" t="inlineStr"/>
       <c r="U89" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V89" s="13" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="90" ht="80" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
@@ -13169,7 +13267,7 @@
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -13194,12 +13292,12 @@
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L90" s="11" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M90" s="11" t="inlineStr"/>
@@ -13216,35 +13314,35 @@
       <c r="P90" s="11" t="inlineStr"/>
       <c r="Q90" s="11" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R90" s="11" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S90" s="11" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="91" ht="80" customHeight="1">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>auto-2032354</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B91" s="13" t="n">
@@ -13267,7 +13365,7 @@
       </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
@@ -13292,57 +13390,57 @@
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L91" s="13" t="inlineStr">
         <is>
-          <t>2032354</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M91" s="13" t="inlineStr"/>
       <c r="N91" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O91" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P91" s="13" t="inlineStr"/>
       <c r="Q91" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R91" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S91" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T91" s="13" t="inlineStr"/>
       <c r="U91" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V91" s="13" t="inlineStr">
         <is>
-          <t>Suspensión · actualización automática</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="92" ht="80" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>auto-2032355</t>
+          <t>auto-2032354</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
@@ -13390,18 +13488,18 @@
       </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
         </is>
       </c>
       <c r="L92" s="11" t="inlineStr">
         <is>
-          <t>2032355</t>
+          <t>2032354</t>
         </is>
       </c>
       <c r="M92" s="11" t="inlineStr"/>
       <c r="N92" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O92" s="11" t="inlineStr">
@@ -13428,7 +13526,7 @@
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
@@ -13440,7 +13538,7 @@
     <row r="93" ht="80" customHeight="1">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>auto-2032235</t>
+          <t>auto-2032355</t>
         </is>
       </c>
       <c r="B93" s="13" t="n">
@@ -13453,12 +13551,12 @@
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
@@ -13488,18 +13586,18 @@
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
         </is>
       </c>
       <c r="L93" s="13" t="inlineStr">
         <is>
-          <t>2032235</t>
+          <t>2032355</t>
         </is>
       </c>
       <c r="M93" s="13" t="inlineStr"/>
       <c r="N93" s="13" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O93" s="13" t="inlineStr">
@@ -13526,19 +13624,19 @@
       <c r="T93" s="13" t="inlineStr"/>
       <c r="U93" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
         </is>
       </c>
       <c r="V93" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="94" ht="80" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>auto-2032255</t>
+          <t>auto-2032235</t>
         </is>
       </c>
       <c r="B94" s="11" t="n">
@@ -13586,18 +13684,18 @@
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
+          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
         </is>
       </c>
       <c r="L94" s="11" t="inlineStr">
         <is>
-          <t>2032255</t>
+          <t>2032235</t>
         </is>
       </c>
       <c r="M94" s="11" t="inlineStr"/>
       <c r="N94" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 05 de junio de 2026 10:11 h</t>
         </is>
       </c>
       <c r="O94" s="11" t="inlineStr">
@@ -13624,7 +13722,7 @@
       <c r="T94" s="11" t="inlineStr"/>
       <c r="U94" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
         </is>
       </c>
       <c r="V94" s="11" t="inlineStr">
@@ -13636,7 +13734,7 @@
     <row r="95" ht="80" customHeight="1">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>auto-2032255</t>
         </is>
       </c>
       <c r="B95" s="13" t="n">
@@ -13659,7 +13757,7 @@
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -13669,7 +13767,7 @@
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I95" s="13" t="inlineStr">
@@ -13679,54 +13777,62 @@
       </c>
       <c r="J95" s="13" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
         </is>
       </c>
       <c r="L95" s="13" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2032255</t>
         </is>
       </c>
       <c r="M95" s="13" t="inlineStr"/>
-      <c r="N95" s="13" t="inlineStr"/>
-      <c r="O95" s="13" t="inlineStr"/>
+      <c r="N95" s="13" t="inlineStr">
+        <is>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
+        </is>
+      </c>
+      <c r="O95" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P95" s="13" t="inlineStr"/>
       <c r="Q95" s="13" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R95" s="13" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S95" s="13" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T95" s="13" t="inlineStr"/>
       <c r="U95" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
         </is>
       </c>
       <c r="V95" s="13" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="96" ht="80" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>auto-2032412</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
@@ -13749,7 +13855,7 @@
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G96" s="11" t="inlineStr">
@@ -13774,57 +13880,57 @@
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>DESECHAMIENTO DE LA DEMANDA EN EL JUICIO ORAL MERCANTIL. ES INVÁLIDO CUANDO SE BASA EN UNA APRECIACIÓN FORMAL DEL DESAHOGO DE LA PREVENCIÓN REALIZADA EN TÉRMINOS DEL ARTÍCULO 1390 BIS 12 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L96" s="11" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2032412</t>
         </is>
       </c>
       <c r="M96" s="11" t="inlineStr"/>
       <c r="N96" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O96" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P96" s="11" t="inlineStr"/>
       <c r="Q96" s="11" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R96" s="11" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S96" s="11" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T96" s="11" t="inlineStr"/>
       <c r="U96" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032412</t>
         </is>
       </c>
       <c r="V96" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="97" ht="80" customHeight="1">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
@@ -13847,7 +13953,7 @@
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
@@ -13857,7 +13963,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr">
@@ -13867,62 +13973,54 @@
       </c>
       <c r="J97" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M97" s="13" t="inlineStr"/>
-      <c r="N97" s="13" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="O97" s="13" t="inlineStr">
-        <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N97" s="13" t="inlineStr"/>
+      <c r="O97" s="13" t="inlineStr"/>
       <c r="P97" s="13" t="inlineStr"/>
       <c r="Q97" s="13" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R97" s="13" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S97" s="13" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T97" s="13" t="inlineStr"/>
       <c r="U97" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V97" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="98" ht="80" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
@@ -13940,12 +14038,12 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G98" s="11" t="inlineStr">
@@ -13965,17 +14063,17 @@
       </c>
       <c r="J98" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L98" s="11" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M98" s="11" t="inlineStr"/>
@@ -13986,41 +14084,41 @@
       </c>
       <c r="O98" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P98" s="11" t="inlineStr"/>
       <c r="Q98" s="11" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R98" s="11" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S98" s="11" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T98" s="11" t="inlineStr"/>
       <c r="U98" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V98" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="99" ht="80" customHeight="1">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B99" s="13" t="n">
@@ -14038,12 +14136,12 @@
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
@@ -14063,62 +14161,62 @@
       </c>
       <c r="J99" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L99" s="13" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M99" s="13" t="inlineStr"/>
       <c r="N99" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O99" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P99" s="13" t="inlineStr"/>
       <c r="Q99" s="13" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R99" s="13" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S99" s="13" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T99" s="13" t="inlineStr"/>
       <c r="U99" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V99" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="100" ht="80" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
@@ -14136,12 +14234,12 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G100" s="11" t="inlineStr">
@@ -14151,7 +14249,7 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
@@ -14161,62 +14259,62 @@
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L100" s="11" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M100" s="11" t="inlineStr"/>
       <c r="N100" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O100" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P100" s="11" t="inlineStr"/>
       <c r="Q100" s="11" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R100" s="11" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S100" s="11" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T100" s="11" t="inlineStr"/>
       <c r="U100" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V100" s="11" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="101" ht="80" customHeight="1">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B101" s="13" t="n">
@@ -14234,12 +14332,12 @@
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -14264,57 +14362,57 @@
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M101" s="13" t="inlineStr"/>
       <c r="N101" s="13" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O101" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R101" s="13" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S101" s="13" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T101" s="13" t="inlineStr"/>
       <c r="U101" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V101" s="13" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="102" ht="80" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>auto-2032124</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
@@ -14332,12 +14430,12 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -14347,7 +14445,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -14362,57 +14460,57 @@
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>2032124</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M102" s="11" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O102" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P102" s="11" t="inlineStr"/>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R102" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S102" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="103" ht="80" customHeight="1">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B103" s="13" t="n">
@@ -14430,12 +14528,12 @@
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
@@ -14445,7 +14543,7 @@
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr">
@@ -14455,54 +14553,62 @@
       </c>
       <c r="J103" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L103" s="13" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M103" s="13" t="inlineStr"/>
-      <c r="N103" s="13" t="inlineStr"/>
-      <c r="O103" s="13" t="inlineStr"/>
+      <c r="N103" s="13" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="O103" s="13" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P103" s="13" t="inlineStr"/>
       <c r="Q103" s="13" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R103" s="13" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S103" s="13" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T103" s="13" t="inlineStr"/>
       <c r="U103" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V103" s="13" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="104" ht="80" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
@@ -14525,7 +14631,7 @@
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G104" s="11" t="inlineStr">
@@ -14535,7 +14641,7 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
@@ -14545,62 +14651,62 @@
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M104" s="11" t="inlineStr"/>
       <c r="N104" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
         </is>
       </c>
       <c r="O104" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P104" s="11" t="inlineStr"/>
       <c r="Q104" s="11" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R104" s="11" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S104" s="11" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V104" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="105" ht="80" customHeight="1">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B105" s="13" t="n">
@@ -14623,7 +14729,7 @@
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -14633,7 +14739,7 @@
       </c>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I105" s="13" t="inlineStr">
@@ -14643,62 +14749,54 @@
       </c>
       <c r="J105" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M105" s="13" t="inlineStr"/>
-      <c r="N105" s="13" t="inlineStr">
-        <is>
-          <t>Novena Época</t>
-        </is>
-      </c>
-      <c r="O105" s="13" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N105" s="13" t="inlineStr"/>
+      <c r="O105" s="13" t="inlineStr"/>
       <c r="P105" s="13" t="inlineStr"/>
       <c r="Q105" s="13" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R105" s="13" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S105" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T105" s="13" t="inlineStr"/>
       <c r="U105" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V105" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="106" ht="80" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
@@ -14716,22 +14814,22 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
@@ -14741,58 +14839,62 @@
       </c>
       <c r="J106" s="11" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M106" s="11" t="inlineStr"/>
       <c r="N106" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O106" s="11" t="inlineStr"/>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O106" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P106" s="11" t="inlineStr"/>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R106" s="11" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S106" s="11" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="107" ht="80" customHeight="1">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
@@ -14810,12 +14912,12 @@
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
@@ -14825,7 +14927,7 @@
       </c>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr">
@@ -14840,18 +14942,18 @@
       </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M107" s="13" t="inlineStr"/>
       <c r="N107" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="O107" s="13" t="inlineStr">
@@ -14862,35 +14964,35 @@
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R107" s="13" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S107" s="13" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T107" s="13" t="inlineStr"/>
       <c r="U107" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V107" s="13" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="108" ht="80" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>auto-2032319</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
@@ -14908,22 +15010,22 @@
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I108" s="11" t="inlineStr">
@@ -14933,62 +15035,58 @@
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>2032319</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M108" s="11" t="inlineStr"/>
       <c r="N108" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
-        </is>
-      </c>
-      <c r="O108" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O108" s="11" t="inlineStr"/>
       <c r="P108" s="11" t="inlineStr"/>
       <c r="Q108" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R108" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S108" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva · actualización automática</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="109" ht="80" customHeight="1">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B109" s="13" t="n">
@@ -15006,22 +15104,22 @@
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F109" s="13" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I109" s="13" t="inlineStr">
@@ -15031,58 +15129,62 @@
       </c>
       <c r="J109" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M109" s="13" t="inlineStr"/>
-      <c r="N109" s="13" t="inlineStr"/>
+      <c r="N109" s="13" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
       <c r="O109" s="13" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P109" s="13" t="inlineStr"/>
       <c r="Q109" s="13" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R109" s="13" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S109" s="13" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T109" s="13" t="inlineStr"/>
       <c r="U109" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V109" s="13" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="110" ht="80" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>auto-2032319</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
@@ -15105,17 +15207,17 @@
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I110" s="11" t="inlineStr">
@@ -15130,49 +15232,57 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
         </is>
       </c>
       <c r="L110" s="11" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>2032319</t>
         </is>
       </c>
       <c r="M110" s="11" t="inlineStr"/>
-      <c r="N110" s="11" t="inlineStr"/>
-      <c r="O110" s="11" t="inlineStr"/>
+      <c r="N110" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O110" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P110" s="11" t="inlineStr"/>
       <c r="Q110" s="11" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R110" s="11" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S110" s="11" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T110" s="11" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
         </is>
       </c>
       <c r="V110" s="11" t="inlineStr">
         <is>
-          <t>posesión derivada · concepto de propietario · interversión</t>
+          <t>Usucapión / Prescripción positiva · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="111" ht="80" customHeight="1">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>con-asa-001</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B111" s="13" t="n">
@@ -15185,27 +15295,27 @@
       </c>
       <c r="D111" s="13" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F111" s="13" t="inlineStr">
         <is>
-          <t>Asambleas — convocatoria y validez</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I111" s="13" t="inlineStr">
@@ -15215,54 +15325,58 @@
       </c>
       <c r="J111" s="13" t="inlineStr">
         <is>
-          <t>Federal — interpreta LPCI CDMX</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>Art. 32 LPCI CDMX</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M111" s="13" t="inlineStr"/>
       <c r="N111" s="13" t="inlineStr"/>
-      <c r="O111" s="13" t="inlineStr"/>
+      <c r="O111" s="13" t="inlineStr">
+        <is>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+        </is>
+      </c>
       <c r="P111" s="13" t="inlineStr"/>
       <c r="Q111" s="13" t="inlineStr">
         <is>
-          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R111" s="13" t="inlineStr">
         <is>
-          <t>Defensa frecuente de minorías condominales.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S111" s="13" t="inlineStr">
         <is>
-          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T111" s="13" t="inlineStr"/>
       <c r="U111" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
         </is>
       </c>
       <c r="V111" s="13" t="inlineStr">
         <is>
-          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
+          <t>pericial · topografía · identidad del bien</t>
         </is>
       </c>
     </row>
     <row r="112" ht="80" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>amp-cui-001</t>
+          <t>civ-usu-005</t>
         </is>
       </c>
       <c r="B112" s="11" t="n">
@@ -15275,27 +15389,27 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
         <is>
-          <t>Reconocimiento e interés legítimo</t>
+          <t>Posesión derivada vs. originaria</t>
         </is>
       </c>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I112" s="11" t="inlineStr">
@@ -15310,57 +15424,49 @@
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L112" s="11" t="inlineStr">
         <is>
-          <t>2032085</t>
+          <t>2030499</t>
         </is>
       </c>
       <c r="M112" s="11" t="inlineStr"/>
-      <c r="N112" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O112" s="11" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N112" s="11" t="inlineStr"/>
+      <c r="O112" s="11" t="inlineStr"/>
       <c r="P112" s="11" t="inlineStr"/>
       <c r="Q112" s="11" t="inlineStr">
         <is>
-          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
         </is>
       </c>
       <c r="R112" s="11" t="inlineStr">
         <is>
-          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
         </is>
       </c>
       <c r="S112" s="11" t="inlineStr">
         <is>
-          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
         </is>
       </c>
       <c r="T112" s="11" t="inlineStr"/>
       <c r="U112" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
       <c r="V112" s="11" t="inlineStr">
         <is>
-          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
+          <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
     <row r="113" ht="80" customHeight="1">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>amp-cui-002</t>
+          <t>con-asa-001</t>
         </is>
       </c>
       <c r="B113" s="13" t="n">
@@ -15373,17 +15479,17 @@
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>Interés legítimo para combatir omisiones legislativas</t>
+          <t>Asambleas — convocatoria y validez</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
@@ -15393,7 +15499,7 @@
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I113" s="13" t="inlineStr">
@@ -15403,62 +15509,54 @@
       </c>
       <c r="J113" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta LPCI CDMX</t>
         </is>
       </c>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
+          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
         </is>
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
-          <t>2032086</t>
+          <t>Art. 32 LPCI CDMX</t>
         </is>
       </c>
       <c r="M113" s="13" t="inlineStr"/>
-      <c r="N113" s="13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O113" s="13" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N113" s="13" t="inlineStr"/>
+      <c r="O113" s="13" t="inlineStr"/>
       <c r="P113" s="13" t="inlineStr"/>
       <c r="Q113" s="13" t="inlineStr">
         <is>
-          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
+          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
         </is>
       </c>
       <c r="R113" s="13" t="inlineStr">
         <is>
-          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
+          <t>Defensa frecuente de minorías condominales.</t>
         </is>
       </c>
       <c r="S113" s="13" t="inlineStr">
         <is>
-          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
+          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
         </is>
       </c>
       <c r="T113" s="13" t="inlineStr"/>
       <c r="U113" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
         </is>
       </c>
       <c r="V113" s="13" t="inlineStr">
         <is>
-          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
+          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
         </is>
       </c>
     </row>
     <row r="114" ht="80" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>auto-2032312</t>
+          <t>amp-cui-001</t>
         </is>
       </c>
       <c r="B114" s="11" t="n">
@@ -15476,12 +15574,12 @@
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Medio ambiente sano</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Reconocimiento e interés legítimo</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
@@ -15506,57 +15604,57 @@
       </c>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
+          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L114" s="11" t="inlineStr">
         <is>
-          <t>2032312</t>
+          <t>2032085</t>
         </is>
       </c>
       <c r="M114" s="11" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O114" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P114" s="11" t="inlineStr"/>
       <c r="Q114" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
         </is>
       </c>
       <c r="R114" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
         </is>
       </c>
       <c r="S114" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
         </is>
       </c>
       <c r="T114" s="11" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
         </is>
       </c>
       <c r="V114" s="11" t="inlineStr">
         <is>
-          <t>Medio ambiente sano · actualización automática</t>
+          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
         </is>
       </c>
     </row>
     <row r="115" ht="80" customHeight="1">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>auto-2032313</t>
+          <t>amp-cui-002</t>
         </is>
       </c>
       <c r="B115" s="13" t="n">
@@ -15574,12 +15672,12 @@
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F115" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Interés legítimo para combatir omisiones legislativas</t>
         </is>
       </c>
       <c r="G115" s="13" t="inlineStr">
@@ -15604,57 +15702,57 @@
       </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
+          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
         </is>
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
-          <t>2032313</t>
+          <t>2032086</t>
         </is>
       </c>
       <c r="M115" s="13" t="inlineStr"/>
       <c r="N115" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O115" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P115" s="13" t="inlineStr"/>
       <c r="Q115" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
         </is>
       </c>
       <c r="R115" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
         </is>
       </c>
       <c r="S115" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
         </is>
       </c>
       <c r="T115" s="13" t="inlineStr"/>
       <c r="U115" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
         </is>
       </c>
       <c r="V115" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano · actualización automática</t>
+          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
         </is>
       </c>
     </row>
     <row r="116" ht="80" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>auto-2032154</t>
+          <t>auto-2032312</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
@@ -15672,7 +15770,7 @@
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr">
@@ -15702,18 +15800,18 @@
       </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L116" s="11" t="inlineStr">
         <is>
-          <t>2032154</t>
+          <t>2032312</t>
         </is>
       </c>
       <c r="M116" s="11" t="inlineStr"/>
       <c r="N116" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O116" s="11" t="inlineStr">
@@ -15740,19 +15838,19 @@
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="117" ht="80" customHeight="1">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>auto-2032184</t>
+          <t>auto-2032313</t>
         </is>
       </c>
       <c r="B117" s="13" t="n">
@@ -15770,7 +15868,7 @@
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F117" s="13" t="inlineStr">
@@ -15800,18 +15898,18 @@
       </c>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>2032184</t>
+          <t>2032313</t>
         </is>
       </c>
       <c r="M117" s="13" t="inlineStr"/>
       <c r="N117" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O117" s="13" t="inlineStr">
@@ -15838,19 +15936,19 @@
       <c r="T117" s="13" t="inlineStr"/>
       <c r="U117" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
         </is>
       </c>
       <c r="V117" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="118" ht="80" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>auto-2032279</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
@@ -15898,18 +15996,18 @@
       </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L118" s="11" t="inlineStr">
         <is>
-          <t>2032279</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M118" s="11" t="inlineStr"/>
       <c r="N118" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O118" s="11" t="inlineStr">
@@ -15936,7 +16034,7 @@
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
@@ -15948,7 +16046,7 @@
     <row r="119" ht="80" customHeight="1">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>auto-2032302</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B119" s="13" t="n">
@@ -15996,18 +16094,18 @@
       </c>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
-          <t>2032302</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M119" s="13" t="inlineStr"/>
       <c r="N119" s="13" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O119" s="13" t="inlineStr">
@@ -16034,7 +16132,7 @@
       <c r="T119" s="13" t="inlineStr"/>
       <c r="U119" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
         </is>
       </c>
       <c r="V119" s="13" t="inlineStr">
@@ -16046,7 +16144,7 @@
     <row r="120" ht="80" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>auto-2032309</t>
+          <t>auto-2032279</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
@@ -16094,18 +16192,18 @@
       </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
+          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
         </is>
       </c>
       <c r="L120" s="11" t="inlineStr">
         <is>
-          <t>2032309</t>
+          <t>2032279</t>
         </is>
       </c>
       <c r="M120" s="11" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O120" s="11" t="inlineStr">
@@ -16132,7 +16230,7 @@
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
@@ -16144,7 +16242,7 @@
     <row r="121" ht="80" customHeight="1">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>auto-2032325</t>
+          <t>auto-2032302</t>
         </is>
       </c>
       <c r="B121" s="13" t="n">
@@ -16192,18 +16290,18 @@
       </c>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
         </is>
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>2032325</t>
+          <t>2032302</t>
         </is>
       </c>
       <c r="M121" s="13" t="inlineStr"/>
       <c r="N121" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O121" s="13" t="inlineStr">
@@ -16230,7 +16328,7 @@
       <c r="T121" s="13" t="inlineStr"/>
       <c r="U121" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
         </is>
       </c>
       <c r="V121" s="13" t="inlineStr">
@@ -16242,7 +16340,7 @@
     <row r="122" ht="80" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>auto-2032326</t>
+          <t>auto-2032309</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
@@ -16290,12 +16388,12 @@
       </c>
       <c r="K122" s="12" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
+          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
         </is>
       </c>
       <c r="L122" s="11" t="inlineStr">
         <is>
-          <t>2032326</t>
+          <t>2032309</t>
         </is>
       </c>
       <c r="M122" s="11" t="inlineStr"/>
@@ -16328,7 +16426,7 @@
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
@@ -16340,7 +16438,7 @@
     <row r="123" ht="80" customHeight="1">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>auto-2032327</t>
+          <t>auto-2032325</t>
         </is>
       </c>
       <c r="B123" s="13" t="n">
@@ -16388,12 +16486,12 @@
       </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
         </is>
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>2032327</t>
+          <t>2032325</t>
         </is>
       </c>
       <c r="M123" s="13" t="inlineStr"/>
@@ -16426,7 +16524,7 @@
       <c r="T123" s="13" t="inlineStr"/>
       <c r="U123" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
         </is>
       </c>
       <c r="V123" s="13" t="inlineStr">
@@ -16438,7 +16536,7 @@
     <row r="124" ht="80" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>auto-2032338</t>
+          <t>auto-2032326</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
@@ -16486,12 +16584,12 @@
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L124" s="11" t="inlineStr">
         <is>
-          <t>2032338</t>
+          <t>2032326</t>
         </is>
       </c>
       <c r="M124" s="11" t="inlineStr"/>
@@ -16524,7 +16622,7 @@
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
@@ -16536,7 +16634,7 @@
     <row r="125" ht="80" customHeight="1">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>auto-2032340</t>
+          <t>auto-2032327</t>
         </is>
       </c>
       <c r="B125" s="13" t="n">
@@ -16584,12 +16682,12 @@
       </c>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
+          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
         </is>
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>2032340</t>
+          <t>2032327</t>
         </is>
       </c>
       <c r="M125" s="13" t="inlineStr"/>
@@ -16622,7 +16720,7 @@
       <c r="T125" s="13" t="inlineStr"/>
       <c r="U125" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
         </is>
       </c>
       <c r="V125" s="13" t="inlineStr">
@@ -16634,7 +16732,7 @@
     <row r="126" ht="80" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>auto-2032347</t>
+          <t>auto-2032338</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
@@ -16682,12 +16780,12 @@
       </c>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
+          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
         </is>
       </c>
       <c r="L126" s="11" t="inlineStr">
         <is>
-          <t>2032347</t>
+          <t>2032338</t>
         </is>
       </c>
       <c r="M126" s="11" t="inlineStr"/>
@@ -16720,7 +16818,7 @@
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
@@ -16732,7 +16830,7 @@
     <row r="127" ht="80" customHeight="1">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>auto-2032376</t>
+          <t>auto-2032340</t>
         </is>
       </c>
       <c r="B127" s="13" t="n">
@@ -16780,18 +16878,18 @@
       </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
+          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
         </is>
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>2032376</t>
+          <t>2032340</t>
         </is>
       </c>
       <c r="M127" s="13" t="inlineStr"/>
       <c r="N127" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O127" s="13" t="inlineStr">
@@ -16818,7 +16916,7 @@
       <c r="T127" s="13" t="inlineStr"/>
       <c r="U127" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
         </is>
       </c>
       <c r="V127" s="13" t="inlineStr">
@@ -16830,7 +16928,7 @@
     <row r="128" ht="80" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032347</t>
         </is>
       </c>
       <c r="B128" s="11" t="n">
@@ -16848,12 +16946,12 @@
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr">
@@ -16878,57 +16976,57 @@
       </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
         </is>
       </c>
       <c r="L128" s="11" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032347</t>
         </is>
       </c>
       <c r="M128" s="11" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O128" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P128" s="11" t="inlineStr"/>
       <c r="Q128" s="11" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R128" s="11" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S128" s="11" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="129" ht="80" customHeight="1">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-002</t>
+          <t>auto-2032376</t>
         </is>
       </c>
       <c r="B129" s="13" t="n">
@@ -16941,22 +17039,22 @@
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>69-B — recurso de revocación y buzón tributario</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
@@ -16976,57 +17074,57 @@
       </c>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
+          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
         </is>
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
-          <t>2031931</t>
+          <t>2032376</t>
         </is>
       </c>
       <c r="M129" s="13" t="inlineStr"/>
       <c r="N129" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
         </is>
       </c>
       <c r="O129" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P129" s="13" t="inlineStr"/>
       <c r="Q129" s="13" t="inlineStr">
         <is>
-          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R129" s="13" t="inlineStr">
         <is>
-          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S129" s="13" t="inlineStr">
         <is>
-          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T129" s="13" t="inlineStr"/>
       <c r="U129" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
         </is>
       </c>
       <c r="V129" s="13" t="inlineStr">
         <is>
-          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="130" ht="80" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-003</t>
+          <t>amp-gen-001</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
@@ -17039,17 +17137,17 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género interseccional</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>Materialidad — fundar y motivar</t>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr">
@@ -17074,57 +17172,57 @@
       </c>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
         </is>
       </c>
       <c r="L130" s="11" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>2032067</t>
         </is>
       </c>
       <c r="M130" s="11" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O130" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P130" s="11" t="inlineStr"/>
       <c r="Q130" s="11" t="inlineStr">
         <is>
-          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
         </is>
       </c>
       <c r="R130" s="11" t="inlineStr">
         <is>
-          <t>Defensa fuerte para contribuyentes auditados.</t>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
         </is>
       </c>
       <c r="S130" s="11" t="inlineStr">
         <is>
-          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
         </is>
       </c>
       <c r="T130" s="11" t="inlineStr"/>
       <c r="U130" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
       <c r="V130" s="11" t="inlineStr">
         <is>
-          <t>69-B · materialidad · fundamentación · 12a Época</t>
+          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="131" ht="80" customHeight="1">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-004</t>
+          <t>fis-cfd-002</t>
         </is>
       </c>
       <c r="B131" s="13" t="n">
@@ -17147,12 +17245,12 @@
       </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>Nulidad EFOS — efectos sobre proveedor</t>
+          <t>69-B — recurso de revocación y buzón tributario</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
@@ -17172,12 +17270,12 @@
       </c>
       <c r="K131" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
+          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
         </is>
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>2031349</t>
+          <t>2031931</t>
         </is>
       </c>
       <c r="M131" s="13" t="inlineStr"/>
@@ -17194,35 +17292,35 @@
       <c r="P131" s="13" t="inlineStr"/>
       <c r="Q131" s="13" t="inlineStr">
         <is>
-          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
+          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
         </is>
       </c>
       <c r="R131" s="13" t="inlineStr">
         <is>
-          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
+          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
         </is>
       </c>
       <c r="S131" s="13" t="inlineStr">
         <is>
-          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
+          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
         </is>
       </c>
       <c r="T131" s="13" t="inlineStr"/>
       <c r="U131" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
         </is>
       </c>
       <c r="V131" s="13" t="inlineStr">
         <is>
-          <t>EFOS · nulidad · deducciones · 12a Época</t>
+          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
         </is>
       </c>
     </row>
     <row r="132" ht="80" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>auto-2032254</t>
+          <t>fis-cfd-003</t>
         </is>
       </c>
       <c r="B132" s="11" t="n">
@@ -17235,17 +17333,17 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Materialidad — fundar y motivar</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr">
@@ -17270,57 +17368,57 @@
       </c>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L132" s="11" t="inlineStr">
         <is>
-          <t>2032254</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M132" s="11" t="inlineStr"/>
       <c r="N132" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O132" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P132" s="11" t="inlineStr"/>
       <c r="Q132" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
         </is>
       </c>
       <c r="R132" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa fuerte para contribuyentes auditados.</t>
         </is>
       </c>
       <c r="S132" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
         </is>
       </c>
       <c r="T132" s="11" t="inlineStr"/>
       <c r="U132" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V132" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado · actualización automática</t>
+          <t>69-B · materialidad · fundamentación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="133" ht="80" customHeight="1">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>lab-des-002</t>
+          <t>fis-cfd-004</t>
         </is>
       </c>
       <c r="B133" s="13" t="n">
@@ -17333,17 +17431,17 @@
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>Carga patrón cuando alega rescisión justificada posterior</t>
+          <t>Nulidad EFOS — efectos sobre proveedor</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
@@ -17353,7 +17451,7 @@
       </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I133" s="13" t="inlineStr">
@@ -17368,18 +17466,18 @@
       </c>
       <c r="K133" s="14" t="inlineStr">
         <is>
-          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
         </is>
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>2031349</t>
         </is>
       </c>
       <c r="M133" s="13" t="inlineStr"/>
       <c r="N133" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O133" s="13" t="inlineStr">
@@ -17390,35 +17488,35 @@
       <c r="P133" s="13" t="inlineStr"/>
       <c r="Q133" s="13" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
+          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
         </is>
       </c>
       <c r="R133" s="13" t="inlineStr">
         <is>
-          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
+          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
         </is>
       </c>
       <c r="S133" s="13" t="inlineStr">
         <is>
-          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
+          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
         </is>
       </c>
       <c r="T133" s="13" t="inlineStr"/>
       <c r="U133" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
         </is>
       </c>
       <c r="V133" s="13" t="inlineStr">
         <is>
-          <t>despido · rescisión · carga probatoria patrón</t>
+          <t>EFOS · nulidad · deducciones · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="134" ht="80" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>lab-ren-001</t>
+          <t>auto-2032254</t>
         </is>
       </c>
       <c r="B134" s="11" t="n">
@@ -17436,12 +17534,12 @@
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Hora de terminación — carga del patrón</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr">
@@ -17451,7 +17549,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -17466,57 +17564,57 @@
       </c>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
+          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
         </is>
       </c>
       <c r="L134" s="11" t="inlineStr">
         <is>
-          <t>2028640</t>
+          <t>2032254</t>
         </is>
       </c>
       <c r="M134" s="11" t="inlineStr"/>
       <c r="N134" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O134" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P134" s="11" t="inlineStr"/>
       <c r="Q134" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R134" s="11" t="inlineStr">
         <is>
-          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S134" s="11" t="inlineStr">
         <is>
-          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T134" s="11" t="inlineStr"/>
       <c r="U134" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
         </is>
       </c>
       <c r="V134" s="11" t="inlineStr">
         <is>
-          <t>renuncia · hora despido · carga probatoria</t>
+          <t>Despido injustificado · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="135" ht="80" customHeight="1">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>lab-ren-002</t>
+          <t>lab-des-002</t>
         </is>
       </c>
       <c r="B135" s="13" t="n">
@@ -17534,12 +17632,12 @@
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
+          <t>Carga patrón cuando alega rescisión justificada posterior</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
@@ -17564,18 +17662,18 @@
       </c>
       <c r="K135" s="14" t="inlineStr">
         <is>
-          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
+          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
         </is>
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>2027058</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M135" s="13" t="inlineStr"/>
       <c r="N135" s="13" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O135" s="13" t="inlineStr">
@@ -17586,35 +17684,35 @@
       <c r="P135" s="13" t="inlineStr"/>
       <c r="Q135" s="13" t="inlineStr">
         <is>
-          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
+          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
         </is>
       </c>
       <c r="R135" s="13" t="inlineStr">
         <is>
-          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
+          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
         </is>
       </c>
       <c r="S135" s="13" t="inlineStr">
         <is>
-          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
+          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
         </is>
       </c>
       <c r="T135" s="13" t="inlineStr"/>
       <c r="U135" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V135" s="13" t="inlineStr">
         <is>
-          <t>renuncia · jubilación · veracidad · carga reforzada</t>
+          <t>despido · rescisión · carga probatoria patrón</t>
         </is>
       </c>
     </row>
     <row r="136" ht="80" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>sen-020</t>
+          <t>lab-ren-001</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
@@ -17627,27 +17725,27 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>Costas en juicio mercantil — tasación</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
+          <t>Hora de terminación — carga del patrón</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -17657,58 +17755,62 @@
       </c>
       <c r="J136" s="11" t="inlineStr">
         <is>
-          <t>Primer y Segundo Circuito</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K136" s="12" t="inlineStr">
         <is>
-          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
+          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
         </is>
       </c>
       <c r="L136" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados — múltiples</t>
+          <t>2028640</t>
         </is>
       </c>
       <c r="M136" s="11" t="inlineStr"/>
       <c r="N136" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O136" s="11" t="inlineStr"/>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P136" s="11" t="inlineStr"/>
       <c r="Q136" s="11" t="inlineStr">
         <is>
-          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
+          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
         </is>
       </c>
       <c r="R136" s="11" t="inlineStr">
         <is>
-          <t>Marco práctico para pretensión y oposición a costas.</t>
+          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
         </is>
       </c>
       <c r="S136" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
+          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
         </is>
       </c>
       <c r="T136" s="11" t="inlineStr"/>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
         </is>
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>costas · tasación · arancel · mercantil</t>
+          <t>renuncia · hora despido · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="137" ht="80" customHeight="1">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>auto-2032198</t>
+          <t>lab-ren-002</t>
         </is>
       </c>
       <c r="B137" s="13" t="n">
@@ -17721,17 +17823,17 @@
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
@@ -17741,7 +17843,7 @@
       </c>
       <c r="H137" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I137" s="13" t="inlineStr">
@@ -17756,57 +17858,57 @@
       </c>
       <c r="K137" s="14" t="inlineStr">
         <is>
-          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
+          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
         </is>
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
-          <t>2032198</t>
+          <t>2027058</t>
         </is>
       </c>
       <c r="M137" s="13" t="inlineStr"/>
       <c r="N137" s="13" t="inlineStr">
         <is>
-          <t>viernes 29 de mayo de 2026 10:34 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O137" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P137" s="13" t="inlineStr"/>
       <c r="Q137" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
         </is>
       </c>
       <c r="R137" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
         </is>
       </c>
       <c r="S137" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
         </is>
       </c>
       <c r="T137" s="13" t="inlineStr"/>
       <c r="U137" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
         </is>
       </c>
       <c r="V137" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>renuncia · jubilación · veracidad · carga reforzada</t>
         </is>
       </c>
     </row>
     <row r="138" ht="80" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>auto-2032274</t>
+          <t>sen-020</t>
         </is>
       </c>
       <c r="B138" s="11" t="n">
@@ -17824,22 +17926,22 @@
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Costas en juicio mercantil — tasación</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H138" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I138" s="11" t="inlineStr">
@@ -17849,62 +17951,58 @@
       </c>
       <c r="J138" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer y Segundo Circuito</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
+          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
         </is>
       </c>
       <c r="L138" s="11" t="inlineStr">
         <is>
-          <t>2032274</t>
+          <t>Línea de Colegiados — múltiples</t>
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr"/>
       <c r="N138" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
-        </is>
-      </c>
-      <c r="O138" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr"/>
       <c r="P138" s="11" t="inlineStr"/>
       <c r="Q138" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
         </is>
       </c>
       <c r="R138" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Marco práctico para pretensión y oposición a costas.</t>
         </is>
       </c>
       <c r="S138" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
         </is>
       </c>
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>costas · tasación · arancel · mercantil</t>
         </is>
       </c>
     </row>
     <row r="139" ht="80" customHeight="1">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>auto-2032198</t>
         </is>
       </c>
       <c r="B139" s="13" t="n">
@@ -17927,17 +18025,17 @@
       </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H139" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I139" s="13" t="inlineStr">
@@ -17952,57 +18050,57 @@
       </c>
       <c r="K139" s="14" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
         </is>
       </c>
       <c r="L139" s="13" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2032198</t>
         </is>
       </c>
       <c r="M139" s="13" t="inlineStr"/>
       <c r="N139" s="13" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O139" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P139" s="13" t="inlineStr"/>
       <c r="Q139" s="13" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R139" s="13" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S139" s="13" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T139" s="13" t="inlineStr"/>
       <c r="U139" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
         </is>
       </c>
       <c r="V139" s="13" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="140" ht="80" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>auto-2032274</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
@@ -18025,7 +18123,7 @@
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr">
@@ -18050,57 +18148,57 @@
       </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L140" s="11" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2032274</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr"/>
       <c r="N140" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O140" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P140" s="11" t="inlineStr"/>
       <c r="Q140" s="11" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R140" s="11" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S140" s="11" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="141" ht="80" customHeight="1">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>auto-2032414</t>
         </is>
       </c>
       <c r="B141" s="13" t="n">
@@ -18118,12 +18216,12 @@
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
@@ -18133,7 +18231,7 @@
       </c>
       <c r="H141" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I141" s="13" t="inlineStr">
@@ -18148,57 +18246,57 @@
       </c>
       <c r="K141" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>INCIDENTE DE LIQUIDACIÓN DE GASTOS Y COSTAS EN EL JUICIO EJECUTIVO MERCANTIL ORAL. SU ADMISIÓN DEBE NOTIFICARSE DE MANERA PERSONAL, AL CONSTITUIR UN PROCEDIMIENTO CONTENCIOSO AUTÓNOMO E INDEPENDIENTE, Y EQUIPARARSE CON EL EMPLAZAMIENTO A JUICIO.</t>
         </is>
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2032414</t>
         </is>
       </c>
       <c r="M141" s="13" t="inlineStr"/>
       <c r="N141" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O141" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P141" s="13" t="inlineStr"/>
       <c r="Q141" s="13" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R141" s="13" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S141" s="13" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T141" s="13" t="inlineStr"/>
       <c r="U141" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032414</t>
         </is>
       </c>
       <c r="V141" s="13" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="142" ht="80" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
@@ -18216,22 +18314,22 @@
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I142" s="11" t="inlineStr">
@@ -18246,18 +18344,18 @@
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L142" s="11" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M142" s="11" t="inlineStr"/>
       <c r="N142" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O142" s="11" t="inlineStr">
@@ -18268,35 +18366,35 @@
       <c r="P142" s="11" t="inlineStr"/>
       <c r="Q142" s="11" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R142" s="11" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S142" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
         <is>
-          <t>pagaré · pagarés seriados · lugar de pago</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="143" ht="80" customHeight="1">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>auto-2032371</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B143" s="13" t="n">
@@ -18309,17 +18407,17 @@
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
@@ -18344,57 +18442,57 @@
       </c>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>COSA JUZGADA EN EL JUICIO DE AMPARO. CUANDO SE INVOLUCRAN DERECHOS DE NIÑAS, NIÑOS Y ADOLESCENTES, SU ACTUALIZACIÓN REQUIERE UN ANÁLISIS REFORZADO Y UNA CORRESPONDENCIA MATERIAL ENTRE LO PREVIAMENTE RESUELTO Y EL ACTO RECLAMADO.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>2032371</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M143" s="13" t="inlineStr"/>
       <c r="N143" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O143" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P143" s="13" t="inlineStr"/>
       <c r="Q143" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R143" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S143" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T143" s="13" t="inlineStr"/>
       <c r="U143" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032371</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V143" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia · actualización automática</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="144" ht="80" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
@@ -18407,22 +18505,22 @@
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H144" s="11" t="inlineStr">
@@ -18442,18 +18540,18 @@
       </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L144" s="11" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M144" s="11" t="inlineStr"/>
       <c r="N144" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O144" s="11" t="inlineStr">
@@ -18464,35 +18562,35 @@
       <c r="P144" s="11" t="inlineStr"/>
       <c r="Q144" s="11" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R144" s="11" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S144" s="11" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>pagaré · acción causal · ordinario mercantil</t>
         </is>
       </c>
     </row>
     <row r="145" ht="80" customHeight="1">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>mer-pag-003</t>
         </is>
       </c>
       <c r="B145" s="13" t="n">
@@ -18505,17 +18603,17 @@
       </c>
       <c r="D145" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Pagarés seriados — lugar de pago</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
@@ -18540,18 +18638,18 @@
       </c>
       <c r="K145" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
         </is>
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2019464</t>
         </is>
       </c>
       <c r="M145" s="13" t="inlineStr"/>
       <c r="N145" s="13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="O145" s="13" t="inlineStr">
@@ -18562,35 +18660,35 @@
       <c r="P145" s="13" t="inlineStr"/>
       <c r="Q145" s="13" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
         </is>
       </c>
       <c r="R145" s="13" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
         </is>
       </c>
       <c r="S145" s="13" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
         </is>
       </c>
       <c r="T145" s="13" t="inlineStr"/>
       <c r="U145" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
       <c r="V145" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
     <row r="146" ht="80" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>auto-2032371</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
@@ -18608,12 +18706,12 @@
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr">
@@ -18638,57 +18736,57 @@
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>COSA JUZGADA EN EL JUICIO DE AMPARO. CUANDO SE INVOLUCRAN DERECHOS DE NIÑAS, NIÑOS Y ADOLESCENTES, SU ACTUALIZACIÓN REQUIERE UN ANÁLISIS REFORZADO Y UNA CORRESPONDENCIA MATERIAL ENTRE LO PREVIAMENTE RESUELTO Y EL ACTO RECLAMADO.</t>
         </is>
       </c>
       <c r="L146" s="11" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2032371</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr"/>
       <c r="N146" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
         </is>
       </c>
       <c r="O146" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P146" s="11" t="inlineStr"/>
       <c r="Q146" s="11" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R146" s="11" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S146" s="11" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T146" s="11" t="inlineStr"/>
       <c r="U146" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032371</t>
         </is>
       </c>
       <c r="V146" s="11" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>Cadena de custodia · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="147" ht="80" customHeight="1">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>pen-cad-002</t>
         </is>
       </c>
       <c r="B147" s="13" t="n">
@@ -18706,22 +18804,22 @@
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I147" s="13" t="inlineStr">
@@ -18736,57 +18834,57 @@
       </c>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
         </is>
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2027962</t>
         </is>
       </c>
       <c r="M147" s="13" t="inlineStr"/>
       <c r="N147" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O147" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P147" s="13" t="inlineStr"/>
       <c r="Q147" s="13" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
         </is>
       </c>
       <c r="R147" s="13" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
         </is>
       </c>
       <c r="S147" s="13" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
         </is>
       </c>
       <c r="T147" s="13" t="inlineStr"/>
       <c r="U147" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
         </is>
       </c>
       <c r="V147" s="13" t="inlineStr">
         <is>
-          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
         </is>
       </c>
     </row>
     <row r="148" ht="80" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>auto-2032300</t>
+          <t>pen-cad-003</t>
         </is>
       </c>
       <c r="B148" s="11" t="n">
@@ -18804,12 +18902,12 @@
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Transgresión no torna ilícita la prueba</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr">
@@ -18819,7 +18917,7 @@
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr">
@@ -18834,57 +18932,57 @@
       </c>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
         </is>
       </c>
       <c r="L148" s="11" t="inlineStr">
         <is>
-          <t>2032300</t>
+          <t>2021845</t>
         </is>
       </c>
       <c r="M148" s="11" t="inlineStr"/>
       <c r="N148" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="O148" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P148" s="11" t="inlineStr"/>
       <c r="Q148" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
         </is>
       </c>
       <c r="R148" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
         </is>
       </c>
       <c r="S148" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
         </is>
       </c>
       <c r="T148" s="11" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
         </is>
       </c>
       <c r="V148" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>cadena custodia · valor probatorio · exclusión</t>
         </is>
       </c>
     </row>
     <row r="149" ht="80" customHeight="1">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>auto-2032301</t>
+          <t>pen-ppo-001</t>
         </is>
       </c>
       <c r="B149" s="13" t="n">
@@ -18902,12 +19000,12 @@
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Prisión preventiva oficiosa</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
@@ -18932,57 +19030,57 @@
       </c>
       <c r="K149" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
-          <t>2032301</t>
+          <t>2032107</t>
         </is>
       </c>
       <c r="M149" s="13" t="inlineStr"/>
       <c r="N149" s="13" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O149" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P149" s="13" t="inlineStr"/>
       <c r="Q149" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
         </is>
       </c>
       <c r="R149" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
         </is>
       </c>
       <c r="S149" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
         </is>
       </c>
       <c r="T149" s="13" t="inlineStr"/>
       <c r="U149" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
         </is>
       </c>
       <c r="V149" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>PPO · víctima · legitimación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="150" ht="80" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>auto-2032304</t>
+          <t>pen-ppo-002</t>
         </is>
       </c>
       <c r="B150" s="11" t="n">
@@ -19000,12 +19098,12 @@
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Prisión preventiva oficiosa</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Cese cuando MP no prueba prolongación</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
@@ -19030,57 +19128,57 @@
       </c>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
         </is>
       </c>
       <c r="L150" s="11" t="inlineStr">
         <is>
-          <t>2032304</t>
+          <t>2032108</t>
         </is>
       </c>
       <c r="M150" s="11" t="inlineStr"/>
       <c r="N150" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O150" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P150" s="11" t="inlineStr"/>
       <c r="Q150" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
         </is>
       </c>
       <c r="R150" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
         </is>
       </c>
       <c r="S150" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
         </is>
       </c>
       <c r="T150" s="11" t="inlineStr"/>
       <c r="U150" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032304</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
         </is>
       </c>
       <c r="V150" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="151" ht="80" customHeight="1">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>auto-2032335</t>
+          <t>auto-2032300</t>
         </is>
       </c>
       <c r="B151" s="13" t="n">
@@ -19128,18 +19226,18 @@
       </c>
       <c r="K151" s="14" t="inlineStr">
         <is>
-          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
         </is>
       </c>
       <c r="L151" s="13" t="inlineStr">
         <is>
-          <t>2032335</t>
+          <t>2032300</t>
         </is>
       </c>
       <c r="M151" s="13" t="inlineStr"/>
       <c r="N151" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O151" s="13" t="inlineStr">
@@ -19166,7 +19264,7 @@
       <c r="T151" s="13" t="inlineStr"/>
       <c r="U151" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
         </is>
       </c>
       <c r="V151" s="13" t="inlineStr">
@@ -19178,7 +19276,7 @@
     <row r="152" ht="80" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>auto-2032337</t>
+          <t>auto-2032301</t>
         </is>
       </c>
       <c r="B152" s="11" t="n">
@@ -19226,18 +19324,18 @@
       </c>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>PERSONAS INIMPUTABLES. ES IMPROCEDENTE CONDENARLAS AL PAGO DE LA REPARACIÓN DEL DAÑO, POR LO QUE EL ESTADO DEBE ASUMIRLO DE MANERA SUBSIDIARIA.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
         </is>
       </c>
       <c r="L152" s="11" t="inlineStr">
         <is>
-          <t>2032337</t>
+          <t>2032301</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr"/>
       <c r="N152" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O152" s="11" t="inlineStr">
@@ -19264,7 +19362,7 @@
       <c r="T152" s="11" t="inlineStr"/>
       <c r="U152" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032337</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
         </is>
       </c>
       <c r="V152" s="11" t="inlineStr">
@@ -19276,7 +19374,7 @@
     <row r="153" ht="80" customHeight="1">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>auto-2032390</t>
+          <t>auto-2032304</t>
         </is>
       </c>
       <c r="B153" s="13" t="n">
@@ -19324,18 +19422,18 @@
       </c>
       <c r="K153" s="14" t="inlineStr">
         <is>
-          <t>PAGO DE INDEMNIZACIÓN POR DAÑOS PUNITIVOS. PROCEDE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DEL LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO, Y CONDUCTAS IRREGULARES E INJUSTIFICADAS DERIVADAS DE UN CONTRATO DE SEGURO.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
         </is>
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
-          <t>2032390</t>
+          <t>2032304</t>
         </is>
       </c>
       <c r="M153" s="13" t="inlineStr"/>
       <c r="N153" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O153" s="13" t="inlineStr">
@@ -19362,17 +19460,311 @@
       <c r="T153" s="13" t="inlineStr"/>
       <c r="U153" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032304</t>
+        </is>
+      </c>
+      <c r="V153" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="80" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032335</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H154" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J154" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K154" s="12" t="inlineStr">
+        <is>
+          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
+        </is>
+      </c>
+      <c r="L154" s="11" t="inlineStr">
+        <is>
+          <t>2032335</t>
+        </is>
+      </c>
+      <c r="M154" s="11" t="inlineStr"/>
+      <c r="N154" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O154" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P154" s="11" t="inlineStr"/>
+      <c r="Q154" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R154" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S154" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T154" s="11" t="inlineStr"/>
+      <c r="U154" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+        </is>
+      </c>
+      <c r="V154" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="80" customHeight="1">
+      <c r="A155" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032337</t>
+        </is>
+      </c>
+      <c r="B155" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D155" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F155" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G155" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H155" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J155" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K155" s="14" t="inlineStr">
+        <is>
+          <t>PERSONAS INIMPUTABLES. ES IMPROCEDENTE CONDENARLAS AL PAGO DE LA REPARACIÓN DEL DAÑO, POR LO QUE EL ESTADO DEBE ASUMIRLO DE MANERA SUBSIDIARIA.</t>
+        </is>
+      </c>
+      <c r="L155" s="13" t="inlineStr">
+        <is>
+          <t>2032337</t>
+        </is>
+      </c>
+      <c r="M155" s="13" t="inlineStr"/>
+      <c r="N155" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O155" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P155" s="13" t="inlineStr"/>
+      <c r="Q155" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R155" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S155" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T155" s="13" t="inlineStr"/>
+      <c r="U155" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032337</t>
+        </is>
+      </c>
+      <c r="V155" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="80" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032390</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G156" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H156" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K156" s="12" t="inlineStr">
+        <is>
+          <t>PAGO DE INDEMNIZACIÓN POR DAÑOS PUNITIVOS. PROCEDE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DEL LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO, Y CONDUCTAS IRREGULARES E INJUSTIFICADAS DERIVADAS DE UN CONTRATO DE SEGURO.</t>
+        </is>
+      </c>
+      <c r="L156" s="11" t="inlineStr">
+        <is>
+          <t>2032390</t>
+        </is>
+      </c>
+      <c r="M156" s="11" t="inlineStr"/>
+      <c r="N156" s="11" t="inlineStr">
+        <is>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
+        </is>
+      </c>
+      <c r="O156" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P156" s="11" t="inlineStr"/>
+      <c r="Q156" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R156" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S156" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T156" s="11" t="inlineStr"/>
+      <c r="U156" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032390</t>
         </is>
       </c>
-      <c r="V153" s="13" t="inlineStr">
+      <c r="V156" s="11" t="inlineStr">
         <is>
           <t>Reparación del daño · actualización automática</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V153"/>
+  <autoFilter ref="A1:V156"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19383,7 +19775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20469,7 +20861,7 @@
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>auto-2032278</t>
+          <t>auto-2032420</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
@@ -20487,7 +20879,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -20497,7 +20889,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -20517,18 +20909,18 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>ABUSO DE FUNCIONES. PARA QUE SE CONFIGURE ESE TIPO ADMINISTRATIVO BASTA LA MATERIALIZACIÓN DE CUALQUIERA DE LOS SUPUESTOS ESTABLECIDOS POR EL ARTÍCULO 57 DE LA LEY GENERAL DE RESPONSABILIDADES ADMINISTRATIVAS.</t>
+          <t>PENSIÓN DE CESANTÍA EN EDAD AVANZADA. INTERPRETACIÓN DEL SISTEMA NORMATIVO QUE LA REGULA.</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>2032278</t>
+          <t>2032420</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
@@ -20555,27 +20947,27 @@
       <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032278</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032420</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>civ-agua-002</t>
+          <t>auto-2032278</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Tribunales Colegiados</t>
+          <t>Plenos Regionales</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -20585,22 +20977,22 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Agua y servicios públicos</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Cobros excesivos y nulidad</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
@@ -20610,54 +21002,62 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
+          <t>ABUSO DE FUNCIONES. PARA QUE SE CONFIGURE ESE TIPO ADMINISTRATIVO BASTA LA MATERIALIZACIÓN DE CUALQUIERA DE LOS SUPUESTOS ESTABLECIDOS POR EL ARTÍCULO 57 DE LA LEY GENERAL DE RESPONSABILIDADES ADMINISTRATIVAS.</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>Criterio TJA</t>
+          <t>2032278</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
-      <c r="N13" s="13" t="inlineStr"/>
-      <c r="O13" s="13" t="inlineStr"/>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
+        </is>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P13" s="13" t="inlineStr"/>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S13" s="13" t="inlineStr">
         <is>
-          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr"/>
       <c r="U13" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032278</t>
         </is>
       </c>
       <c r="V13" s="13" t="inlineStr">
         <is>
-          <t>cobro excesivo · medidor · TJA</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-001</t>
+          <t>civ-agua-002</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -20675,12 +21075,12 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud</t>
+          <t>Agua y servicios públicos</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Reasignación sexual — IMSS</t>
+          <t>Cobros excesivos y nulidad</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -20690,7 +21090,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -20700,62 +21100,54 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
+          <t>AGUA. LOS COBROS NOTORIAMENTE EXCESIVOS POR EL SERVICIO PUEDEN COMBATIRSE EN JUICIO CONTENCIOSO ADMINISTRATIVO Y, EN SU CASO, AMPARO INDIRECTO.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>2032111</t>
+          <t>Criterio TJA</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N14" s="11" t="inlineStr"/>
+      <c r="O14" s="11" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
+          <t>El usuario puede impugnar boletas excesivas por la vía contenciosa ante el TJA y, en su caso, amparo indirecto. La autoridad debe motivar el consumo y permitir verificación independiente del medidor.</t>
         </is>
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
+          <t>Vía estándar contra cobros irregulares de SACMEX y similares.</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
+          <t>Solicitar verificación del medidor y aclaración administrativa son requisitos previos. Conservar acuses. El TJA CDMX y Edomex han resuelto favorablemente múltiples casos de cobros aberrantes.</t>
         </is>
       </c>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2008331</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
+          <t>cobro excesivo · medidor · TJA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>amp-sal-002</t>
+          <t>amp-sal-001</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -20778,7 +21170,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Efectos del amparo contra negativa de cirugía</t>
+          <t>Reasignación sexual — IMSS</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -20803,12 +21195,12 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
+          <t>REASIGNACIÓN SEXUAL. EL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DEBE GARANTIZAR A LAS PERSONAS TRANSEXUALES LA POSIBILIDAD DE OPTAR POR UNA INTERVENCIÓN MÉDICA HORMONAL, QUIRÚRGICA O AMBAS.</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>2032110</t>
+          <t>2032111</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
@@ -20825,35 +21217,35 @@
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
+          <t>El IMSS debe garantizar a personas transexuales acceso a tratamientos hormonales, quirúrgicos o combinados de reasignación. La negativa es violatoria del derecho a la salud y la identidad.</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Define alcance positivo del amparo en salud.</t>
+          <t>Hito de inclusión sanitaria de personas trans en sistema social.</t>
         </is>
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
+          <t>Personas trans que sean derechohabientes pueden ampararse contra negativas del IMSS.</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr"/>
       <c r="U15" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032111</t>
         </is>
       </c>
       <c r="V15" s="13" t="inlineStr">
         <is>
-          <t>amparo efectos · cirugía · salud · 12a Época</t>
+          <t>reasignación sexual · IMSS · personas trans · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>amp-sal-003</t>
+          <t>amp-sal-002</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
@@ -20876,7 +21268,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Autonomía IMSS limitada por DDHH</t>
+          <t>Efectos del amparo contra negativa de cirugía</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -20901,12 +21293,12 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
+          <t>REASIGNACIÓN SEXUAL. EFECTOS DEL AMPARO CONCEDIDO CONTRA LA NEGATIVA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL (IMSS) DE PRACTICAR LA CIRUGÍA RELATIVA.</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>2032087</t>
+          <t>2032110</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr"/>
@@ -20923,35 +21315,35 @@
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="11" t="inlineStr">
         <is>
-          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
+          <t>Cuando se concede amparo contra negativa de cirugía de reasignación, los efectos obligan al IMSS a programar y practicar el procedimiento conforme a estándares médicos, no a meramente analizar la petición.</t>
         </is>
       </c>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>Marco general contra negativas burocráticas del IMSS.</t>
+          <t>Define alcance positivo del amparo en salud.</t>
         </is>
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
-          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
+          <t>Sentencia de amparo no es solo papel: ordena ejecutar la cirugía con plazos.</t>
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032110</t>
         </is>
       </c>
       <c r="V16" s="11" t="inlineStr">
         <is>
-          <t>salud · IMSS · autonomía limitada · 12a Época</t>
+          <t>amparo efectos · cirugía · salud · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>auto-2032131</t>
+          <t>amp-sal-003</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -20974,7 +21366,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Autonomía IMSS limitada por DDHH</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -20999,57 +21391,57 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
+          <t>DERECHO HUMANO A LA SALUD. EL MARGEN DE AUTONOMÍA DEL INSTITUTO MEXICANO DEL SEGURO SOCIAL PARA ESTABLECER POLÍTICAS PÚBLICAS, ESTUDIOS Y CAMPAÑAS EN ESA MATERIA, NO IMPLICA QUE ESTÉ EXENTO DE GARANTIZARLO A LAS PERSONAS DERECHOHABIENTES.</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>2032131</t>
+          <t>2032087</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr"/>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr"/>
       <c r="Q17" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La autonomía técnica y administrativa del IMSS para diseñar políticas no lo exime de garantizar el derecho a la salud individualmente. Las políticas no pueden ser pretexto para negar atención.</t>
         </is>
       </c>
       <c r="R17" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Marco general contra negativas burocráticas del IMSS.</t>
         </is>
       </c>
       <c r="S17" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El IMSS no puede escudarse en 'no está en cuadro básico' o 'no es política'.</t>
         </is>
       </c>
       <c r="T17" s="13" t="inlineStr"/>
       <c r="U17" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032087</t>
         </is>
       </c>
       <c r="V17" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano a la salud · actualización automática</t>
+          <t>salud · IMSS · autonomía limitada · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>auto-2032246</t>
+          <t>auto-2032131</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
@@ -21097,18 +21489,18 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>ALIMENTOS A PERSONAS MENORES DE EDAD CON DISCAPACIDAD. SU CONTENIDO COMPRENDE MEDIDAS DE HABILITACIÓN, REHABILITACIÓN Y DESARROLLO INTEGRAL QUE PERMITAN ELIMINAR BARRERAS Y PARTICIPAR DE MANERA PLENA Y EFECTIVA EN LA SOCIEDAD EN CONDICIONES DE IGUALDAD.</t>
+          <t>PENSIONES EN EL ESTADO DE JALISCO. EL ARTÍCULO 52 DE LA LEY DEL INSTITUTO DE PENSIONES DE LA ENTIDAD FEDERATIVA VIOLA EL DERECHO A LA SEGURIDAD SOCIAL.</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>2032246</t>
+          <t>2032131</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
@@ -21135,7 +21527,7 @@
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032246</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032131</t>
         </is>
       </c>
       <c r="V18" s="11" t="inlineStr">
@@ -21147,7 +21539,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>auto-2032262</t>
+          <t>auto-2032246</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -21195,12 +21587,12 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DEL AMPARO POR CESACIÓN DE EFECTOS. NO SE ACTUALIZA CUANDO SE RECLAMA LA OMISIÓN DE UNA INSTITUCIÓN DE SALUD PÚBLICA DE ENTREGAR UN MEDICAMENTO A UNA PERSONA POR EL HECHO DE SUMINISTRARLO EN UNA OCASIÓN, SI DEBE SER CONSTANTE Y CONTINUO.</t>
+          <t>ALIMENTOS A PERSONAS MENORES DE EDAD CON DISCAPACIDAD. SU CONTENIDO COMPRENDE MEDIDAS DE HABILITACIÓN, REHABILITACIÓN Y DESARROLLO INTEGRAL QUE PERMITAN ELIMINAR BARRERAS Y PARTICIPAR DE MANERA PLENA Y EFECTIVA EN LA SOCIEDAD EN CONDICIONES DE IGUALDAD.</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>2032262</t>
+          <t>2032246</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
@@ -21233,7 +21625,7 @@
       <c r="T19" s="13" t="inlineStr"/>
       <c r="U19" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032262</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032246</t>
         </is>
       </c>
       <c r="V19" s="13" t="inlineStr">
@@ -21245,7 +21637,7 @@
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>auto-2032353</t>
+          <t>auto-2032262</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
@@ -21293,18 +21685,18 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN DE PLANO EN AMPARO INDIRECTO. PROCEDE PARA ORDENAR UNA VALORACIÓN MÉDICA EN EL DOMICILIO DE UNA PERSONA, CUANDO TIENE UNA MOVILIDAD RESTRINGIDA.</t>
+          <t>IMPROCEDENCIA DEL AMPARO POR CESACIÓN DE EFECTOS. NO SE ACTUALIZA CUANDO SE RECLAMA LA OMISIÓN DE UNA INSTITUCIÓN DE SALUD PÚBLICA DE ENTREGAR UN MEDICAMENTO A UNA PERSONA POR EL HECHO DE SUMINISTRARLO EN UNA OCASIÓN, SI DEBE SER CONSTANTE Y CONTINUO.</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>2032353</t>
+          <t>2032262</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
@@ -21331,7 +21723,7 @@
       <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032353</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032262</t>
         </is>
       </c>
       <c r="V20" s="11" t="inlineStr">
@@ -21343,7 +21735,7 @@
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>auto-2032177</t>
+          <t>auto-2032353</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
@@ -21361,7 +21753,7 @@
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -21391,18 +21783,18 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>SUSPENSIÓN DE PLANO EN AMPARO INDIRECTO. PROCEDE PARA ORDENAR UNA VALORACIÓN MÉDICA EN EL DOMICILIO DE UNA PERSONA, CUANDO TIENE UNA MOVILIDAD RESTRINGIDA.</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>2032177</t>
+          <t>2032353</t>
         </is>
       </c>
       <c r="M21" s="13" t="inlineStr"/>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O21" s="13" t="inlineStr">
@@ -21429,19 +21821,19 @@
       <c r="T21" s="13" t="inlineStr"/>
       <c r="U21" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032353</t>
         </is>
       </c>
       <c r="V21" s="13" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>auto-2032233</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
@@ -21489,18 +21881,18 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>2032233</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
@@ -21527,7 +21919,7 @@
       <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr">
@@ -21539,7 +21931,7 @@
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>auto-2032330</t>
+          <t>auto-2032233</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
@@ -21567,7 +21959,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -21587,18 +21979,18 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
+          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>2032330</t>
+          <t>2032233</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr"/>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 05 de junio de 2026 10:11</t>
         </is>
       </c>
       <c r="O23" s="13" t="inlineStr">
@@ -21625,17 +22017,115 @@
       <c r="T23" s="13" t="inlineStr"/>
       <c r="U23" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
+        </is>
+      </c>
+      <c r="V23" s="13" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032330</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>2032330</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr"/>
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr"/>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
         </is>
       </c>
-      <c r="V23" s="13" t="inlineStr">
+      <c r="V24" s="11" t="inlineStr">
         <is>
           <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V23"/>
+  <autoFilter ref="A1:V24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22753,7 +23243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V39"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24947,7 +25437,7 @@
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>auto-2032412</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -24970,7 +25460,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -24980,7 +25470,7 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
@@ -24990,54 +25480,62 @@
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>DESECHAMIENTO DE LA DEMANDA EN EL JUICIO ORAL MERCANTIL. ES INVÁLIDO CUANDO SE BASA EN UNA APRECIACIÓN FORMAL DEL DESAHOGO DE LA PREVENCIÓN REALIZADA EN TÉRMINOS DEL ARTÍCULO 1390 BIS 12 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2032412</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr"/>
-      <c r="N24" s="11" t="inlineStr"/>
-      <c r="O24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P24" s="11" t="inlineStr"/>
       <c r="Q24" s="11" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R24" s="11" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S24" s="11" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032412</t>
         </is>
       </c>
       <c r="V24" s="11" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
@@ -25060,7 +25558,7 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -25070,7 +25568,7 @@
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
@@ -25080,62 +25578,54 @@
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr"/>
-      <c r="N25" s="13" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O25" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N25" s="13" t="inlineStr"/>
+      <c r="O25" s="13" t="inlineStr"/>
       <c r="P25" s="13" t="inlineStr"/>
       <c r="Q25" s="13" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R25" s="13" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S25" s="13" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T25" s="13" t="inlineStr"/>
       <c r="U25" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V25" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="26" ht="80" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
@@ -25158,7 +25648,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -25168,7 +25658,7 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -25178,62 +25668,62 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr"/>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P26" s="11" t="inlineStr"/>
       <c r="Q26" s="11" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R26" s="11" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S26" s="11" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V26" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
@@ -25251,12 +25741,12 @@
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
@@ -25266,7 +25756,7 @@
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
@@ -25281,57 +25771,57 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr"/>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr"/>
       <c r="Q27" s="13" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R27" s="13" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S27" s="13" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T27" s="13" t="inlineStr"/>
       <c r="U27" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V27" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
@@ -25354,7 +25844,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
@@ -25364,7 +25854,7 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -25374,23 +25864,23 @@
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr"/>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
@@ -25401,35 +25891,35 @@
       <c r="P28" s="11" t="inlineStr"/>
       <c r="Q28" s="11" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R28" s="11" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S28" s="11" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V28" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
@@ -25447,12 +25937,12 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
@@ -25477,57 +25967,57 @@
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O29" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P29" s="13" t="inlineStr"/>
       <c r="Q29" s="13" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R29" s="13" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S29" s="13" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T29" s="13" t="inlineStr"/>
       <c r="U29" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V29" s="13" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
@@ -25545,12 +26035,12 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -25575,18 +26065,18 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
@@ -25597,35 +26087,35 @@
       <c r="P30" s="11" t="inlineStr"/>
       <c r="Q30" s="11" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S30" s="11" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="31" ht="80" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>auto-2032124</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
@@ -25643,12 +26133,12 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -25658,7 +26148,7 @@
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
@@ -25673,57 +26163,57 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>2032124</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr"/>
       <c r="N31" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr"/>
       <c r="Q31" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R31" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S31" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T31" s="13" t="inlineStr"/>
       <c r="U31" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V31" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="32" ht="80" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
@@ -25746,7 +26236,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G32" s="11" t="inlineStr">
@@ -25756,7 +26246,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -25766,54 +26256,62 @@
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr"/>
-      <c r="N32" s="11" t="inlineStr"/>
-      <c r="O32" s="11" t="inlineStr"/>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P32" s="11" t="inlineStr"/>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R32" s="11" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S32" s="11" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="33" ht="80" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
@@ -25836,7 +26334,7 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -25846,7 +26344,7 @@
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -25856,62 +26354,54 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr"/>
-      <c r="N33" s="13" t="inlineStr">
-        <is>
-          <t>Novena Época</t>
-        </is>
-      </c>
-      <c r="O33" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N33" s="13" t="inlineStr"/>
+      <c r="O33" s="13" t="inlineStr"/>
       <c r="P33" s="13" t="inlineStr"/>
       <c r="Q33" s="13" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R33" s="13" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S33" s="13" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T33" s="13" t="inlineStr"/>
       <c r="U33" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V33" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="34" ht="80" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
@@ -25934,7 +26424,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -25954,17 +26444,17 @@
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr"/>
@@ -25975,41 +26465,41 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr"/>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R34" s="11" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S34" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="35" ht="80" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
@@ -26027,22 +26517,22 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
@@ -26052,58 +26542,62 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr"/>
       <c r="N35" s="13" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O35" s="13" t="inlineStr"/>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O35" s="13" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P35" s="13" t="inlineStr"/>
       <c r="Q35" s="13" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R35" s="13" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S35" s="13" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T35" s="13" t="inlineStr"/>
       <c r="U35" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V35" s="13" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="36" ht="80" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
@@ -26121,22 +26615,22 @@
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -26146,62 +26640,58 @@
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O36" s="11" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="inlineStr"/>
       <c r="P36" s="11" t="inlineStr"/>
       <c r="Q36" s="11" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R36" s="11" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S36" s="11" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T36" s="11" t="inlineStr"/>
       <c r="U36" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V36" s="11" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="37" ht="80" customHeight="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>auto-2032319</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
@@ -26219,12 +26709,12 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -26249,57 +26739,57 @@
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>2032319</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr"/>
       <c r="N37" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O37" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P37" s="13" t="inlineStr"/>
       <c r="Q37" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R37" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S37" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T37" s="13" t="inlineStr"/>
       <c r="U37" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V37" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva · actualización automática</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="38" ht="80" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>auto-2032319</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
@@ -26322,17 +26812,17 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -26342,58 +26832,62 @@
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>2032319</t>
         </is>
       </c>
       <c r="M38" s="11" t="inlineStr"/>
-      <c r="N38" s="11" t="inlineStr"/>
+      <c r="N38" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr"/>
       <c r="Q38" s="11" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R38" s="11" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S38" s="11" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>Usucapión / Prescripción positiva · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="39" ht="80" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
@@ -26416,7 +26910,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
@@ -26426,7 +26920,7 @@
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
@@ -26436,52 +26930,146 @@
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr"/>
       <c r="N39" s="13" t="inlineStr"/>
-      <c r="O39" s="13" t="inlineStr"/>
+      <c r="O39" s="13" t="inlineStr">
+        <is>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+        </is>
+      </c>
       <c r="P39" s="13" t="inlineStr"/>
       <c r="Q39" s="13" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R39" s="13" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S39" s="13" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T39" s="13" t="inlineStr"/>
       <c r="U39" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+        </is>
+      </c>
+      <c r="V39" s="13" t="inlineStr">
+        <is>
+          <t>pericial · topografía · identidad del bien</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>civ-usu-005</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Civil</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>Usucapión / Prescripción positiva</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Posesión derivada vs. originaria</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>jurisprudencia</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+        </is>
+      </c>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
+          <t>2030499</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="inlineStr"/>
+      <c r="N40" s="11" t="inlineStr"/>
+      <c r="O40" s="11" t="inlineStr"/>
+      <c r="P40" s="11" t="inlineStr"/>
+      <c r="Q40" s="11" t="inlineStr">
+        <is>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+        </is>
+      </c>
+      <c r="R40" s="11" t="inlineStr">
+        <is>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+        </is>
+      </c>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+        </is>
+      </c>
+      <c r="T40" s="11" t="inlineStr"/>
+      <c r="U40" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
-      <c r="V39" s="13" t="inlineStr">
+      <c r="V40" s="11" t="inlineStr">
         <is>
           <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V39"/>
+  <autoFilter ref="A1:V40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
